--- a/Hardware-Designing/Deliverables/BOM/LCSC BOM.xlsx
+++ b/Hardware-Designing/Deliverables/BOM/LCSC BOM.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14400" windowHeight="12345"/>
+    <workbookView windowWidth="24000" windowHeight="9795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -436,14 +436,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="&quot;$&quot;#,##0.00000"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.00000"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -504,6 +504,13 @@
     <font>
       <u/>
       <sz val="10"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
       <color theme="10"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -520,11 +527,93 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -543,57 +632,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -602,50 +640,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -656,8 +662,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -684,73 +691,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -762,109 +871,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1046,17 +1053,28 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1076,35 +1094,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1126,11 +1120,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1146,15 +1153,15 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1164,133 +1171,133 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1361,22 +1368,19 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1389,16 +1393,16 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="10" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -1774,10 +1778,10 @@
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="32"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="31"/>
       <c r="S1" s="2"/>
-      <c r="T1" s="32"/>
+      <c r="T1" s="31"/>
     </row>
     <row r="2" ht="16.5" spans="1:20">
       <c r="A2" s="4" t="s">
@@ -1834,14 +1838,14 @@
       <c r="R2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="33" t="s">
+      <c r="S2" s="32" t="s">
         <v>19</v>
       </c>
       <c r="T2" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" ht="15.75" spans="1:20">
+    <row r="3" spans="1:20">
       <c r="A3" s="7">
         <v>1</v>
       </c>
@@ -1851,13 +1855,13 @@
       <c r="C3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="40" t="s">
+      <c r="E3" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="40" t="s">
+      <c r="F3" s="39" t="s">
         <v>25</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -1869,7 +1873,7 @@
       <c r="I3" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="41" t="s">
+      <c r="J3" s="40" t="s">
         <v>29</v>
       </c>
       <c r="K3" s="11">
@@ -1903,9 +1907,9 @@
         <f>R3*M3</f>
         <v>0.126</v>
       </c>
-      <c r="T3" s="34"/>
+      <c r="T3" s="33"/>
     </row>
-    <row r="4" ht="15.75" spans="1:20">
+    <row r="4" spans="1:20">
       <c r="A4" s="7">
         <v>2</v>
       </c>
@@ -1913,13 +1917,13 @@
       <c r="C4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="F4" s="40" t="s">
         <v>33</v>
       </c>
       <c r="G4" s="11" t="s">
@@ -1931,7 +1935,7 @@
       <c r="I4" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="41" t="s">
+      <c r="J4" s="40" t="s">
         <v>35</v>
       </c>
       <c r="K4" s="11">
@@ -1965,7 +1969,7 @@
         <f t="shared" ref="S4:S21" si="3">R4*M4</f>
         <v>0.051</v>
       </c>
-      <c r="T4" s="34"/>
+      <c r="T4" s="33"/>
     </row>
     <row r="5" ht="16.5" spans="1:20">
       <c r="A5" s="7">
@@ -1974,16 +1978,16 @@
       <c r="B5" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="40" t="s">
+      <c r="F5" s="39" t="s">
         <v>40</v>
       </c>
       <c r="G5" s="11" t="s">
@@ -2001,14 +2005,14 @@
       <c r="K5" s="11">
         <v>4</v>
       </c>
-      <c r="L5" s="26">
+      <c r="L5" s="22">
         <v>30</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="N5" s="23" t="s">
+      <c r="N5" s="26" t="s">
         <v>30</v>
       </c>
       <c r="O5" s="24">
@@ -2029,7 +2033,7 @@
         <f t="shared" si="3"/>
         <v>1.264</v>
       </c>
-      <c r="T5" s="34"/>
+      <c r="T5" s="33"/>
     </row>
     <row r="6" ht="16.5" spans="1:20">
       <c r="A6" s="7">
@@ -2038,16 +2042,16 @@
       <c r="B6" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="41" t="s">
+      <c r="D6" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="41" t="s">
+      <c r="F6" s="40" t="s">
         <v>48</v>
       </c>
       <c r="G6" s="11" t="s">
@@ -2093,9 +2097,9 @@
         <f t="shared" si="3"/>
         <v>0.562</v>
       </c>
-      <c r="T6" s="34"/>
+      <c r="T6" s="33"/>
     </row>
-    <row r="7" ht="15.75" spans="1:20">
+    <row r="7" spans="1:20">
       <c r="A7" s="7">
         <v>5</v>
       </c>
@@ -2105,13 +2109,13 @@
       <c r="C7" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="41" t="s">
+      <c r="E7" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="41" t="s">
+      <c r="F7" s="40" t="s">
         <v>55</v>
       </c>
       <c r="G7" s="11" t="s">
@@ -2123,7 +2127,7 @@
       <c r="I7" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="J7" s="41" t="s">
+      <c r="J7" s="40" t="s">
         <v>59</v>
       </c>
       <c r="K7" s="14">
@@ -2136,7 +2140,7 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="N7" s="23" t="s">
+      <c r="N7" s="26" t="s">
         <v>30</v>
       </c>
       <c r="O7" s="24">
@@ -2157,23 +2161,23 @@
         <f t="shared" si="3"/>
         <v>0.03</v>
       </c>
-      <c r="T7" s="34"/>
+      <c r="T7" s="33"/>
     </row>
     <row r="8" ht="15.75" spans="1:20">
       <c r="A8" s="7">
         <v>6</v>
       </c>
       <c r="B8" s="15"/>
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="41" t="s">
+      <c r="D8" s="40" t="s">
         <v>61</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="41" t="s">
+      <c r="F8" s="40" t="s">
         <v>63</v>
       </c>
       <c r="G8" s="11" t="s">
@@ -2181,7 +2185,7 @@
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="11"/>
-      <c r="J8" s="41" t="s">
+      <c r="J8" s="40" t="s">
         <v>59</v>
       </c>
       <c r="K8" s="14">
@@ -2192,7 +2196,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N8" s="23"/>
+      <c r="N8" s="26"/>
       <c r="O8" s="24"/>
       <c r="P8" s="25">
         <f t="shared" si="1"/>
@@ -2207,23 +2211,23 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T8" s="34"/>
+      <c r="T8" s="33"/>
     </row>
     <row r="9" ht="15.75" spans="1:20">
       <c r="A9" s="7">
         <v>7</v>
       </c>
       <c r="B9" s="15"/>
-      <c r="C9" s="43" t="s">
+      <c r="C9" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="41" t="s">
+      <c r="D9" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="E9" s="41" t="s">
+      <c r="E9" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="41" t="s">
+      <c r="F9" s="40" t="s">
         <v>67</v>
       </c>
       <c r="G9" s="11" t="s">
@@ -2235,7 +2239,7 @@
       <c r="I9" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J9" s="41" t="s">
+      <c r="J9" s="40" t="s">
         <v>70</v>
       </c>
       <c r="K9" s="14">
@@ -2248,7 +2252,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N9" s="23" t="s">
+      <c r="N9" s="26" t="s">
         <v>30</v>
       </c>
       <c r="O9" s="24">
@@ -2269,7 +2273,7 @@
         <f t="shared" si="3"/>
         <v>0.0075</v>
       </c>
-      <c r="T9" s="34"/>
+      <c r="T9" s="33"/>
     </row>
     <row r="10" ht="15.75" spans="1:20">
       <c r="A10" s="7">
@@ -2279,13 +2283,13 @@
       <c r="C10" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="41" t="s">
+      <c r="D10" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="E10" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="41" t="s">
+      <c r="F10" s="40" t="s">
         <v>73</v>
       </c>
       <c r="G10" s="11" t="s">
@@ -2297,7 +2301,7 @@
       <c r="I10" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="J10" s="41" t="s">
+      <c r="J10" s="40" t="s">
         <v>76</v>
       </c>
       <c r="K10" s="14">
@@ -2310,7 +2314,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N10" s="23" t="s">
+      <c r="N10" s="26" t="s">
         <v>30</v>
       </c>
       <c r="O10" s="24">
@@ -2331,7 +2335,7 @@
         <f t="shared" si="3"/>
         <v>0.0085</v>
       </c>
-      <c r="T10" s="34"/>
+      <c r="T10" s="33"/>
     </row>
     <row r="11" ht="15.75" spans="1:20">
       <c r="A11" s="7">
@@ -2341,13 +2345,13 @@
       <c r="C11" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="41" t="s">
+      <c r="D11" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="E11" s="41" t="s">
+      <c r="E11" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="41" t="s">
+      <c r="F11" s="40" t="s">
         <v>79</v>
       </c>
       <c r="G11" s="11" t="s">
@@ -2359,7 +2363,7 @@
       <c r="I11" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="41" t="s">
+      <c r="J11" s="40" t="s">
         <v>81</v>
       </c>
       <c r="K11" s="14">
@@ -2372,7 +2376,7 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="N11" s="23" t="s">
+      <c r="N11" s="26" t="s">
         <v>30</v>
       </c>
       <c r="O11" s="25">
@@ -2402,16 +2406,16 @@
       <c r="B12" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="43" t="s">
+      <c r="C12" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="D12" s="41" t="s">
+      <c r="D12" s="40" t="s">
         <v>84</v>
       </c>
       <c r="E12" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="41" t="s">
+      <c r="F12" s="40" t="s">
         <v>85</v>
       </c>
       <c r="G12" s="11"/>
@@ -2428,7 +2432,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N12" s="28"/>
+      <c r="N12" s="26"/>
       <c r="O12" s="25"/>
       <c r="P12" s="25">
         <f t="shared" si="1"/>
@@ -2452,16 +2456,16 @@
       <c r="B13" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="43" t="s">
+      <c r="C13" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="41" t="s">
+      <c r="D13" s="40" t="s">
         <v>88</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="41" t="s">
+      <c r="F13" s="40" t="s">
         <v>89</v>
       </c>
       <c r="G13" s="11" t="s">
@@ -2486,7 +2490,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N13" s="23" t="s">
+      <c r="N13" s="26" t="s">
         <v>30</v>
       </c>
       <c r="O13" s="24">
@@ -2507,7 +2511,7 @@
         <f t="shared" si="3"/>
         <v>4.166</v>
       </c>
-      <c r="T13" s="35"/>
+      <c r="T13" s="34"/>
     </row>
     <row r="14" ht="15.75" spans="1:20">
       <c r="A14" s="7">
@@ -2516,16 +2520,16 @@
       <c r="B14" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="43" t="s">
+      <c r="C14" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="D14" s="41" t="s">
+      <c r="D14" s="40" t="s">
         <v>94</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="41" t="s">
+      <c r="F14" s="40" t="s">
         <v>95</v>
       </c>
       <c r="G14" s="11" t="s">
@@ -2550,7 +2554,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N14" s="23" t="s">
+      <c r="N14" s="26" t="s">
         <v>30</v>
       </c>
       <c r="O14" s="25">
@@ -2571,23 +2575,23 @@
         <f t="shared" si="3"/>
         <v>25.5525</v>
       </c>
-      <c r="T14" s="36"/>
+      <c r="T14" s="35"/>
     </row>
     <row r="15" ht="15.75" spans="1:20">
       <c r="A15" s="7">
         <v>13</v>
       </c>
       <c r="B15" s="15"/>
-      <c r="C15" s="43" t="s">
+      <c r="C15" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="D15" s="41" t="s">
+      <c r="D15" s="40" t="s">
         <v>99</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="F15" s="41" t="s">
+      <c r="F15" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G15" s="11" t="s">
@@ -2606,8 +2610,8 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N15" s="29"/>
-      <c r="O15" s="29"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28"/>
       <c r="P15" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2616,12 +2620,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R15" s="37"/>
+      <c r="R15" s="36"/>
       <c r="S15" s="25">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T15" s="37"/>
+      <c r="T15" s="36"/>
     </row>
     <row r="16" ht="15.75" spans="1:20">
       <c r="A16" s="7">
@@ -2631,13 +2635,13 @@
       <c r="C16" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="D16" s="41" t="s">
+      <c r="D16" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="E16" s="41" t="s">
+      <c r="E16" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="F16" s="41" t="s">
+      <c r="F16" s="40" t="s">
         <v>106</v>
       </c>
       <c r="G16" s="11" t="s">
@@ -2662,7 +2666,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N16" s="23" t="s">
+      <c r="N16" s="26" t="s">
         <v>30</v>
       </c>
       <c r="O16" s="25">
@@ -2683,7 +2687,7 @@
         <f t="shared" si="3"/>
         <v>1.256</v>
       </c>
-      <c r="T16" s="37"/>
+      <c r="T16" s="36"/>
     </row>
     <row r="17" ht="15.75" spans="1:20">
       <c r="A17" s="7">
@@ -2693,13 +2697,13 @@
       <c r="C17" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="D17" s="41" t="s">
+      <c r="D17" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="E17" s="41" t="s">
+      <c r="E17" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="F17" s="41" t="s">
+      <c r="F17" s="40" t="s">
         <v>112</v>
       </c>
       <c r="G17" s="11" t="s">
@@ -2724,7 +2728,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N17" s="23" t="s">
+      <c r="N17" s="26" t="s">
         <v>30</v>
       </c>
       <c r="O17" s="25">
@@ -2745,7 +2749,7 @@
         <f t="shared" si="3"/>
         <v>8.25</v>
       </c>
-      <c r="T17" s="38"/>
+      <c r="T17" s="37"/>
     </row>
     <row r="18" ht="15.75" spans="1:20">
       <c r="A18" s="7">
@@ -2754,16 +2758,16 @@
       <c r="B18" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="C18" s="43" t="s">
+      <c r="C18" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="D18" s="41" t="s">
+      <c r="D18" s="40" t="s">
         <v>117</v>
       </c>
       <c r="E18" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="F18" s="41" t="s">
+      <c r="F18" s="40" t="s">
         <v>118</v>
       </c>
       <c r="G18" s="11" t="s">
@@ -2778,7 +2782,7 @@
       <c r="J18" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K18" s="30">
+      <c r="K18" s="29">
         <v>1</v>
       </c>
       <c r="L18" s="22">
@@ -2788,7 +2792,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N18" s="23" t="s">
+      <c r="N18" s="26" t="s">
         <v>30</v>
       </c>
       <c r="O18" s="25">
@@ -2809,7 +2813,7 @@
         <f t="shared" si="3"/>
         <v>1.121</v>
       </c>
-      <c r="T18" s="39"/>
+      <c r="T18" s="38"/>
     </row>
     <row r="19" ht="15.75" spans="1:20">
       <c r="A19" s="7">
@@ -2819,13 +2823,13 @@
       <c r="C19" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="D19" s="40" t="s">
+      <c r="D19" s="39" t="s">
         <v>122</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="40" t="s">
+      <c r="F19" s="39" t="s">
         <v>123</v>
       </c>
       <c r="G19" s="11" t="s">
@@ -2840,7 +2844,7 @@
       <c r="J19" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K19" s="30">
+      <c r="K19" s="29">
         <v>1</v>
       </c>
       <c r="L19" s="22">
@@ -2850,7 +2854,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N19" s="23" t="s">
+      <c r="N19" s="26" t="s">
         <v>30</v>
       </c>
       <c r="O19" s="25">
@@ -2871,23 +2875,23 @@
         <f t="shared" si="3"/>
         <v>0.155</v>
       </c>
-      <c r="T19" s="39"/>
+      <c r="T19" s="38"/>
     </row>
     <row r="20" ht="15.75" spans="1:20">
       <c r="A20" s="7">
         <v>18</v>
       </c>
       <c r="B20" s="19"/>
-      <c r="C20" s="43" t="s">
+      <c r="C20" s="42" t="s">
         <v>126</v>
       </c>
-      <c r="D20" s="41" t="s">
+      <c r="D20" s="40" t="s">
         <v>127</v>
       </c>
       <c r="E20" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="F20" s="41" t="s">
+      <c r="F20" s="40" t="s">
         <v>128</v>
       </c>
       <c r="G20" s="11" t="s">
@@ -2902,7 +2906,7 @@
       <c r="J20" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K20" s="30">
+      <c r="K20" s="29">
         <v>1</v>
       </c>
       <c r="L20" s="22">
@@ -2912,7 +2916,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N20" s="23" t="s">
+      <c r="N20" s="26" t="s">
         <v>30</v>
       </c>
       <c r="O20" s="25">
@@ -2933,23 +2937,23 @@
         <f t="shared" si="3"/>
         <v>0.248</v>
       </c>
-      <c r="T20" s="39"/>
+      <c r="T20" s="38"/>
     </row>
     <row r="21" ht="15.75" spans="1:20">
       <c r="A21" s="7">
         <v>19</v>
       </c>
       <c r="B21" s="20"/>
-      <c r="C21" s="43" t="s">
+      <c r="C21" s="42" t="s">
         <v>130</v>
       </c>
-      <c r="D21" s="41" t="s">
+      <c r="D21" s="40" t="s">
         <v>131</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="F21" s="41" t="s">
+      <c r="F21" s="40" t="s">
         <v>132</v>
       </c>
       <c r="G21" s="11" t="s">
@@ -2964,7 +2968,7 @@
       <c r="J21" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K21" s="30">
+      <c r="K21" s="29">
         <v>5</v>
       </c>
       <c r="L21" s="11" t="s">
@@ -2992,7 +2996,7 @@
       <c r="S21" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="T21" s="39"/>
+      <c r="T21" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3023,7 +3027,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cdb3d112-8688-489c-bd87-ba9c8af473f4}</x14:id>
+          <x14:id>{cd993221-8966-4a70-95a1-78e348db6a81}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3037,7 +3041,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{397039e1-9e62-4ef1-a35c-9d6ca27cf6ff}</x14:id>
+          <x14:id>{a076f2c8-98ba-47b2-bf63-4eebf46a19ba}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3051,7 +3055,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c48074dc-3e13-47aa-9721-310de81d0939}</x14:id>
+          <x14:id>{b891dcfd-4448-437e-8894-c31c7321d958}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3080,7 +3084,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cdb3d112-8688-489c-bd87-ba9c8af473f4}">
+          <x14:cfRule type="dataBar" id="{cd993221-8966-4a70-95a1-78e348db6a81}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -3093,7 +3097,7 @@
           <xm:sqref>P3:P20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{397039e1-9e62-4ef1-a35c-9d6ca27cf6ff}">
+          <x14:cfRule type="dataBar" id="{a076f2c8-98ba-47b2-bf63-4eebf46a19ba}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -3106,7 +3110,7 @@
           <xm:sqref>S3:S20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c48074dc-3e13-47aa-9721-310de81d0939}">
+          <x14:cfRule type="dataBar" id="{b891dcfd-4448-437e-8894-c31c7321d958}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/Hardware-Designing/Deliverables/BOM/LCSC BOM.xlsx
+++ b/Hardware-Designing/Deliverables/BOM/LCSC BOM.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9795"/>
+    <workbookView windowWidth="28800" windowHeight="12495"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="180">
   <si>
     <t>Bill of Material (BOM) for  Martin Transmitter</t>
   </si>
@@ -86,7 +86,7 @@
 </t>
   </si>
   <si>
-    <t>C1, C2, C3, C4</t>
+    <t>C1, C2, C3, C4, C11, C13</t>
   </si>
   <si>
     <t>CAP-0603</t>
@@ -99,16 +99,38 @@
 </t>
   </si>
   <si>
-    <t>C913912</t>
+    <t xml:space="preserve">C76711
+</t>
+  </si>
+  <si>
+    <t>CGA3E2X7R1H104KT0Y0N</t>
+  </si>
+  <si>
+    <t>0.1uF</t>
+  </si>
+  <si>
+    <t>LCSC</t>
+  </si>
+  <si>
+    <t>CAP CER 4.7UF 25V X5R 0603</t>
+  </si>
+  <si>
+    <t>C10, C12</t>
+  </si>
+  <si>
+    <t>GRM188R61E475KE11D</t>
+  </si>
+  <si>
+    <t>Murata</t>
+  </si>
+  <si>
+    <t>C90057</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>0.1uF</t>
-  </si>
-  <si>
-    <t>LCSC</t>
+    <t>4.7uF</t>
   </si>
   <si>
     <t xml:space="preserve">CAP CER 1UF 25V X5R 0603
@@ -174,6 +196,39 @@
     <t>C139445</t>
   </si>
   <si>
+    <t xml:space="preserve">TRANS NPN 40V 0.6A SMD SOT23-3
+</t>
+  </si>
+  <si>
+    <t>Q2, Q3</t>
+  </si>
+  <si>
+    <t>sot-23</t>
+  </si>
+  <si>
+    <t>MMBT2222A-7-F</t>
+  </si>
+  <si>
+    <t>C94515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOSFET N/P-CH 60V/50V SC70-6
+</t>
+  </si>
+  <si>
+    <t>Q4</t>
+  </si>
+  <si>
+    <t>SOT-363</t>
+  </si>
+  <si>
+    <t>BSS8402DW-7-F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C156386
+</t>
+  </si>
+  <si>
     <t>Resistors</t>
   </si>
   <si>
@@ -181,7 +236,7 @@
 </t>
   </si>
   <si>
-    <t>R4, R5, R6, R8, R11</t>
+    <t>R6, R8, R11, R15, R16</t>
   </si>
   <si>
     <t>RES-0603</t>
@@ -218,10 +273,13 @@
 </t>
   </si>
   <si>
+    <t>Local Supplier</t>
+  </si>
+  <si>
     <t>RES SMD 4.7K OHM 1% 1/10W 0603</t>
   </si>
   <si>
-    <t>R9</t>
+    <t>R9, R26</t>
   </si>
   <si>
     <t>RC0603FR-074K7L</t>
@@ -271,6 +329,91 @@
     <t>560R</t>
   </si>
   <si>
+    <t>RES 1K OHM 5% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>R18</t>
+  </si>
+  <si>
+    <t>RMCF0603JJ1K00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stackpole </t>
+  </si>
+  <si>
+    <t>C103209</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>RES SMD 22.1K OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>R19</t>
+  </si>
+  <si>
+    <t>ERJ-3EKF2212V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panasonic </t>
+  </si>
+  <si>
+    <t>C25961</t>
+  </si>
+  <si>
+    <t>22.1K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RES 47.5K OHM 1% 1/10W 0603
+</t>
+  </si>
+  <si>
+    <t>R20</t>
+  </si>
+  <si>
+    <t>RC0603FR-0747K5L</t>
+  </si>
+  <si>
+    <t>C137715</t>
+  </si>
+  <si>
+    <t>45.K</t>
+  </si>
+  <si>
+    <t>RES SMD 0 OHM JUMPER 1/10W 0603</t>
+  </si>
+  <si>
+    <t>R21</t>
+  </si>
+  <si>
+    <t>RC0603JR-070RP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C100699
+</t>
+  </si>
+  <si>
+    <t>0R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RES 100K OHM 5% 1/10W 0603
+</t>
+  </si>
+  <si>
+    <t>R22, R23, R24, R25</t>
+  </si>
+  <si>
+    <t>RC0603JR-07100KL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C100048
+</t>
+  </si>
+  <si>
+    <t>100K</t>
+  </si>
+  <si>
     <t>Sensor</t>
   </si>
   <si>
@@ -320,23 +463,6 @@
     <t>C529577</t>
   </si>
   <si>
-    <t>IC ADC 12BIT SIGMA-DELTA 10VSSOP</t>
-  </si>
-  <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10-VSSOP
-</t>
-  </si>
-  <si>
-    <t>ADS1013IDGST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Texas Instruments
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">IC COMP DUAL VOLT LP 8SOIC
 </t>
   </si>
@@ -375,6 +501,25 @@
     <t>C145519</t>
   </si>
   <si>
+    <t>IC USB TO UART BRIDGE QFN24</t>
+  </si>
+  <si>
+    <t>U5</t>
+  </si>
+  <si>
+    <t>QFN-24_4x4</t>
+  </si>
+  <si>
+    <t>CP2102N-A02-GQFN24R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silicon Labs
+</t>
+  </si>
+  <si>
+    <t>C969151</t>
+  </si>
+  <si>
     <t>Connector</t>
   </si>
   <si>
@@ -410,16 +555,13 @@
     <t>C158012</t>
   </si>
   <si>
-    <t>CONN HEADER VERT 4POS 2.5MM</t>
-  </si>
-  <si>
-    <t>J3</t>
-  </si>
-  <si>
-    <t>B4B-XH-A(LF)(SN)</t>
-  </si>
-  <si>
-    <t>C144395</t>
+    <t>Solder Bridge ON</t>
+  </si>
+  <si>
+    <t>SB1</t>
+  </si>
+  <si>
+    <t>Solder Bridge</t>
   </si>
   <si>
     <t>Test Point ON</t>
@@ -429,6 +571,12 @@
   </si>
   <si>
     <t>TEST POINT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Component Cost </t>
+  </si>
+  <si>
+    <t>Single Board Cost</t>
   </si>
 </sst>
 </file>
@@ -436,14 +584,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.00000"/>
+    <numFmt numFmtId="178" formatCode="&quot;$&quot;#,##0.00000"/>
+    <numFmt numFmtId="179" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -486,10 +634,17 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -504,21 +659,22 @@
     <font>
       <u/>
       <sz val="10"/>
-      <color rgb="FF800080"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
-      <color theme="10"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="14"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -527,11 +683,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <sz val="10"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -542,36 +696,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -585,11 +717,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -602,6 +740,14 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="Calibri"/>
@@ -610,15 +756,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -632,6 +771,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -640,8 +786,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -649,20 +804,26 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
@@ -691,7 +852,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -703,7 +864,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -715,13 +894,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -733,31 +906,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -769,25 +918,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -799,55 +930,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -865,7 +954,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -875,8 +1024,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="23">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -974,13 +1135,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color auto="1"/>
       </top>
       <bottom style="thin">
@@ -992,29 +1166,146 @@
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top style="medium">
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1053,13 +1344,73 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color auto="1"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1118,15 +1469,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1145,6 +1487,26 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -1153,13 +1515,13 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1171,134 +1533,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="33" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="37" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1320,101 +1688,324 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1736,7 +2327,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:T31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.71428571428571" customWidth="1"/>
@@ -1749,1265 +2340,1973 @@
     <col min="8" max="8" width="14.7142857142857" customWidth="1"/>
     <col min="9" max="9" width="21.7142857142857" customWidth="1"/>
     <col min="11" max="11" width="21.8571428571429" customWidth="1"/>
-    <col min="12" max="12" width="12.5714285714286" customWidth="1"/>
+    <col min="12" max="12" width="12.5714285714286" style="1" customWidth="1"/>
     <col min="13" max="13" width="11.4285714285714" customWidth="1"/>
-    <col min="14" max="14" width="12.8571428571429" customWidth="1"/>
-    <col min="15" max="15" width="12.4285714285714" customWidth="1"/>
+    <col min="14" max="14" width="12.8571428571429" style="2" customWidth="1"/>
+    <col min="15" max="15" width="12.4285714285714" style="2" customWidth="1"/>
     <col min="16" max="17" width="13.4285714285714" customWidth="1"/>
-    <col min="18" max="18" width="20.5714285714286" customWidth="1"/>
+    <col min="18" max="18" width="20.5714285714286" style="2" customWidth="1"/>
     <col min="19" max="19" width="14" customWidth="1"/>
     <col min="20" max="20" width="24.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:20">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="31"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="86"/>
+      <c r="R1" s="87"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="87"/>
     </row>
     <row r="2" ht="16.5" spans="1:20">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="21" t="s">
+      <c r="N2" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Q2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="R2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="32" t="s">
+      <c r="S2" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="T2" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
-      <c r="A3" s="7">
+    <row r="3" ht="26.25" spans="1:20">
+      <c r="A3" s="9">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="106" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="39" t="s">
+      <c r="F3" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="40" t="s">
+      <c r="J3" s="108" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="11">
-        <v>4</v>
-      </c>
-      <c r="L3" s="22">
+      <c r="K3" s="14">
+        <v>6</v>
+      </c>
+      <c r="L3" s="50">
         <v>50</v>
       </c>
-      <c r="M3" s="11">
-        <f t="shared" ref="M3:M21" si="0">K3*5</f>
+      <c r="M3" s="51">
+        <f>K3*5</f>
+        <v>30</v>
+      </c>
+      <c r="N3" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="53">
+        <v>0.0094</v>
+      </c>
+      <c r="P3" s="54">
+        <f t="shared" ref="P3:P9" si="0">O3*K3</f>
+        <v>0.0564</v>
+      </c>
+      <c r="Q3" s="54">
+        <f t="shared" ref="Q3:Q9" si="1">O3*L3</f>
+        <v>0.47</v>
+      </c>
+      <c r="R3" s="53">
+        <v>0.0094</v>
+      </c>
+      <c r="S3" s="54">
+        <f t="shared" ref="S3:S9" si="2">R3*M3</f>
+        <v>0.282</v>
+      </c>
+      <c r="T3" s="89"/>
+    </row>
+    <row r="4" ht="15.75" spans="1:20">
+      <c r="A4" s="9">
+        <v>2</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="110" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="111" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="20">
+        <v>2</v>
+      </c>
+      <c r="L4" s="55">
         <v>20</v>
       </c>
-      <c r="N3" s="23" t="s">
+      <c r="M4" s="36">
+        <f t="shared" ref="M4:M29" si="3">K4*5</f>
+        <v>10</v>
+      </c>
+      <c r="N4" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="O3" s="24">
-        <v>0.0063</v>
-      </c>
-      <c r="P3" s="25">
-        <f>O3*K3</f>
-        <v>0.0252</v>
-      </c>
-      <c r="Q3" s="25">
-        <f>O3*L3</f>
-        <v>0.315</v>
-      </c>
-      <c r="R3" s="24">
-        <v>0.0063</v>
-      </c>
-      <c r="S3" s="25">
-        <f>R3*M3</f>
-        <v>0.126</v>
-      </c>
-      <c r="T3" s="33"/>
+      <c r="O4" s="57">
+        <v>0.0576</v>
+      </c>
+      <c r="P4" s="58">
+        <f t="shared" si="0"/>
+        <v>0.1152</v>
+      </c>
+      <c r="Q4" s="58">
+        <f t="shared" si="1"/>
+        <v>1.152</v>
+      </c>
+      <c r="R4" s="57">
+        <v>0.0576</v>
+      </c>
+      <c r="S4" s="58">
+        <f t="shared" si="2"/>
+        <v>0.576</v>
+      </c>
+      <c r="T4" s="90"/>
     </row>
-    <row r="4" spans="1:20">
-      <c r="A4" s="7">
+    <row r="5" ht="15.75" spans="1:20">
+      <c r="A5" s="9">
+        <v>3</v>
+      </c>
+      <c r="B5" s="22"/>
+      <c r="C5" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="112" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="113" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="113" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="113" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" s="26">
         <v>2</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="11">
-        <v>2</v>
-      </c>
-      <c r="L4" s="22">
+      <c r="L5" s="59">
         <v>50</v>
       </c>
-      <c r="M4" s="11">
+      <c r="M5" s="47">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N5" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" s="61">
+        <v>0.0051</v>
+      </c>
+      <c r="P5" s="62">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="N4" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="O4" s="24">
+        <v>0.0102</v>
+      </c>
+      <c r="Q5" s="62">
+        <f t="shared" si="1"/>
+        <v>0.255</v>
+      </c>
+      <c r="R5" s="61">
         <v>0.0051</v>
       </c>
-      <c r="P4" s="25">
-        <f t="shared" ref="P4:P21" si="1">O4*K4</f>
-        <v>0.0102</v>
-      </c>
-      <c r="Q4" s="25">
-        <f t="shared" ref="Q4:Q21" si="2">O4*L4</f>
-        <v>0.255</v>
-      </c>
-      <c r="R4" s="24">
-        <v>0.0051</v>
-      </c>
-      <c r="S4" s="25">
-        <f t="shared" ref="S4:S21" si="3">R4*M4</f>
+      <c r="S5" s="62">
+        <f t="shared" si="2"/>
         <v>0.051</v>
       </c>
-      <c r="T4" s="33"/>
-    </row>
-    <row r="5" ht="16.5" spans="1:20">
-      <c r="A5" s="7">
-        <v>3</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="41" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="11">
-        <v>4</v>
-      </c>
-      <c r="L5" s="22">
-        <v>30</v>
-      </c>
-      <c r="M5" s="11">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="N5" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="O5" s="24">
-        <v>0.0632</v>
-      </c>
-      <c r="P5" s="25">
-        <f t="shared" si="1"/>
-        <v>0.2528</v>
-      </c>
-      <c r="Q5" s="25">
-        <f t="shared" si="2"/>
-        <v>1.896</v>
-      </c>
-      <c r="R5" s="24">
-        <v>0.0632</v>
-      </c>
-      <c r="S5" s="25">
-        <f t="shared" si="3"/>
-        <v>1.264</v>
-      </c>
-      <c r="T5" s="33"/>
+      <c r="T5" s="91"/>
     </row>
     <row r="6" ht="16.5" spans="1:20">
-      <c r="A6" s="7">
+      <c r="A6" s="9">
         <v>4</v>
       </c>
       <c r="B6" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="114" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="D6" s="115" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="E6" s="116" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="40" t="s">
+      <c r="F6" s="116" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="40" t="s">
+      <c r="G6" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="H6" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="I6" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="11">
+      <c r="J6" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" s="31">
+        <v>4</v>
+      </c>
+      <c r="L6" s="64">
+        <v>30</v>
+      </c>
+      <c r="M6" s="63">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="N6" s="65" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6" s="66">
+        <v>0.0632</v>
+      </c>
+      <c r="P6" s="67">
+        <f t="shared" si="0"/>
+        <v>0.2528</v>
+      </c>
+      <c r="Q6" s="67">
+        <f t="shared" si="1"/>
+        <v>1.896</v>
+      </c>
+      <c r="R6" s="66">
+        <v>0.0632</v>
+      </c>
+      <c r="S6" s="67">
+        <f t="shared" si="2"/>
+        <v>1.264</v>
+      </c>
+      <c r="T6" s="92"/>
+    </row>
+    <row r="7" ht="15.75" spans="1:20">
+      <c r="A7" s="9">
+        <v>5</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="117" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="106" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="108" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="108" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="14">
         <v>1</v>
       </c>
-      <c r="L6" s="22">
+      <c r="L7" s="50">
         <v>10</v>
       </c>
-      <c r="M6" s="11">
+      <c r="M7" s="51">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="N7" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7" s="53">
+        <v>0.1124</v>
+      </c>
+      <c r="P7" s="54">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N6" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="O6" s="24">
         <v>0.1124</v>
       </c>
-      <c r="P6" s="25">
+      <c r="Q7" s="54">
         <f t="shared" si="1"/>
+        <v>1.124</v>
+      </c>
+      <c r="R7" s="53">
         <v>0.1124</v>
       </c>
-      <c r="Q6" s="25">
+      <c r="S7" s="54">
         <f t="shared" si="2"/>
-        <v>1.124</v>
-      </c>
-      <c r="R6" s="24">
-        <v>0.1124</v>
-      </c>
-      <c r="S6" s="25">
-        <f t="shared" si="3"/>
         <v>0.562</v>
       </c>
-      <c r="T6" s="33"/>
-    </row>
-    <row r="7" spans="1:20">
-      <c r="A7" s="7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="J7" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="K7" s="14">
-        <v>5</v>
-      </c>
-      <c r="L7" s="27">
-        <v>100</v>
-      </c>
-      <c r="M7" s="11">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="N7" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="O7" s="24">
-        <v>0.0012</v>
-      </c>
-      <c r="P7" s="25">
-        <f t="shared" si="1"/>
-        <v>0.006</v>
-      </c>
-      <c r="Q7" s="25">
-        <f t="shared" si="2"/>
-        <v>0.12</v>
-      </c>
-      <c r="R7" s="24">
-        <v>0.0012</v>
-      </c>
-      <c r="S7" s="25">
-        <f t="shared" si="3"/>
-        <v>0.03</v>
-      </c>
-      <c r="T7" s="33"/>
+      <c r="T7" s="89"/>
     </row>
     <row r="8" ht="15.75" spans="1:20">
-      <c r="A8" s="7">
+      <c r="A8" s="9">
         <v>6</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="42" t="s">
+      <c r="B8" s="16"/>
+      <c r="C8" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="110" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="111" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="40" t="s">
+      <c r="F8" s="111" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="G8" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="40" t="s">
+      <c r="I8" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" s="20">
+        <v>2</v>
+      </c>
+      <c r="L8" s="55">
+        <v>20</v>
+      </c>
+      <c r="M8" s="36">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N8" s="69" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" s="57">
+        <v>0.0354</v>
+      </c>
+      <c r="P8" s="58">
+        <f t="shared" si="0"/>
+        <v>0.0708</v>
+      </c>
+      <c r="Q8" s="58">
+        <f t="shared" si="1"/>
+        <v>0.708</v>
+      </c>
+      <c r="R8" s="57">
+        <v>0.0354</v>
+      </c>
+      <c r="S8" s="58">
+        <f t="shared" si="2"/>
+        <v>0.354</v>
+      </c>
+      <c r="T8" s="90"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9" s="9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="22"/>
+      <c r="C9" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="D9" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="K8" s="14">
+      <c r="E9" s="113" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" s="113" t="s">
+        <v>66</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" s="26">
         <v>1</v>
       </c>
-      <c r="L8" s="22"/>
-      <c r="M8" s="11">
+      <c r="L9" s="59">
+        <v>10</v>
+      </c>
+      <c r="M9" s="47">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="N9" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="O9" s="61">
+        <v>0.0984</v>
+      </c>
+      <c r="P9" s="62">
         <f t="shared" si="0"/>
+        <v>0.0984</v>
+      </c>
+      <c r="Q9" s="62">
+        <f t="shared" si="1"/>
+        <v>0.984</v>
+      </c>
+      <c r="R9" s="61">
+        <v>0.0984</v>
+      </c>
+      <c r="S9" s="62">
+        <f t="shared" si="2"/>
+        <v>0.492</v>
+      </c>
+      <c r="T9" s="91"/>
+    </row>
+    <row r="10" ht="26.25" spans="1:20">
+      <c r="A10" s="9">
+        <v>8</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="106" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="108" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10" s="108" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="J10" s="108" t="s">
+        <v>76</v>
+      </c>
+      <c r="K10" s="34">
         <v>5</v>
       </c>
-      <c r="N8" s="26"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="25">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R8" s="24"/>
-      <c r="S8" s="25">
+      <c r="L10" s="50">
+        <v>100</v>
+      </c>
+      <c r="M10" s="51">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="T8" s="33"/>
+        <v>25</v>
+      </c>
+      <c r="N10" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="O10" s="53">
+        <v>0.0012</v>
+      </c>
+      <c r="P10" s="54">
+        <f t="shared" ref="P10:P20" si="4">O10*K10</f>
+        <v>0.006</v>
+      </c>
+      <c r="Q10" s="54">
+        <f t="shared" ref="Q10:Q14" si="5">O10*L10</f>
+        <v>0.12</v>
+      </c>
+      <c r="R10" s="53">
+        <v>0.0012</v>
+      </c>
+      <c r="S10" s="54">
+        <f t="shared" ref="S10:S14" si="6">R10*M10</f>
+        <v>0.03</v>
+      </c>
+      <c r="T10" s="89"/>
     </row>
-    <row r="9" ht="15.75" spans="1:20">
-      <c r="A9" s="7">
+    <row r="11" spans="1:20">
+      <c r="A11" s="9">
+        <v>9</v>
+      </c>
+      <c r="B11" s="16"/>
+      <c r="C11" s="118" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="110" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="111" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="H11" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11" s="111" t="s">
+        <v>76</v>
+      </c>
+      <c r="K11" s="19">
+        <v>1</v>
+      </c>
+      <c r="L11" s="55">
         <v>7</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J9" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="K9" s="14">
+      <c r="M11" s="36">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="N11" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="O11" s="58">
+        <v>0.4762</v>
+      </c>
+      <c r="P11" s="54">
+        <f>O11*K11</f>
+        <v>0.4762</v>
+      </c>
+      <c r="Q11" s="54">
+        <f>O11*L11</f>
+        <v>3.3334</v>
+      </c>
+      <c r="R11" s="58">
+        <v>0.4762</v>
+      </c>
+      <c r="S11" s="54">
+        <f>R11*M11</f>
+        <v>2.381</v>
+      </c>
+      <c r="T11" s="93"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="A12" s="9">
+        <v>10</v>
+      </c>
+      <c r="B12" s="16"/>
+      <c r="C12" s="118" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="110" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="111" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" s="111" t="s">
+        <v>85</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="I12" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12" s="111" t="s">
+        <v>88</v>
+      </c>
+      <c r="K12" s="19">
+        <v>2</v>
+      </c>
+      <c r="L12" s="71">
+        <v>100</v>
+      </c>
+      <c r="M12" s="36">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N12" s="69" t="s">
+        <v>30</v>
+      </c>
+      <c r="O12" s="57">
+        <v>0.0016</v>
+      </c>
+      <c r="P12" s="58">
+        <f t="shared" si="4"/>
+        <v>0.0032</v>
+      </c>
+      <c r="Q12" s="58">
+        <f t="shared" si="5"/>
+        <v>0.16</v>
+      </c>
+      <c r="R12" s="57">
+        <v>0.0016</v>
+      </c>
+      <c r="S12" s="58">
+        <f t="shared" si="6"/>
+        <v>0.016</v>
+      </c>
+      <c r="T12" s="93"/>
+    </row>
+    <row r="13" ht="15.75" spans="1:20">
+      <c r="A13" s="9">
+        <v>11</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="110" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13" s="111" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="111" t="s">
+        <v>91</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="I13" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="J13" s="111" t="s">
+        <v>94</v>
+      </c>
+      <c r="K13" s="19">
         <v>1</v>
       </c>
-      <c r="L9" s="22">
+      <c r="L13" s="71">
         <v>100</v>
       </c>
-      <c r="M9" s="11">
-        <f t="shared" si="0"/>
+      <c r="M13" s="36">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N9" s="26" t="s">
+      <c r="N13" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="O9" s="24">
-        <v>0.0015</v>
-      </c>
-      <c r="P9" s="25">
-        <f t="shared" si="1"/>
-        <v>0.0015</v>
-      </c>
-      <c r="Q9" s="25">
-        <f t="shared" si="2"/>
-        <v>0.15</v>
-      </c>
-      <c r="R9" s="24">
-        <v>0.0015</v>
-      </c>
-      <c r="S9" s="25">
-        <f t="shared" si="3"/>
-        <v>0.0075</v>
-      </c>
-      <c r="T9" s="33"/>
-    </row>
-    <row r="10" ht="15.75" spans="1:20">
-      <c r="A10" s="7">
-        <v>8</v>
-      </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="40" t="s">
-        <v>73</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="J10" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="K10" s="14">
-        <v>1</v>
-      </c>
-      <c r="L10" s="22">
-        <v>100</v>
-      </c>
-      <c r="M10" s="11">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N10" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="O10" s="24">
+      <c r="O13" s="57">
         <v>0.0017</v>
       </c>
-      <c r="P10" s="25">
-        <f t="shared" si="1"/>
+      <c r="P13" s="58">
+        <f t="shared" si="4"/>
         <v>0.0017</v>
       </c>
-      <c r="Q10" s="25">
-        <f t="shared" si="2"/>
+      <c r="Q13" s="58">
+        <f t="shared" si="5"/>
         <v>0.17</v>
       </c>
-      <c r="R10" s="24">
+      <c r="R13" s="57">
         <v>0.0017</v>
       </c>
-      <c r="S10" s="25">
-        <f t="shared" si="3"/>
+      <c r="S13" s="58">
+        <f t="shared" si="6"/>
         <v>0.0085</v>
       </c>
-      <c r="T10" s="33"/>
-    </row>
-    <row r="11" ht="15.75" spans="1:20">
-      <c r="A11" s="7">
-        <v>9</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" s="40" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="K11" s="14">
-        <v>3</v>
-      </c>
-      <c r="L11" s="22">
-        <v>100</v>
-      </c>
-      <c r="M11" s="11">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="N11" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="O11" s="25">
-        <v>0.002</v>
-      </c>
-      <c r="P11" s="25">
-        <f t="shared" si="1"/>
-        <v>0.006</v>
-      </c>
-      <c r="Q11" s="25">
-        <f t="shared" si="2"/>
-        <v>0.2</v>
-      </c>
-      <c r="R11" s="25">
-        <v>0.002</v>
-      </c>
-      <c r="S11" s="25">
-        <f t="shared" si="3"/>
-        <v>0.03</v>
-      </c>
-      <c r="T11" s="25"/>
-    </row>
-    <row r="12" ht="16.5" spans="1:20">
-      <c r="A12" s="7">
-        <v>10</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="D12" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K12" s="11">
-        <v>1</v>
-      </c>
-      <c r="L12" s="22"/>
-      <c r="M12" s="11">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N12" s="26"/>
-      <c r="O12" s="25"/>
-      <c r="P12" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="25">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R12" s="25"/>
-      <c r="S12" s="25">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="T12" s="25"/>
-    </row>
-    <row r="13" ht="16.5" spans="1:20">
-      <c r="A13" s="7">
-        <v>11</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K13" s="11">
-        <v>2</v>
-      </c>
-      <c r="L13" s="22">
-        <v>12</v>
-      </c>
-      <c r="M13" s="11">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="N13" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="O13" s="24">
-        <v>0.4166</v>
-      </c>
-      <c r="P13" s="25">
-        <f t="shared" si="1"/>
-        <v>0.8332</v>
-      </c>
-      <c r="Q13" s="25">
-        <f t="shared" si="2"/>
-        <v>4.9992</v>
-      </c>
-      <c r="R13" s="25">
-        <v>0.4166</v>
-      </c>
-      <c r="S13" s="25">
-        <f t="shared" si="3"/>
-        <v>4.166</v>
-      </c>
-      <c r="T13" s="34"/>
+      <c r="T13" s="94"/>
     </row>
     <row r="14" ht="15.75" spans="1:20">
-      <c r="A14" s="7">
+      <c r="A14" s="9">
         <v>12</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C14" s="42" t="s">
-        <v>93</v>
-      </c>
-      <c r="D14" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" s="40" t="s">
+      <c r="B14" s="16"/>
+      <c r="C14" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="D14" s="110" t="s">
         <v>96</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="E14" s="111" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="111" t="s">
         <v>97</v>
       </c>
-      <c r="I14" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K14" s="14">
-        <v>1</v>
-      </c>
-      <c r="L14" s="22">
-        <v>7</v>
-      </c>
-      <c r="M14" s="11">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N14" s="26" t="s">
+      <c r="G14" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="I14" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="J14" s="111" t="s">
+        <v>99</v>
+      </c>
+      <c r="K14" s="19">
+        <v>3</v>
+      </c>
+      <c r="L14" s="71">
+        <v>100</v>
+      </c>
+      <c r="M14" s="36">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="N14" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="O14" s="25">
-        <v>5.1105</v>
-      </c>
-      <c r="P14" s="25">
-        <f t="shared" si="1"/>
-        <v>5.1105</v>
-      </c>
-      <c r="Q14" s="25">
-        <f t="shared" si="2"/>
-        <v>35.7735</v>
-      </c>
-      <c r="R14" s="25">
-        <v>5.1105</v>
-      </c>
-      <c r="S14" s="25">
-        <f t="shared" si="3"/>
-        <v>25.5525</v>
-      </c>
-      <c r="T14" s="35"/>
+      <c r="O14" s="58">
+        <v>0.0019</v>
+      </c>
+      <c r="P14" s="58">
+        <f t="shared" si="4"/>
+        <v>0.0057</v>
+      </c>
+      <c r="Q14" s="58">
+        <f t="shared" si="5"/>
+        <v>0.19</v>
+      </c>
+      <c r="R14" s="58">
+        <v>0.0019</v>
+      </c>
+      <c r="S14" s="58">
+        <f t="shared" si="6"/>
+        <v>0.0285</v>
+      </c>
+      <c r="T14" s="95"/>
     </row>
     <row r="15" ht="15.75" spans="1:20">
-      <c r="A15" s="7">
+      <c r="A15" s="9">
         <v>13</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="42" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="E15" s="10" t="s">
+      <c r="B15" s="16"/>
+      <c r="C15" s="118" t="s">
         <v>100</v>
       </c>
-      <c r="F15" s="40" t="s">
+      <c r="D15" s="110" t="s">
         <v>101</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="E15" s="111" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" s="111" t="s">
         <v>102</v>
       </c>
-      <c r="H15" s="12"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K15" s="14">
+      <c r="G15" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="H15" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="I15" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="J15" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="K15" s="19">
         <v>1</v>
       </c>
-      <c r="L15" s="22"/>
-      <c r="M15" s="11">
-        <f t="shared" si="0"/>
+      <c r="L15" s="55">
+        <v>100</v>
+      </c>
+      <c r="M15" s="36">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N15" s="28"/>
-      <c r="O15" s="28"/>
-      <c r="P15" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="25">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R15" s="36"/>
-      <c r="S15" s="25">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="T15" s="36"/>
+      <c r="N15" s="69" t="s">
+        <v>30</v>
+      </c>
+      <c r="O15" s="58">
+        <v>0.0013</v>
+      </c>
+      <c r="P15" s="58">
+        <f t="shared" si="4"/>
+        <v>0.0013</v>
+      </c>
+      <c r="Q15" s="58">
+        <f t="shared" ref="Q15:Q20" si="7">O15*L15</f>
+        <v>0.13</v>
+      </c>
+      <c r="R15" s="58">
+        <v>0.0013</v>
+      </c>
+      <c r="S15" s="58">
+        <f t="shared" ref="S15:S20" si="8">R15*M15</f>
+        <v>0.0065</v>
+      </c>
+      <c r="T15" s="96"/>
     </row>
     <row r="16" ht="15.75" spans="1:20">
-      <c r="A16" s="7">
+      <c r="A16" s="9">
         <v>14</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D16" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="E16" s="40" t="s">
-        <v>105</v>
-      </c>
-      <c r="F16" s="40" t="s">
+      <c r="B16" s="16"/>
+      <c r="C16" s="118" t="s">
         <v>106</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="D16" s="110" t="s">
         <v>107</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="E16" s="111" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" s="111" t="s">
         <v>108</v>
       </c>
-      <c r="I16" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K16" s="14">
+      <c r="G16" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="H16" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="I16" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="K16" s="19">
         <v>1</v>
       </c>
-      <c r="L16" s="22">
-        <v>7</v>
-      </c>
-      <c r="M16" s="11">
-        <f t="shared" si="0"/>
+      <c r="L16" s="55">
+        <v>100</v>
+      </c>
+      <c r="M16" s="36">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N16" s="26" t="s">
+      <c r="N16" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="O16" s="25">
-        <v>0.2512</v>
-      </c>
-      <c r="P16" s="25">
-        <f t="shared" si="1"/>
-        <v>0.2512</v>
-      </c>
-      <c r="Q16" s="25">
-        <f t="shared" si="2"/>
-        <v>1.7584</v>
-      </c>
-      <c r="R16" s="25">
-        <v>0.2512</v>
-      </c>
-      <c r="S16" s="25">
-        <f t="shared" si="3"/>
-        <v>1.256</v>
-      </c>
-      <c r="T16" s="36"/>
+      <c r="O16" s="58">
+        <v>0.0014</v>
+      </c>
+      <c r="P16" s="58">
+        <f t="shared" si="4"/>
+        <v>0.0014</v>
+      </c>
+      <c r="Q16" s="58">
+        <f t="shared" si="7"/>
+        <v>0.14</v>
+      </c>
+      <c r="R16" s="58">
+        <v>0.0014</v>
+      </c>
+      <c r="S16" s="58">
+        <f t="shared" si="8"/>
+        <v>0.007</v>
+      </c>
+      <c r="T16" s="96"/>
     </row>
     <row r="17" ht="15.75" spans="1:20">
-      <c r="A17" s="7">
+      <c r="A17" s="9">
         <v>15</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="E17" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="F17" s="40" t="s">
+      <c r="B17" s="16"/>
+      <c r="C17" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="D17" s="110" t="s">
         <v>113</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="E17" s="111" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="111" t="s">
         <v>114</v>
       </c>
-      <c r="I17" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J17" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K17" s="14">
+      <c r="G17" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="I17" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="J17" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="K17" s="19">
         <v>1</v>
       </c>
-      <c r="L17" s="22">
-        <v>7</v>
-      </c>
-      <c r="M17" s="11">
-        <f t="shared" si="0"/>
+      <c r="L17" s="55">
+        <v>100</v>
+      </c>
+      <c r="M17" s="36">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N17" s="26" t="s">
+      <c r="N17" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="O17" s="25">
-        <v>1.65</v>
-      </c>
-      <c r="P17" s="25">
-        <f t="shared" si="1"/>
-        <v>1.65</v>
-      </c>
-      <c r="Q17" s="25">
-        <f t="shared" si="2"/>
-        <v>11.55</v>
-      </c>
-      <c r="R17" s="25">
-        <v>1.65</v>
-      </c>
-      <c r="S17" s="25">
-        <f t="shared" si="3"/>
-        <v>8.25</v>
-      </c>
-      <c r="T17" s="37"/>
+      <c r="O17" s="58">
+        <v>0.0019</v>
+      </c>
+      <c r="P17" s="58">
+        <f t="shared" si="4"/>
+        <v>0.0019</v>
+      </c>
+      <c r="Q17" s="58">
+        <f t="shared" si="7"/>
+        <v>0.19</v>
+      </c>
+      <c r="R17" s="58">
+        <v>0.0019</v>
+      </c>
+      <c r="S17" s="58">
+        <f t="shared" si="8"/>
+        <v>0.0095</v>
+      </c>
+      <c r="T17" s="97"/>
     </row>
     <row r="18" ht="15.75" spans="1:20">
-      <c r="A18" s="7">
+      <c r="A18" s="9">
         <v>16</v>
       </c>
-      <c r="B18" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="C18" s="42" t="s">
-        <v>116</v>
-      </c>
-      <c r="D18" s="40" t="s">
+      <c r="B18" s="16"/>
+      <c r="C18" s="118" t="s">
         <v>117</v>
       </c>
-      <c r="E18" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="F18" s="40" t="s">
+      <c r="D18" s="110" t="s">
         <v>118</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="E18" s="111" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="111" t="s">
         <v>119</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="G18" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="I18" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J18" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K18" s="29">
+      <c r="I18" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="J18" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="K18" s="19">
         <v>1</v>
       </c>
-      <c r="L18" s="22">
+      <c r="L18" s="55">
+        <v>100</v>
+      </c>
+      <c r="M18" s="36">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="N18" s="56" t="s">
+        <v>30</v>
+      </c>
+      <c r="O18" s="58">
+        <v>0.0013</v>
+      </c>
+      <c r="P18" s="58">
+        <f t="shared" si="4"/>
+        <v>0.0013</v>
+      </c>
+      <c r="Q18" s="58">
+        <f t="shared" si="7"/>
+        <v>0.13</v>
+      </c>
+      <c r="R18" s="58">
+        <v>0.0013</v>
+      </c>
+      <c r="S18" s="58">
+        <f t="shared" si="8"/>
+        <v>0.0065</v>
+      </c>
+      <c r="T18" s="98"/>
+    </row>
+    <row r="19" spans="1:20">
+      <c r="A19" s="9">
+        <v>17</v>
+      </c>
+      <c r="B19" s="22"/>
+      <c r="C19" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="D19" s="112" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19" s="113" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" s="113" t="s">
+        <v>124</v>
+      </c>
+      <c r="G19" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="H19" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="I19" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="J19" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="K19" s="25">
+        <v>4</v>
+      </c>
+      <c r="L19" s="59">
+        <v>100</v>
+      </c>
+      <c r="M19" s="47">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="N19" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="O19" s="62">
+        <v>0.0011</v>
+      </c>
+      <c r="P19" s="62">
+        <f t="shared" si="4"/>
+        <v>0.0044</v>
+      </c>
+      <c r="Q19" s="62">
+        <f t="shared" si="7"/>
+        <v>0.11</v>
+      </c>
+      <c r="R19" s="62">
+        <v>0.0011</v>
+      </c>
+      <c r="S19" s="62">
+        <f t="shared" si="8"/>
+        <v>0.022</v>
+      </c>
+      <c r="T19" s="99"/>
+    </row>
+    <row r="20" ht="16.5" spans="1:20">
+      <c r="A20" s="9">
+        <v>18</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="C20" s="114" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="115" t="s">
+        <v>129</v>
+      </c>
+      <c r="E20" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" s="116" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="I20" s="63" t="s">
+        <v>36</v>
+      </c>
+      <c r="J20" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="K20" s="31">
+        <v>1</v>
+      </c>
+      <c r="L20" s="64">
         <v>7</v>
       </c>
-      <c r="M18" s="11">
-        <f t="shared" si="0"/>
+      <c r="M20" s="63">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N18" s="26" t="s">
+      <c r="N20" s="72" t="s">
+        <v>82</v>
+      </c>
+      <c r="O20" s="67">
+        <v>0.318</v>
+      </c>
+      <c r="P20" s="67">
+        <f t="shared" si="4"/>
+        <v>0.318</v>
+      </c>
+      <c r="Q20" s="67">
+        <f t="shared" si="7"/>
+        <v>2.226</v>
+      </c>
+      <c r="R20" s="67">
+        <v>0.318</v>
+      </c>
+      <c r="S20" s="67">
+        <f t="shared" si="8"/>
+        <v>1.59</v>
+      </c>
+      <c r="T20" s="100"/>
+    </row>
+    <row r="21" ht="16.5" spans="1:20">
+      <c r="A21" s="9">
+        <v>19</v>
+      </c>
+      <c r="B21" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="C21" s="119" t="s">
+        <v>132</v>
+      </c>
+      <c r="D21" s="120" t="s">
+        <v>133</v>
+      </c>
+      <c r="E21" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="F21" s="120" t="s">
+        <v>134</v>
+      </c>
+      <c r="G21" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="H21" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="I21" s="73" t="s">
+        <v>36</v>
+      </c>
+      <c r="J21" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="K21" s="40">
+        <v>2</v>
+      </c>
+      <c r="L21" s="73">
+        <v>12</v>
+      </c>
+      <c r="M21" s="73">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N21" s="74" t="s">
         <v>30</v>
       </c>
-      <c r="O18" s="25">
+      <c r="O21" s="75">
+        <v>0.4166</v>
+      </c>
+      <c r="P21" s="76">
+        <f t="shared" ref="P21:P27" si="9">O21*K21</f>
+        <v>0.8332</v>
+      </c>
+      <c r="Q21" s="76">
+        <f t="shared" ref="Q21:Q27" si="10">O21*L21</f>
+        <v>4.9992</v>
+      </c>
+      <c r="R21" s="76">
+        <v>0.4166</v>
+      </c>
+      <c r="S21" s="76">
+        <f t="shared" ref="S21:S27" si="11">R21*M21</f>
+        <v>4.166</v>
+      </c>
+      <c r="T21" s="101"/>
+    </row>
+    <row r="22" ht="15.75" spans="1:20">
+      <c r="A22" s="9">
+        <v>20</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" s="117" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="108" t="s">
+        <v>139</v>
+      </c>
+      <c r="E22" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" s="108" t="s">
+        <v>140</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="I22" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="J22" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="K22" s="34">
+        <v>1</v>
+      </c>
+      <c r="L22" s="77">
+        <v>6</v>
+      </c>
+      <c r="M22" s="51">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="N22" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="O22" s="54">
+        <v>5.1105</v>
+      </c>
+      <c r="P22" s="54">
+        <f t="shared" si="9"/>
+        <v>5.1105</v>
+      </c>
+      <c r="Q22" s="54">
+        <f t="shared" si="10"/>
+        <v>30.663</v>
+      </c>
+      <c r="R22" s="54">
+        <v>5.1105</v>
+      </c>
+      <c r="S22" s="54">
+        <f t="shared" si="11"/>
+        <v>25.5525</v>
+      </c>
+      <c r="T22" s="102"/>
+    </row>
+    <row r="23" ht="15.75" spans="1:20">
+      <c r="A23" s="9">
+        <v>21</v>
+      </c>
+      <c r="B23" s="16"/>
+      <c r="C23" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="D23" s="111" t="s">
+        <v>144</v>
+      </c>
+      <c r="E23" s="111" t="s">
+        <v>145</v>
+      </c>
+      <c r="F23" s="111" t="s">
+        <v>146</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="I23" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="J23" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="K23" s="19">
+        <v>1</v>
+      </c>
+      <c r="L23" s="78">
+        <v>6</v>
+      </c>
+      <c r="M23" s="36">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="N23" s="56" t="s">
+        <v>30</v>
+      </c>
+      <c r="O23" s="58">
+        <v>0.2512</v>
+      </c>
+      <c r="P23" s="58">
+        <f t="shared" si="9"/>
+        <v>0.2512</v>
+      </c>
+      <c r="Q23" s="58">
+        <f t="shared" si="10"/>
+        <v>1.5072</v>
+      </c>
+      <c r="R23" s="58">
+        <v>0.2512</v>
+      </c>
+      <c r="S23" s="58">
+        <f t="shared" si="11"/>
+        <v>1.256</v>
+      </c>
+      <c r="T23" s="103"/>
+    </row>
+    <row r="24" ht="15.75" spans="1:20">
+      <c r="A24" s="9">
+        <v>22</v>
+      </c>
+      <c r="B24" s="16"/>
+      <c r="C24" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" s="111" t="s">
+        <v>150</v>
+      </c>
+      <c r="E24" s="111" t="s">
+        <v>151</v>
+      </c>
+      <c r="F24" s="111" t="s">
+        <v>152</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="H24" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="I24" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="J24" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="K24" s="19">
+        <v>1</v>
+      </c>
+      <c r="L24" s="78">
+        <v>6</v>
+      </c>
+      <c r="M24" s="36">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="N24" s="56" t="s">
+        <v>30</v>
+      </c>
+      <c r="O24" s="58">
+        <v>1.65</v>
+      </c>
+      <c r="P24" s="58">
+        <f t="shared" si="9"/>
+        <v>1.65</v>
+      </c>
+      <c r="Q24" s="58">
+        <f t="shared" si="10"/>
+        <v>9.9</v>
+      </c>
+      <c r="R24" s="58">
+        <v>1.65</v>
+      </c>
+      <c r="S24" s="58">
+        <f t="shared" si="11"/>
+        <v>8.25</v>
+      </c>
+      <c r="T24" s="103"/>
+    </row>
+    <row r="25" ht="15.75" spans="1:20">
+      <c r="A25" s="9">
+        <v>23</v>
+      </c>
+      <c r="B25" s="22"/>
+      <c r="C25" s="121" t="s">
+        <v>155</v>
+      </c>
+      <c r="D25" s="113" t="s">
+        <v>156</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="F25" s="113" t="s">
+        <v>158</v>
+      </c>
+      <c r="G25" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="H25" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="I25" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="J25" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="K25" s="25">
+        <v>1</v>
+      </c>
+      <c r="L25" s="79">
+        <v>6</v>
+      </c>
+      <c r="M25" s="47">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="N25" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="O25" s="62">
+        <v>3.1053</v>
+      </c>
+      <c r="P25" s="62">
+        <f t="shared" si="9"/>
+        <v>3.1053</v>
+      </c>
+      <c r="Q25" s="62">
+        <f t="shared" si="10"/>
+        <v>18.6318</v>
+      </c>
+      <c r="R25" s="104">
+        <v>3.1053</v>
+      </c>
+      <c r="S25" s="62">
+        <f t="shared" si="11"/>
+        <v>15.5265</v>
+      </c>
+      <c r="T25" s="105"/>
+    </row>
+    <row r="26" ht="15.75" spans="1:20">
+      <c r="A26" s="9">
+        <v>24</v>
+      </c>
+      <c r="B26" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="C26" s="117" t="s">
+        <v>162</v>
+      </c>
+      <c r="D26" s="108" t="s">
+        <v>163</v>
+      </c>
+      <c r="E26" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F26" s="108" t="s">
+        <v>164</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="H26" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="I26" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="K26" s="12">
+        <v>1</v>
+      </c>
+      <c r="L26" s="80">
+        <v>7</v>
+      </c>
+      <c r="M26" s="51">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="N26" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="O26" s="54">
         <v>0.2242</v>
       </c>
-      <c r="P18" s="25">
-        <f t="shared" si="1"/>
+      <c r="P26" s="54">
+        <f t="shared" si="9"/>
         <v>0.2242</v>
       </c>
-      <c r="Q18" s="25">
-        <f t="shared" si="2"/>
+      <c r="Q26" s="54">
+        <f t="shared" si="10"/>
         <v>1.5694</v>
       </c>
-      <c r="R18" s="25">
+      <c r="R26" s="54">
         <v>0.2242</v>
       </c>
-      <c r="S18" s="25">
+      <c r="S26" s="54">
+        <f t="shared" si="11"/>
+        <v>1.121</v>
+      </c>
+      <c r="T26" s="102"/>
+    </row>
+    <row r="27" ht="15.75" spans="1:20">
+      <c r="A27" s="9">
+        <v>25</v>
+      </c>
+      <c r="B27" s="43"/>
+      <c r="C27" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="D27" s="122" t="s">
+        <v>168</v>
+      </c>
+      <c r="E27" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="F27" s="122" t="s">
+        <v>169</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H27" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="I27" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="J27" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="K27" s="18">
+        <v>1</v>
+      </c>
+      <c r="L27" s="71">
+        <v>20</v>
+      </c>
+      <c r="M27" s="36">
         <f t="shared" si="3"/>
-        <v>1.121</v>
-      </c>
-      <c r="T18" s="38"/>
+        <v>5</v>
+      </c>
+      <c r="N27" s="56" t="s">
+        <v>30</v>
+      </c>
+      <c r="O27" s="58">
+        <v>0.031</v>
+      </c>
+      <c r="P27" s="58">
+        <f t="shared" si="9"/>
+        <v>0.031</v>
+      </c>
+      <c r="Q27" s="58">
+        <f t="shared" si="10"/>
+        <v>0.62</v>
+      </c>
+      <c r="R27" s="58">
+        <v>0.031</v>
+      </c>
+      <c r="S27" s="58">
+        <f t="shared" si="11"/>
+        <v>0.155</v>
+      </c>
+      <c r="T27" s="103"/>
     </row>
-    <row r="19" ht="15.75" spans="1:20">
-      <c r="A19" s="7">
-        <v>17</v>
-      </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D19" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="F19" s="39" t="s">
-        <v>123</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J19" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K19" s="29">
+    <row r="28" ht="15.75" spans="1:20">
+      <c r="A28" s="9">
+        <v>26</v>
+      </c>
+      <c r="B28" s="43"/>
+      <c r="C28" s="109" t="s">
+        <v>172</v>
+      </c>
+      <c r="D28" s="122" t="s">
+        <v>173</v>
+      </c>
+      <c r="E28" s="122" t="s">
+        <v>174</v>
+      </c>
+      <c r="F28" s="122" t="s">
+        <v>174</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="H28" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="I28" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="K28" s="18">
         <v>1</v>
       </c>
-      <c r="L19" s="22">
-        <v>20</v>
-      </c>
-      <c r="M19" s="11">
-        <f t="shared" si="0"/>
+      <c r="L28" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="M28" s="36">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N19" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="O19" s="25">
-        <v>0.031</v>
-      </c>
-      <c r="P19" s="25">
-        <f t="shared" si="1"/>
-        <v>0.031</v>
-      </c>
-      <c r="Q19" s="25">
-        <f t="shared" si="2"/>
-        <v>0.62</v>
-      </c>
-      <c r="R19" s="25">
-        <v>0.031</v>
-      </c>
-      <c r="S19" s="25">
+      <c r="N28" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="O28" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="P28" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q28" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="R28" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="S28" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="T28" s="103"/>
+    </row>
+    <row r="29" ht="15.75" spans="1:20">
+      <c r="A29" s="9">
+        <v>27</v>
+      </c>
+      <c r="B29" s="45"/>
+      <c r="C29" s="123" t="s">
+        <v>175</v>
+      </c>
+      <c r="D29" s="113" t="s">
+        <v>176</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" s="113" t="s">
+        <v>177</v>
+      </c>
+      <c r="G29" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="H29" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="I29" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="J29" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="K29" s="24">
+        <v>5</v>
+      </c>
+      <c r="L29" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="M29" s="47">
         <f t="shared" si="3"/>
-        <v>0.155</v>
-      </c>
-      <c r="T19" s="38"/>
+        <v>25</v>
+      </c>
+      <c r="N29" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="O29" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="P29" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q29" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="R29" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="S29" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="T29" s="105"/>
     </row>
-    <row r="20" ht="15.75" spans="1:20">
-      <c r="A20" s="7">
-        <v>18</v>
-      </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="42" t="s">
-        <v>126</v>
-      </c>
-      <c r="D20" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K20" s="29">
-        <v>1</v>
-      </c>
-      <c r="L20" s="22">
-        <v>10</v>
-      </c>
-      <c r="M20" s="11">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N20" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="O20" s="25">
-        <v>0.0496</v>
-      </c>
-      <c r="P20" s="25">
-        <f t="shared" si="1"/>
-        <v>0.0496</v>
-      </c>
-      <c r="Q20" s="25">
-        <f t="shared" si="2"/>
-        <v>0.496</v>
-      </c>
-      <c r="R20" s="25">
-        <v>0.0496</v>
-      </c>
-      <c r="S20" s="25">
-        <f t="shared" si="3"/>
-        <v>0.248</v>
-      </c>
-      <c r="T20" s="38"/>
+    <row r="30" ht="19.5" spans="11:17">
+      <c r="K30" s="81" t="s">
+        <v>178</v>
+      </c>
+      <c r="L30" s="81"/>
+      <c r="M30" s="81"/>
+      <c r="N30" s="81"/>
+      <c r="O30" s="82">
+        <f>SUM(O3:O29)</f>
+        <v>11.9779</v>
+      </c>
+      <c r="P30" s="83"/>
+      <c r="Q30" s="82">
+        <f>SUM(Q3:Q29)</f>
+        <v>81.379</v>
+      </c>
     </row>
-    <row r="21" ht="15.75" spans="1:20">
-      <c r="A21" s="7">
-        <v>19</v>
-      </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="42" t="s">
-        <v>130</v>
-      </c>
-      <c r="D21" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K21" s="29">
-        <v>5</v>
-      </c>
-      <c r="L21" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="M21" s="11">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="N21" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="O21" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="P21" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q21" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="R21" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="S21" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="T21" s="38"/>
+    <row r="31" ht="18.75" spans="11:17">
+      <c r="K31" s="84" t="s">
+        <v>179</v>
+      </c>
+      <c r="L31" s="84"/>
+      <c r="M31" s="84"/>
+      <c r="N31" s="84"/>
+      <c r="O31" s="85">
+        <f>SUM(O29:O30)</f>
+        <v>11.9779</v>
+      </c>
+      <c r="P31" s="83"/>
+      <c r="Q31" s="85">
+        <f>Q30/5</f>
+        <v>16.2758</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="8">
     <mergeCell ref="A1:R1"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B7:B11"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="K30:N30"/>
+    <mergeCell ref="K31:N31"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B19"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B26:B29"/>
   </mergeCells>
-  <conditionalFormatting sqref="M3:M21">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="P5">
+    <cfRule type="dataBar" priority="19">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF555A"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{17ead634-21f4-47f8-9caf-3e33964eef6a}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S5">
+    <cfRule type="dataBar" priority="20">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{e82d952d-e01f-4b1e-88a2-b8f49a93f47d}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P6">
+    <cfRule type="dataBar" priority="17">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF555A"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{22c13d5c-4bf4-4b37-90e4-ebe21692e9fe}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S6">
+    <cfRule type="dataBar" priority="18">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{0b329ca3-e34e-4aab-a503-7fd611db2f97}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P21">
+    <cfRule type="dataBar" priority="9">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF555A"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{6a42876f-f14c-4636-b38b-e24c555d0c5a}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S21">
+    <cfRule type="dataBar" priority="10">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{158646a7-fb27-493b-a7ff-54d604bad301}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P22">
+    <cfRule type="dataBar" priority="7">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF555A"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{1136fb38-d2f8-4ea9-a367-22b6430b29d9}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S22">
+    <cfRule type="dataBar" priority="8">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{d4a5cf13-cf84-4591-9fcc-49ff52f9f1c4}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O31">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{235feb0c-ee6b-4a59-bd6e-7a0589e24a48}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q31">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{682ecf16-2ac7-45c0-acde-784824b45411}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M3:M29">
+    <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3018,7 +4317,77 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P20">
+  <conditionalFormatting sqref="P3:P4">
+    <cfRule type="dataBar" priority="21">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF555A"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{a5ed5b40-261c-4d63-8171-03de1591b7d6}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P7:P9">
+    <cfRule type="dataBar" priority="15">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF555A"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9387ee67-d922-4edd-9da9-92a432bdb36f}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P10:P11">
+    <cfRule type="dataBar" priority="13">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF555A"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{c4f90b74-b997-4150-b66d-3e2b67e9d539}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P12:P20">
+    <cfRule type="dataBar" priority="11">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF555A"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9858b0c3-d0f8-40ab-a4eb-b7fa3cd44c37}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P23:P25">
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF555A"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{aa3267bb-7df4-4184-a49b-e7450b91d10b}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P26:P27">
     <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
@@ -3027,13 +4396,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cd993221-8966-4a70-95a1-78e348db6a81}</x14:id>
+          <x14:id>{bfab5b23-2bbb-4d00-9329-1fc3154f45b1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S3:S20">
-    <cfRule type="dataBar" priority="26">
+  <conditionalFormatting sqref="S3:S4">
+    <cfRule type="dataBar" priority="22">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3041,13 +4410,83 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a076f2c8-98ba-47b2-bf63-4eebf46a19ba}</x14:id>
+          <x14:id>{5d986308-f274-4102-be29-1d0cf74d077b}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S7:S9">
+    <cfRule type="dataBar" priority="16">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{85d471b6-7ba0-466d-8a61-5132ff9b9e71}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S10:S11">
+    <cfRule type="dataBar" priority="14">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{6e2e58f7-fe6a-4762-93a9-566ca5cdf7ec}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S12:S20">
+    <cfRule type="dataBar" priority="12">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{ff02f8a1-a0ab-48ba-bc5d-837b4f090483}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S23:S25">
+    <cfRule type="dataBar" priority="6">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{a4531ed6-7a23-45f2-be31-301bd5ea9251}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S26:S27">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{dd42d827-22d9-4a2d-8948-02763cac3774}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T11:T12 T14">
-    <cfRule type="dataBar" priority="27">
+    <cfRule type="dataBar" priority="49">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3055,27 +4494,35 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b891dcfd-4448-437e-8894-c31c7321d958}</x14:id>
+          <x14:id>{08ce510f-e31e-46c1-b283-c5a0291b5e7c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="N3" r:id="rId1" display="LCSC"/>
-    <hyperlink ref="N4" r:id="rId2" display="LCSC"/>
-    <hyperlink ref="N5" r:id="rId3" display="LCSC"/>
-    <hyperlink ref="N6" r:id="rId4" display="LCSC"/>
-    <hyperlink ref="N7" r:id="rId5" display="LCSC"/>
-    <hyperlink ref="N9" r:id="rId6" display="LCSC"/>
-    <hyperlink ref="N11" r:id="rId7" display="LCSC"/>
-    <hyperlink ref="N10" r:id="rId8" display="LCSC"/>
-    <hyperlink ref="N13" r:id="rId9" display="LCSC"/>
-    <hyperlink ref="N14" r:id="rId10" display="LCSC"/>
-    <hyperlink ref="N16" r:id="rId11" display="LCSC"/>
-    <hyperlink ref="N17" r:id="rId12" display="LCSC"/>
-    <hyperlink ref="N18" r:id="rId13" display="LCSC"/>
-    <hyperlink ref="N19" r:id="rId14" display="LCSC"/>
-    <hyperlink ref="N20" r:id="rId15" display="LCSC"/>
+    <hyperlink ref="N5" r:id="rId1" display="LCSC"/>
+    <hyperlink ref="N6" r:id="rId2" display="LCSC"/>
+    <hyperlink ref="N7" r:id="rId3" display="LCSC"/>
+    <hyperlink ref="N10" r:id="rId4" display="LCSC"/>
+    <hyperlink ref="N12" r:id="rId5" display="LCSC"/>
+    <hyperlink ref="N14" r:id="rId6" display="LCSC"/>
+    <hyperlink ref="N13" r:id="rId7" display="LCSC"/>
+    <hyperlink ref="N21" r:id="rId8" display="LCSC"/>
+    <hyperlink ref="N22" r:id="rId9" display="LCSC"/>
+    <hyperlink ref="N23" r:id="rId10" display="LCSC"/>
+    <hyperlink ref="N24" r:id="rId11" display="LCSC"/>
+    <hyperlink ref="N26" r:id="rId12" display="LCSC"/>
+    <hyperlink ref="N27" r:id="rId13" display="LCSC"/>
+    <hyperlink ref="N3" r:id="rId14" display="LCSC"/>
+    <hyperlink ref="N4" r:id="rId15" display="LCSC"/>
+    <hyperlink ref="N8" r:id="rId16" display="LCSC"/>
+    <hyperlink ref="N9" r:id="rId17" display="LCSC"/>
+    <hyperlink ref="N17" r:id="rId18" display="LCSC"/>
+    <hyperlink ref="N19" r:id="rId19" display="LCSC"/>
+    <hyperlink ref="N15" r:id="rId20" display="LCSC"/>
+    <hyperlink ref="N16" r:id="rId21" display="LCSC"/>
+    <hyperlink ref="N18" r:id="rId22" display="LCSC"/>
+    <hyperlink ref="N25" r:id="rId23" display="LCSC"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
@@ -3084,7 +4531,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cd993221-8966-4a70-95a1-78e348db6a81}">
+          <x14:cfRule type="dataBar" id="{17ead634-21f4-47f8-9caf-3e33964eef6a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -3094,10 +4541,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P3:P20</xm:sqref>
+          <xm:sqref>P5</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a076f2c8-98ba-47b2-bf63-4eebf46a19ba}">
+          <x14:cfRule type="dataBar" id="{e82d952d-e01f-4b1e-88a2-b8f49a93f47d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -3107,10 +4554,270 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>S3:S20</xm:sqref>
+          <xm:sqref>S5</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b891dcfd-4448-437e-8894-c31c7321d958}">
+          <x14:cfRule type="dataBar" id="{22c13d5c-4bf4-4b37-90e4-ebe21692e9fe}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFF555A"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>P6</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{0b329ca3-e34e-4aab-a503-7fd611db2f97}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>S6</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{6a42876f-f14c-4636-b38b-e24c555d0c5a}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFF555A"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>P21</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{158646a7-fb27-493b-a7ff-54d604bad301}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>S21</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{1136fb38-d2f8-4ea9-a367-22b6430b29d9}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFF555A"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>P22</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{d4a5cf13-cf84-4591-9fcc-49ff52f9f1c4}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>S22</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{235feb0c-ee6b-4a59-bd6e-7a0589e24a48}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>O31</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{682ecf16-2ac7-45c0-acde-784824b45411}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>Q31</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{a5ed5b40-261c-4d63-8171-03de1591b7d6}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFF555A"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>P3:P4</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9387ee67-d922-4edd-9da9-92a432bdb36f}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFF555A"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>P7:P9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{c4f90b74-b997-4150-b66d-3e2b67e9d539}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFF555A"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>P10:P11</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9858b0c3-d0f8-40ab-a4eb-b7fa3cd44c37}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFF555A"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>P12:P20</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{aa3267bb-7df4-4184-a49b-e7450b91d10b}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFF555A"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>P23:P25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{bfab5b23-2bbb-4d00-9329-1fc3154f45b1}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFF555A"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>P26:P27</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{5d986308-f274-4102-be29-1d0cf74d077b}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>S3:S4</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{85d471b6-7ba0-466d-8a61-5132ff9b9e71}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>S7:S9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{6e2e58f7-fe6a-4762-93a9-566ca5cdf7ec}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>S10:S11</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{ff02f8a1-a0ab-48ba-bc5d-837b4f090483}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>S12:S20</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{a4531ed6-7a23-45f2-be31-301bd5ea9251}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>S23:S25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{dd42d827-22d9-4a2d-8948-02763cac3774}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>S26:S27</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{08ce510f-e31e-46c1-b283-c5a0291b5e7c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/Hardware-Designing/Deliverables/BOM/LCSC BOM.xlsx
+++ b/Hardware-Designing/Deliverables/BOM/LCSC BOM.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="201">
   <si>
     <t>Bill of Material (BOM) for  Martin Transmitter</t>
   </si>
@@ -374,9 +374,6 @@
     <t>C137715</t>
   </si>
   <si>
-    <t>45.K</t>
-  </si>
-  <si>
     <t>RES SMD 0 OHM JUMPER 1/10W 0603</t>
   </si>
   <si>
@@ -449,16 +446,10 @@
     <t>U1</t>
   </si>
   <si>
-    <t>ESP32-WROOM-32D (8MB)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Espressif Systems
 </t>
   </si>
   <si>
-    <t>C529577</t>
-  </si>
-  <si>
     <t xml:space="preserve">IC COMP DUAL VOLT LP 8SOIC
 </t>
   </si>
@@ -558,9 +549,6 @@
     <t>Single Board Cost</t>
   </si>
   <si>
-    <t>U6</t>
-  </si>
-  <si>
     <t xml:space="preserve">LED RED CLEAR T/H
 </t>
   </si>
@@ -577,9 +565,6 @@
     <t xml:space="preserve">Everlight </t>
   </si>
   <si>
-    <t>Orange 605nm Through Hole 3mm Light Emitting Diodes (LED) ROHS</t>
-  </si>
-  <si>
     <t>LED3</t>
   </si>
   <si>
@@ -606,9 +591,6 @@
     <t>204-10SUBC/C470/S400-A4</t>
   </si>
   <si>
-    <t>D1</t>
-  </si>
-  <si>
     <t>CAP CER 22UF 16V X5R 0603</t>
   </si>
   <si>
@@ -625,17 +607,59 @@
   </si>
   <si>
     <t>22uF</t>
+  </si>
+  <si>
+    <t>LED1</t>
+  </si>
+  <si>
+    <t>Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED ORANGE CLEAR 3MM T/H
+</t>
+  </si>
+  <si>
+    <t>ESP32-WROOM-32E(4MB)</t>
+  </si>
+  <si>
+    <t>C282135</t>
+  </si>
+  <si>
+    <t>C99759</t>
+  </si>
+  <si>
+    <t>C282136</t>
+  </si>
+  <si>
+    <t>C86726</t>
+  </si>
+  <si>
+    <t>47.5K</t>
+  </si>
+  <si>
+    <t>Non Stock in LCSC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C231329
+</t>
+  </si>
+  <si>
+    <t>Utsource</t>
+  </si>
+  <si>
+    <t>Chipsfind</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00000"/>
-    <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00000"/>
+    <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.0000"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -738,8 +762,32 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -758,8 +806,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="33">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -1175,6 +1235,67 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1183,7 +1304,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1224,9 +1345,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1239,9 +1357,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1296,10 +1411,10 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1308,10 +1423,10 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1320,10 +1435,10 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1335,10 +1450,10 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1359,13 +1474,10 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1380,9 +1492,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="169" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="169" fontId="11" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1391,39 +1503,36 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1472,11 +1581,111 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1508,55 +1717,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1845,7 +2018,7 @@
     <col min="5" max="5" width="20.5703125" customWidth="1"/>
     <col min="6" max="6" width="28.42578125" customWidth="1"/>
     <col min="7" max="7" width="17.5703125" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" customWidth="1"/>
     <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="11" max="11" width="21.85546875" customWidth="1"/>
     <col min="12" max="12" width="12.5703125" style="1" customWidth="1"/>
@@ -1859,28 +2032,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="16.5" thickBot="1">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="110"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="138"/>
       <c r="S1" s="3"/>
-      <c r="T1" s="69"/>
+      <c r="T1" s="66"/>
     </row>
     <row r="2" spans="1:20" ht="16.5" thickBot="1">
       <c r="A2" s="4" t="s">
@@ -1922,7 +2095,7 @@
       <c r="M2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="33" t="s">
+      <c r="N2" s="31" t="s">
         <v>14</v>
       </c>
       <c r="O2" s="6" t="s">
@@ -1937,7 +2110,7 @@
       <c r="R2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="70" t="s">
+      <c r="S2" s="67" t="s">
         <v>19</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -1948,19 +2121,19 @@
       <c r="A3" s="7">
         <v>1</v>
       </c>
-      <c r="B3" s="113" t="s">
+      <c r="B3" s="141" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="132" t="s">
-        <v>191</v>
-      </c>
-      <c r="E3" s="89" t="s">
+      <c r="D3" s="106" t="s">
+        <v>185</v>
+      </c>
+      <c r="E3" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="89" t="s">
+      <c r="F3" s="83" t="s">
         <v>24</v>
       </c>
       <c r="G3" s="10" t="s">
@@ -1969,445 +2142,560 @@
       <c r="H3" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="34" t="s">
+      <c r="I3" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="90" t="s">
+      <c r="J3" s="84" t="s">
         <v>28</v>
       </c>
       <c r="K3" s="10">
         <v>6</v>
       </c>
-      <c r="L3" s="35">
+      <c r="L3" s="33">
         <v>50</v>
       </c>
-      <c r="M3" s="36">
+      <c r="M3" s="110">
         <f>K3*5</f>
         <v>30</v>
       </c>
-      <c r="N3" s="37" t="s">
+      <c r="N3" s="111" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="38">
-        <v>9.4000000000000004E-3</v>
-      </c>
-      <c r="P3" s="39">
+      <c r="O3" s="36">
+        <v>9.4999999999999998E-3</v>
+      </c>
+      <c r="P3" s="37">
         <f t="shared" ref="P3:P13" si="0">O3*K3</f>
-        <v>5.6400000000000006E-2</v>
-      </c>
-      <c r="Q3" s="39">
+        <v>5.6999999999999995E-2</v>
+      </c>
+      <c r="Q3" s="37">
         <f t="shared" ref="Q3:Q13" si="1">O3*L3</f>
-        <v>0.47000000000000003</v>
-      </c>
-      <c r="R3" s="38">
-        <v>9.4000000000000004E-3</v>
-      </c>
-      <c r="S3" s="39">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="R3" s="36">
+        <v>9.4999999999999998E-3</v>
+      </c>
+      <c r="S3" s="37">
         <f t="shared" ref="S3:S13" si="2">R3*M3</f>
-        <v>0.28200000000000003</v>
-      </c>
-      <c r="T3" s="71"/>
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="T3" s="68"/>
     </row>
     <row r="4" spans="1:20" ht="15.75" thickBot="1">
-      <c r="A4" s="7"/>
-      <c r="B4" s="114"/>
-      <c r="C4" s="91" t="s">
-        <v>188</v>
-      </c>
-      <c r="D4" s="92" t="s">
-        <v>189</v>
-      </c>
-      <c r="E4" s="93" t="s">
+      <c r="A4" s="7">
+        <v>2</v>
+      </c>
+      <c r="B4" s="142"/>
+      <c r="C4" s="85" t="s">
+        <v>182</v>
+      </c>
+      <c r="D4" s="86" t="s">
+        <v>183</v>
+      </c>
+      <c r="E4" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="131" t="s">
-        <v>190</v>
-      </c>
-      <c r="G4" s="16" t="s">
+      <c r="F4" s="105" t="s">
+        <v>184</v>
+      </c>
+      <c r="G4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="123" t="s">
-        <v>192</v>
-      </c>
-      <c r="I4" s="126" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="124" t="s">
-        <v>193</v>
-      </c>
-      <c r="K4" s="122">
+      <c r="H4" s="99" t="s">
+        <v>186</v>
+      </c>
+      <c r="I4" s="102" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="100" t="s">
+        <v>187</v>
+      </c>
+      <c r="K4" s="98">
         <v>1</v>
       </c>
-      <c r="L4" s="125">
+      <c r="L4" s="101">
         <v>7</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="25">
         <f>K4*5</f>
         <v>5</v>
       </c>
-      <c r="N4" s="127"/>
-      <c r="O4" s="128">
+      <c r="N4" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="103">
         <v>0.19919999999999999</v>
       </c>
-      <c r="P4" s="129"/>
-      <c r="Q4" s="129"/>
-      <c r="R4" s="128"/>
-      <c r="S4" s="129"/>
-      <c r="T4" s="130"/>
+      <c r="P4" s="37">
+        <f t="shared" si="0"/>
+        <v>0.19919999999999999</v>
+      </c>
+      <c r="Q4" s="37">
+        <f t="shared" si="1"/>
+        <v>1.3943999999999999</v>
+      </c>
+      <c r="R4" s="103">
+        <v>0.19919999999999999</v>
+      </c>
+      <c r="S4" s="37">
+        <f t="shared" si="2"/>
+        <v>0.996</v>
+      </c>
+      <c r="T4" s="104"/>
     </row>
     <row r="5" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A5" s="7">
+        <v>3</v>
+      </c>
+      <c r="B5" s="142"/>
+      <c r="C5" s="85" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="87" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="87" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="15">
         <v>2</v>
       </c>
-      <c r="B5" s="114"/>
-      <c r="C5" s="91" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="92" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="93" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="93" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" s="16">
-        <v>2</v>
-      </c>
-      <c r="L5" s="40">
+      <c r="L5" s="38">
         <v>20</v>
       </c>
-      <c r="M5" s="27">
+      <c r="M5" s="25">
         <f t="shared" ref="M5:M33" si="3">K5*5</f>
         <v>10</v>
       </c>
-      <c r="N5" s="41" t="s">
+      <c r="N5" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="40">
         <v>5.7599999999999998E-2</v>
       </c>
-      <c r="P5" s="43">
+      <c r="P5" s="41">
         <f t="shared" si="0"/>
         <v>0.1152</v>
       </c>
-      <c r="Q5" s="43">
+      <c r="Q5" s="41">
         <f t="shared" si="1"/>
         <v>1.1519999999999999</v>
       </c>
-      <c r="R5" s="42">
+      <c r="R5" s="40">
         <v>5.7599999999999998E-2</v>
       </c>
-      <c r="S5" s="43">
+      <c r="S5" s="41">
         <f t="shared" si="2"/>
         <v>0.57599999999999996</v>
       </c>
-      <c r="T5" s="72"/>
+      <c r="T5" s="69"/>
     </row>
     <row r="6" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A6" s="7">
-        <v>3</v>
-      </c>
-      <c r="B6" s="115"/>
-      <c r="C6" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="143"/>
+      <c r="C6" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="94" t="s">
+      <c r="D6" s="88" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="95" t="s">
+      <c r="E6" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="95" t="s">
+      <c r="F6" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="H6" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" s="95" t="s">
+      <c r="I6" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="K6" s="21">
+      <c r="K6" s="19">
         <v>2</v>
       </c>
-      <c r="L6" s="44">
+      <c r="L6" s="42">
         <v>50</v>
       </c>
-      <c r="M6" s="32">
+      <c r="M6" s="30">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="N6" s="45" t="s">
+      <c r="N6" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="O6" s="46">
+      <c r="O6" s="44">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="P6" s="47">
+      <c r="P6" s="45">
         <f t="shared" si="0"/>
         <v>1.0200000000000001E-2</v>
       </c>
-      <c r="Q6" s="47">
+      <c r="Q6" s="45">
         <f t="shared" si="1"/>
         <v>0.255</v>
       </c>
-      <c r="R6" s="46">
+      <c r="R6" s="44">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="S6" s="47">
+      <c r="S6" s="45">
         <f t="shared" si="2"/>
         <v>5.1000000000000004E-2</v>
       </c>
-      <c r="T6" s="73"/>
+      <c r="T6" s="70"/>
     </row>
-    <row r="7" spans="1:20" ht="16.5" thickBot="1">
+    <row r="7" spans="1:20" ht="16.5" customHeight="1" thickBot="1">
       <c r="A7" s="7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="141" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="108" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="107" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" s="92" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="92" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="22">
         <v>4</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="96" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="97" t="s">
-        <v>187</v>
-      </c>
-      <c r="E7" s="98" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="98" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="I7" s="48" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7" s="24">
-        <v>4</v>
-      </c>
-      <c r="L7" s="49">
+      <c r="L7" s="47">
         <v>30</v>
       </c>
-      <c r="M7" s="48">
+      <c r="M7" s="46">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="N7" s="50" t="s">
+      <c r="N7" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="O7" s="51">
-        <v>6.3200000000000006E-2</v>
-      </c>
-      <c r="P7" s="52">
+      <c r="O7" s="49">
+        <v>5.3199999999999997E-2</v>
+      </c>
+      <c r="P7" s="50">
         <f t="shared" si="0"/>
-        <v>0.25280000000000002</v>
-      </c>
-      <c r="Q7" s="52">
+        <v>0.21279999999999999</v>
+      </c>
+      <c r="Q7" s="50">
         <f t="shared" si="1"/>
-        <v>1.8960000000000001</v>
-      </c>
-      <c r="R7" s="51">
-        <v>6.3200000000000006E-2</v>
-      </c>
-      <c r="S7" s="52">
+        <v>1.5959999999999999</v>
+      </c>
+      <c r="R7" s="49">
+        <v>5.3199999999999997E-2</v>
+      </c>
+      <c r="S7" s="50">
         <f t="shared" si="2"/>
-        <v>1.2640000000000002</v>
-      </c>
-      <c r="T7" s="74"/>
+        <v>1.0640000000000001</v>
+      </c>
+      <c r="T7" s="71"/>
     </row>
-    <row r="8" spans="1:20" ht="16.5" thickBot="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="91" t="s">
+    <row r="8" spans="1:20" ht="16.5" customHeight="1" thickBot="1">
+      <c r="A8" s="7">
+        <v>6</v>
+      </c>
+      <c r="B8" s="142"/>
+      <c r="C8" s="85" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" s="86" t="s">
+        <v>170</v>
+      </c>
+      <c r="E8" s="87" t="s">
+        <v>171</v>
+      </c>
+      <c r="F8" s="87" t="s">
+        <v>172</v>
+      </c>
+      <c r="G8" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="D8" s="92" t="s">
-        <v>174</v>
-      </c>
-      <c r="E8" s="93" t="s">
-        <v>175</v>
-      </c>
-      <c r="F8" s="93" t="s">
-        <v>176</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="H8" s="17"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16">
+      <c r="H8" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="I8" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="15">
         <v>1</v>
       </c>
-      <c r="L8" s="40"/>
-      <c r="M8" s="48">
+      <c r="L8" s="38">
+        <v>20</v>
+      </c>
+      <c r="M8" s="25">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N8" s="50"/>
-      <c r="O8" s="51"/>
-      <c r="P8" s="52"/>
-      <c r="Q8" s="52"/>
-      <c r="R8" s="51"/>
-      <c r="S8" s="52"/>
-      <c r="T8" s="74"/>
+      <c r="N8" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="O8" s="40">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="P8" s="41">
+        <f t="shared" si="0"/>
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="Q8" s="41">
+        <f t="shared" si="1"/>
+        <v>0.85999999999999988</v>
+      </c>
+      <c r="R8" s="40">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="S8" s="50">
+        <f t="shared" si="2"/>
+        <v>0.21499999999999997</v>
+      </c>
+      <c r="T8" s="71"/>
     </row>
-    <row r="9" spans="1:20" ht="16.5" thickBot="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="91" t="s">
-        <v>178</v>
-      </c>
-      <c r="D9" s="92" t="s">
-        <v>179</v>
-      </c>
-      <c r="E9" s="93" t="s">
+    <row r="9" spans="1:20" ht="16.5" customHeight="1" thickBot="1">
+      <c r="A9" s="7">
+        <v>7</v>
+      </c>
+      <c r="B9" s="142"/>
+      <c r="C9" s="109" t="s">
+        <v>190</v>
+      </c>
+      <c r="D9" s="86" t="s">
+        <v>174</v>
+      </c>
+      <c r="E9" s="87" t="s">
+        <v>171</v>
+      </c>
+      <c r="F9" s="87" t="s">
         <v>175</v>
       </c>
-      <c r="F9" s="93" t="s">
-        <v>180</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="H9" s="17"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16">
+      <c r="G9" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="I9" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="15">
         <v>1</v>
       </c>
-      <c r="L9" s="40"/>
-      <c r="M9" s="48">
+      <c r="L9" s="38">
+        <v>10</v>
+      </c>
+      <c r="M9" s="25">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N9" s="50"/>
-      <c r="O9" s="51"/>
-      <c r="P9" s="52"/>
-      <c r="Q9" s="52"/>
-      <c r="R9" s="51"/>
-      <c r="S9" s="52"/>
-      <c r="T9" s="74"/>
+      <c r="N9" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="O9" s="40">
+        <v>4.5100000000000001E-2</v>
+      </c>
+      <c r="P9" s="41">
+        <f t="shared" si="0"/>
+        <v>4.5100000000000001E-2</v>
+      </c>
+      <c r="Q9" s="41">
+        <f t="shared" si="1"/>
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="R9" s="40">
+        <v>4.5100000000000001E-2</v>
+      </c>
+      <c r="S9" s="50">
+        <f t="shared" si="2"/>
+        <v>0.22550000000000001</v>
+      </c>
+      <c r="T9" s="71"/>
     </row>
-    <row r="10" spans="1:20" ht="16.5" thickBot="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="91" t="s">
-        <v>181</v>
-      </c>
-      <c r="D10" s="92" t="s">
-        <v>182</v>
-      </c>
-      <c r="E10" s="93" t="s">
-        <v>175</v>
-      </c>
-      <c r="F10" s="93" t="s">
-        <v>183</v>
-      </c>
-      <c r="G10" s="16" t="s">
+    <row r="10" spans="1:20" ht="16.5" customHeight="1" thickBot="1">
+      <c r="A10" s="7">
+        <v>8</v>
+      </c>
+      <c r="B10" s="142"/>
+      <c r="C10" s="85" t="s">
+        <v>176</v>
+      </c>
+      <c r="D10" s="86" t="s">
         <v>177</v>
       </c>
-      <c r="H10" s="17"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16">
+      <c r="E10" s="87" t="s">
+        <v>171</v>
+      </c>
+      <c r="F10" s="87" t="s">
+        <v>178</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" s="15">
         <v>1</v>
       </c>
-      <c r="L10" s="40"/>
-      <c r="M10" s="48">
+      <c r="L10" s="38">
+        <v>10</v>
+      </c>
+      <c r="M10" s="25">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N10" s="50"/>
-      <c r="O10" s="51"/>
-      <c r="P10" s="52"/>
-      <c r="Q10" s="52"/>
-      <c r="R10" s="51"/>
-      <c r="S10" s="52"/>
-      <c r="T10" s="74"/>
+      <c r="N10" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="O10" s="40">
+        <v>5.4800000000000001E-2</v>
+      </c>
+      <c r="P10" s="41">
+        <f t="shared" si="0"/>
+        <v>5.4800000000000001E-2</v>
+      </c>
+      <c r="Q10" s="41">
+        <f t="shared" si="1"/>
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="R10" s="40">
+        <v>5.4800000000000001E-2</v>
+      </c>
+      <c r="S10" s="50">
+        <f t="shared" si="2"/>
+        <v>0.27400000000000002</v>
+      </c>
+      <c r="T10" s="71"/>
     </row>
-    <row r="11" spans="1:20" ht="16.5" thickBot="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="103" t="s">
-        <v>184</v>
-      </c>
-      <c r="D11" s="94" t="s">
-        <v>185</v>
-      </c>
-      <c r="E11" s="95" t="s">
-        <v>175</v>
-      </c>
-      <c r="F11" s="95" t="s">
-        <v>186</v>
-      </c>
-      <c r="G11" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="H11" s="25"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24">
+    <row r="11" spans="1:20" ht="16.5" customHeight="1" thickBot="1">
+      <c r="A11" s="7">
+        <v>9</v>
+      </c>
+      <c r="B11" s="143"/>
+      <c r="C11" s="97" t="s">
+        <v>179</v>
+      </c>
+      <c r="D11" s="88" t="s">
+        <v>180</v>
+      </c>
+      <c r="E11" s="89" t="s">
+        <v>171</v>
+      </c>
+      <c r="F11" s="89" t="s">
+        <v>181</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="I11" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" s="22">
         <v>1</v>
       </c>
-      <c r="L11" s="49"/>
-      <c r="M11" s="48">
+      <c r="L11" s="47">
+        <v>10</v>
+      </c>
+      <c r="M11" s="46">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N11" s="50"/>
-      <c r="O11" s="51"/>
-      <c r="P11" s="52"/>
-      <c r="Q11" s="52"/>
-      <c r="R11" s="51"/>
-      <c r="S11" s="52"/>
-      <c r="T11" s="74"/>
+      <c r="N11" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="O11" s="49">
+        <v>7.5200000000000003E-2</v>
+      </c>
+      <c r="P11" s="50">
+        <f t="shared" si="0"/>
+        <v>7.5200000000000003E-2</v>
+      </c>
+      <c r="Q11" s="50">
+        <f t="shared" si="1"/>
+        <v>0.752</v>
+      </c>
+      <c r="R11" s="49">
+        <v>7.5200000000000003E-2</v>
+      </c>
+      <c r="S11" s="50">
+        <f t="shared" si="2"/>
+        <v>0.376</v>
+      </c>
+      <c r="T11" s="71"/>
     </row>
     <row r="12" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A12" s="7">
-        <v>5</v>
-      </c>
-      <c r="B12" s="116" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="141" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="99" t="s">
+      <c r="C12" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="88" t="s">
+      <c r="D12" s="82" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="90" t="s">
+      <c r="E12" s="84" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="90" t="s">
+      <c r="F12" s="84" t="s">
         <v>53</v>
       </c>
       <c r="G12" s="10" t="s">
@@ -2425,1186 +2713,1194 @@
       <c r="K12" s="10">
         <v>1</v>
       </c>
-      <c r="L12" s="35">
-        <v>10</v>
-      </c>
-      <c r="M12" s="36">
+      <c r="L12" s="33">
+        <v>7</v>
+      </c>
+      <c r="M12" s="34">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N12" s="53" t="s">
+      <c r="N12" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="O12" s="38">
-        <v>0.1124</v>
-      </c>
-      <c r="P12" s="39">
+      <c r="O12" s="36">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="P12" s="37">
         <f t="shared" si="0"/>
-        <v>0.1124</v>
-      </c>
-      <c r="Q12" s="39">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="Q12" s="37">
         <f t="shared" si="1"/>
-        <v>1.1240000000000001</v>
-      </c>
-      <c r="R12" s="38">
-        <v>0.1124</v>
-      </c>
-      <c r="S12" s="39">
+        <v>2.3331</v>
+      </c>
+      <c r="R12" s="36">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="S12" s="37">
         <f t="shared" si="2"/>
-        <v>0.56200000000000006</v>
-      </c>
-      <c r="T12" s="71"/>
+        <v>1.6664999999999999</v>
+      </c>
+      <c r="T12" s="68"/>
     </row>
     <row r="13" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A13" s="7">
-        <v>6</v>
-      </c>
-      <c r="B13" s="117"/>
+        <v>11</v>
+      </c>
+      <c r="B13" s="142"/>
       <c r="C13" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="92" t="s">
+      <c r="D13" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="93" t="s">
+      <c r="E13" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="93" t="s">
+      <c r="F13" s="87" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="H13" s="17" t="s">
+      <c r="H13" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="J13" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="K13" s="16">
+      <c r="I13" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="15">
         <v>2</v>
       </c>
-      <c r="L13" s="40">
+      <c r="L13" s="38">
         <v>20</v>
       </c>
-      <c r="M13" s="27">
+      <c r="M13" s="25">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="N13" s="54" t="s">
+      <c r="N13" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="O13" s="42">
-        <v>3.5400000000000001E-2</v>
-      </c>
-      <c r="P13" s="43">
+      <c r="O13" s="40">
+        <v>3.39E-2</v>
+      </c>
+      <c r="P13" s="41">
         <f t="shared" si="0"/>
-        <v>7.0800000000000002E-2</v>
-      </c>
-      <c r="Q13" s="43">
+        <v>6.7799999999999999E-2</v>
+      </c>
+      <c r="Q13" s="41">
         <f t="shared" si="1"/>
-        <v>0.70799999999999996</v>
-      </c>
-      <c r="R13" s="42">
-        <v>3.5400000000000001E-2</v>
-      </c>
-      <c r="S13" s="43">
+        <v>0.67799999999999994</v>
+      </c>
+      <c r="R13" s="40">
+        <v>3.39E-2</v>
+      </c>
+      <c r="S13" s="41">
         <f t="shared" si="2"/>
-        <v>0.35399999999999998</v>
-      </c>
-      <c r="T13" s="72"/>
+        <v>0.33899999999999997</v>
+      </c>
+      <c r="T13" s="69"/>
     </row>
-    <row r="14" spans="1:20" ht="26.25" thickBot="1">
+    <row r="14" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A14" s="7">
-        <v>8</v>
-      </c>
-      <c r="B14" s="113" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="143"/>
+      <c r="C14" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="E14" s="89" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="89" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="I14" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="J14" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14" s="19">
+        <v>1</v>
+      </c>
+      <c r="L14" s="42">
+        <v>10</v>
+      </c>
+      <c r="M14" s="30">
+        <f>K14*5</f>
+        <v>5</v>
+      </c>
+      <c r="N14" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="O14" s="44">
+        <v>9.8400000000000001E-2</v>
+      </c>
+      <c r="P14" s="45">
+        <f>O14*K14</f>
+        <v>9.8400000000000001E-2</v>
+      </c>
+      <c r="Q14" s="45">
+        <f>O14*L14</f>
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="R14" s="44">
+        <v>9.8400000000000001E-2</v>
+      </c>
+      <c r="S14" s="45">
+        <f>R14*M14</f>
+        <v>0.49199999999999999</v>
+      </c>
+      <c r="T14" s="70"/>
+    </row>
+    <row r="15" spans="1:20" ht="15.75" thickBot="1">
+      <c r="A15" s="7">
+        <v>13</v>
+      </c>
+      <c r="B15" s="141" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C15" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="88" t="s">
+      <c r="D15" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="90" t="s">
+      <c r="E15" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="90" t="s">
+      <c r="F15" s="84" t="s">
         <v>69</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G15" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H15" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="I14" s="36" t="s">
+      <c r="I15" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="J14" s="90" t="s">
+      <c r="J15" s="84" t="s">
         <v>73</v>
       </c>
-      <c r="K14" s="26">
+      <c r="K15" s="24">
         <v>5</v>
       </c>
-      <c r="L14" s="35">
+      <c r="L15" s="33">
         <v>100</v>
       </c>
-      <c r="M14" s="36">
+      <c r="M15" s="34">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="N14" s="53" t="s">
+      <c r="N15" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="O14" s="38">
+      <c r="O15" s="36">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="P14" s="39">
-        <f t="shared" ref="P14:P24" si="4">O14*K14</f>
+      <c r="P15" s="37">
+        <f t="shared" ref="P15:P25" si="4">O15*K15</f>
         <v>5.9999999999999993E-3</v>
       </c>
-      <c r="Q14" s="39">
-        <f t="shared" ref="Q14:Q18" si="5">O14*L14</f>
+      <c r="Q15" s="37">
+        <f t="shared" ref="Q15:Q19" si="5">O15*L15</f>
         <v>0.12</v>
       </c>
-      <c r="R14" s="38">
+      <c r="R15" s="36">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="S14" s="39">
-        <f t="shared" ref="S14:S18" si="6">R14*M14</f>
+      <c r="S15" s="37">
+        <f t="shared" ref="S15:S19" si="6">R15*M15</f>
         <v>0.03</v>
       </c>
-      <c r="T14" s="71"/>
-    </row>
-    <row r="15" spans="1:20">
-      <c r="A15" s="7">
-        <v>9</v>
-      </c>
-      <c r="B15" s="114"/>
-      <c r="C15" s="100" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" s="92" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="F15" s="93" t="s">
-        <v>77</v>
-      </c>
-      <c r="G15" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="H15" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="J15" s="93" t="s">
-        <v>73</v>
-      </c>
-      <c r="K15" s="15">
-        <v>1</v>
-      </c>
-      <c r="L15" s="40">
-        <v>7</v>
-      </c>
-      <c r="M15" s="27">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="N15" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="O15" s="43">
-        <v>0.47620000000000001</v>
-      </c>
-      <c r="P15" s="39">
-        <f>O15*K15</f>
-        <v>0.47620000000000001</v>
-      </c>
-      <c r="Q15" s="39">
-        <f>O15*L15</f>
-        <v>3.3334000000000001</v>
-      </c>
-      <c r="R15" s="43">
-        <v>0.47620000000000001</v>
-      </c>
-      <c r="S15" s="39">
-        <f>R15*M15</f>
-        <v>2.3810000000000002</v>
-      </c>
-      <c r="T15" s="75"/>
+      <c r="T15" s="68"/>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="7">
-        <v>10</v>
-      </c>
-      <c r="B16" s="114"/>
-      <c r="C16" s="100" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" s="92" t="s">
-        <v>81</v>
-      </c>
-      <c r="E16" s="93" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="93" t="s">
-        <v>82</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="I16" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="J16" s="93" t="s">
-        <v>85</v>
-      </c>
-      <c r="K16" s="15">
-        <v>2</v>
-      </c>
-      <c r="L16" s="56">
-        <v>100</v>
-      </c>
-      <c r="M16" s="27">
+        <v>14</v>
+      </c>
+      <c r="B16" s="142"/>
+      <c r="C16" s="94" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="86" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="87" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="J16" s="87" t="s">
+        <v>73</v>
+      </c>
+      <c r="K16" s="14">
+        <v>1</v>
+      </c>
+      <c r="L16" s="38">
+        <v>7</v>
+      </c>
+      <c r="M16" s="25">
         <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="N16" s="54" t="s">
-        <v>29</v>
-      </c>
-      <c r="O16" s="42">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="P16" s="43">
-        <f t="shared" si="4"/>
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="Q16" s="43">
-        <f t="shared" si="5"/>
-        <v>0.16</v>
-      </c>
-      <c r="R16" s="42">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="S16" s="43">
-        <f t="shared" si="6"/>
-        <v>1.6E-2</v>
-      </c>
-      <c r="T16" s="75"/>
+        <v>5</v>
+      </c>
+      <c r="N16" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="O16" s="41">
+        <v>0.47620000000000001</v>
+      </c>
+      <c r="P16" s="37">
+        <f>O16*K16</f>
+        <v>0.47620000000000001</v>
+      </c>
+      <c r="Q16" s="37">
+        <f>O16*L16</f>
+        <v>3.3334000000000001</v>
+      </c>
+      <c r="R16" s="41">
+        <v>0.47620000000000001</v>
+      </c>
+      <c r="S16" s="37">
+        <f>R16*M16</f>
+        <v>2.3810000000000002</v>
+      </c>
+      <c r="T16" s="72"/>
     </row>
     <row r="17" spans="1:20">
       <c r="A17" s="7">
-        <v>11</v>
-      </c>
-      <c r="B17" s="114"/>
-      <c r="C17" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D17" s="92" t="s">
-        <v>87</v>
-      </c>
-      <c r="E17" s="93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="142"/>
+      <c r="C17" s="94" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="86" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="93" t="s">
-        <v>88</v>
-      </c>
-      <c r="G17" s="16" t="s">
+      <c r="F17" s="87" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="H17" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="I17" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="J17" s="93" t="s">
-        <v>91</v>
-      </c>
-      <c r="K17" s="15">
-        <v>1</v>
-      </c>
-      <c r="L17" s="56">
+      <c r="H17" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="I17" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" s="87" t="s">
+        <v>85</v>
+      </c>
+      <c r="K17" s="14">
+        <v>2</v>
+      </c>
+      <c r="L17" s="54">
         <v>100</v>
       </c>
-      <c r="M17" s="27">
+      <c r="M17" s="25">
         <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="N17" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="N17" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="O17" s="42">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="P17" s="43">
+      <c r="O17" s="40">
+        <v>1.9E-3</v>
+      </c>
+      <c r="P17" s="41">
         <f t="shared" si="4"/>
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="Q17" s="43">
+        <v>3.8E-3</v>
+      </c>
+      <c r="Q17" s="41">
         <f t="shared" si="5"/>
-        <v>0.16999999999999998</v>
-      </c>
-      <c r="R17" s="42">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="S17" s="43">
+        <v>0.19</v>
+      </c>
+      <c r="R17" s="40">
+        <v>1.9E-3</v>
+      </c>
+      <c r="S17" s="41">
         <f t="shared" si="6"/>
-        <v>8.4999999999999989E-3</v>
-      </c>
-      <c r="T17" s="76"/>
+        <v>1.9E-2</v>
+      </c>
+      <c r="T17" s="72"/>
     </row>
     <row r="18" spans="1:20">
       <c r="A18" s="7">
-        <v>12</v>
-      </c>
-      <c r="B18" s="114"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="142"/>
       <c r="C18" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="D18" s="92" t="s">
-        <v>93</v>
-      </c>
-      <c r="E18" s="93" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="86" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="F18" s="93" t="s">
-        <v>94</v>
-      </c>
-      <c r="G18" s="16" t="s">
+      <c r="F18" s="87" t="s">
+        <v>88</v>
+      </c>
+      <c r="G18" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="H18" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="I18" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="J18" s="93" t="s">
-        <v>96</v>
-      </c>
-      <c r="K18" s="15">
-        <v>3</v>
-      </c>
-      <c r="L18" s="56">
+      <c r="H18" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="J18" s="87" t="s">
+        <v>91</v>
+      </c>
+      <c r="K18" s="14">
+        <v>1</v>
+      </c>
+      <c r="L18" s="54">
         <v>100</v>
       </c>
-      <c r="M18" s="27">
+      <c r="M18" s="25">
         <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="N18" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="N18" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="O18" s="43">
-        <v>1.9E-3</v>
-      </c>
-      <c r="P18" s="43">
+      <c r="O18" s="40">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="P18" s="41">
         <f t="shared" si="4"/>
-        <v>5.7000000000000002E-3</v>
-      </c>
-      <c r="Q18" s="43">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="Q18" s="41">
         <f t="shared" si="5"/>
-        <v>0.19</v>
-      </c>
-      <c r="R18" s="43">
-        <v>1.9E-3</v>
-      </c>
-      <c r="S18" s="43">
+        <v>0.06</v>
+      </c>
+      <c r="R18" s="40">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="S18" s="41">
         <f t="shared" si="6"/>
-        <v>2.8500000000000001E-2</v>
-      </c>
-      <c r="T18" s="77"/>
+        <v>2.9999999999999996E-3</v>
+      </c>
+      <c r="T18" s="73"/>
     </row>
     <row r="19" spans="1:20">
       <c r="A19" s="7">
-        <v>13</v>
-      </c>
-      <c r="B19" s="114"/>
-      <c r="C19" s="100" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" s="92" t="s">
-        <v>98</v>
-      </c>
-      <c r="E19" s="93" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="142"/>
+      <c r="C19" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="F19" s="93" t="s">
-        <v>99</v>
-      </c>
-      <c r="G19" s="16" t="s">
+      <c r="F19" s="87" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="H19" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="I19" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="J19" s="87" t="s">
+        <v>96</v>
+      </c>
+      <c r="K19" s="14">
+        <v>3</v>
+      </c>
+      <c r="L19" s="54">
         <v>100</v>
       </c>
-      <c r="H19" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="I19" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="J19" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="K19" s="15">
-        <v>1</v>
-      </c>
-      <c r="L19" s="40">
-        <v>100</v>
-      </c>
-      <c r="M19" s="27">
+      <c r="M19" s="25">
         <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="N19" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="N19" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="O19" s="43">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="P19" s="43">
+      <c r="O19" s="41">
+        <v>1.9E-3</v>
+      </c>
+      <c r="P19" s="41">
         <f t="shared" si="4"/>
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q19" s="43">
-        <f t="shared" ref="Q19:Q24" si="7">O19*L19</f>
-        <v>0.13</v>
-      </c>
-      <c r="R19" s="43">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="S19" s="43">
-        <f t="shared" ref="S19:S24" si="8">R19*M19</f>
-        <v>6.4999999999999997E-3</v>
-      </c>
-      <c r="T19" s="78"/>
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="Q19" s="41">
+        <f t="shared" si="5"/>
+        <v>0.19</v>
+      </c>
+      <c r="R19" s="41">
+        <v>1.9E-3</v>
+      </c>
+      <c r="S19" s="41">
+        <f t="shared" si="6"/>
+        <v>2.8500000000000001E-2</v>
+      </c>
+      <c r="T19" s="74"/>
     </row>
     <row r="20" spans="1:20">
       <c r="A20" s="7">
-        <v>14</v>
-      </c>
-      <c r="B20" s="114"/>
-      <c r="C20" s="100" t="s">
-        <v>103</v>
-      </c>
-      <c r="D20" s="92" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20" s="93" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="142"/>
+      <c r="C20" s="94" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="F20" s="93" t="s">
-        <v>105</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="H20" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="I20" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="J20" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="K20" s="15">
+      <c r="F20" s="87" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="H20" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="I20" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="K20" s="14">
         <v>1</v>
       </c>
-      <c r="L20" s="40">
+      <c r="L20" s="38">
         <v>100</v>
       </c>
-      <c r="M20" s="27">
+      <c r="M20" s="25">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N20" s="54" t="s">
+      <c r="N20" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="O20" s="43">
-        <v>1.4E-3</v>
-      </c>
-      <c r="P20" s="43">
+      <c r="O20" s="41">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="P20" s="41">
         <f t="shared" si="4"/>
-        <v>1.4E-3</v>
-      </c>
-      <c r="Q20" s="43">
-        <f t="shared" si="7"/>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="R20" s="43">
-        <v>1.4E-3</v>
-      </c>
-      <c r="S20" s="43">
-        <f t="shared" si="8"/>
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="T20" s="78"/>
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q20" s="41">
+        <f t="shared" ref="Q20:Q25" si="7">O20*L20</f>
+        <v>0.13</v>
+      </c>
+      <c r="R20" s="41">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="S20" s="41">
+        <f t="shared" ref="S20:S25" si="8">R20*M20</f>
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="T20" s="75"/>
     </row>
     <row r="21" spans="1:20">
       <c r="A21" s="7">
-        <v>15</v>
-      </c>
-      <c r="B21" s="114"/>
-      <c r="C21" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D21" s="92" t="s">
-        <v>110</v>
-      </c>
-      <c r="E21" s="93" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="142"/>
+      <c r="C21" s="94" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="86" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="F21" s="93" t="s">
-        <v>111</v>
-      </c>
-      <c r="G21" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="H21" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="I21" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="J21" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="K21" s="15">
+      <c r="F21" s="87" t="s">
+        <v>105</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="H21" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="I21" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="K21" s="14">
         <v>1</v>
       </c>
-      <c r="L21" s="40">
+      <c r="L21" s="38">
         <v>100</v>
       </c>
-      <c r="M21" s="27">
+      <c r="M21" s="25">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N21" s="41" t="s">
+      <c r="N21" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="O21" s="43">
-        <v>1.9E-3</v>
-      </c>
-      <c r="P21" s="43">
+      <c r="O21" s="41">
+        <v>1.4E-3</v>
+      </c>
+      <c r="P21" s="41">
         <f t="shared" si="4"/>
-        <v>1.9E-3</v>
-      </c>
-      <c r="Q21" s="43">
+        <v>1.4E-3</v>
+      </c>
+      <c r="Q21" s="41">
         <f t="shared" si="7"/>
-        <v>0.19</v>
-      </c>
-      <c r="R21" s="43">
-        <v>1.9E-3</v>
-      </c>
-      <c r="S21" s="43">
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="R21" s="41">
+        <v>1.4E-3</v>
+      </c>
+      <c r="S21" s="41">
         <f t="shared" si="8"/>
-        <v>9.4999999999999998E-3</v>
-      </c>
-      <c r="T21" s="79"/>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="T21" s="75"/>
     </row>
     <row r="22" spans="1:20">
       <c r="A22" s="7">
-        <v>16</v>
-      </c>
-      <c r="B22" s="114"/>
-      <c r="C22" s="100" t="s">
-        <v>114</v>
-      </c>
-      <c r="D22" s="92" t="s">
-        <v>115</v>
-      </c>
-      <c r="E22" s="93" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="142"/>
+      <c r="C22" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="86" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="93" t="s">
-        <v>116</v>
-      </c>
-      <c r="G22" s="16" t="s">
+      <c r="F22" s="87" t="s">
+        <v>111</v>
+      </c>
+      <c r="G22" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="H22" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="I22" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="J22" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="K22" s="15">
+      <c r="H22" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="I22" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="K22" s="14">
         <v>1</v>
       </c>
-      <c r="L22" s="40">
+      <c r="L22" s="38">
         <v>100</v>
       </c>
-      <c r="M22" s="27">
+      <c r="M22" s="25">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N22" s="41" t="s">
+      <c r="N22" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O22" s="43">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="P22" s="43">
+      <c r="O22" s="41">
+        <v>1.8E-3</v>
+      </c>
+      <c r="P22" s="41">
         <f t="shared" si="4"/>
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q22" s="43">
+        <v>1.8E-3</v>
+      </c>
+      <c r="Q22" s="41">
         <f t="shared" si="7"/>
-        <v>0.13</v>
-      </c>
-      <c r="R22" s="43">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="S22" s="43">
+        <v>0.18</v>
+      </c>
+      <c r="R22" s="41">
+        <v>1.8E-3</v>
+      </c>
+      <c r="S22" s="41">
         <f t="shared" si="8"/>
-        <v>6.4999999999999997E-3</v>
-      </c>
-      <c r="T22" s="80"/>
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="T22" s="76"/>
     </row>
     <row r="23" spans="1:20">
       <c r="A23" s="7">
-        <v>17</v>
-      </c>
-      <c r="B23" s="115"/>
-      <c r="C23" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="142"/>
+      <c r="C23" s="94" t="s">
+        <v>113</v>
+      </c>
+      <c r="D23" s="86" t="s">
+        <v>114</v>
+      </c>
+      <c r="E23" s="87" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" s="87" t="s">
+        <v>115</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="I23" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="J23" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="K23" s="14">
+        <v>1</v>
+      </c>
+      <c r="L23" s="38">
+        <v>100</v>
+      </c>
+      <c r="M23" s="25">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="N23" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="O23" s="41">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="P23" s="41">
+        <f t="shared" si="4"/>
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="Q23" s="41">
+        <f t="shared" si="7"/>
+        <v>0.16</v>
+      </c>
+      <c r="R23" s="41">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="S23" s="41">
+        <f t="shared" si="8"/>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="T23" s="77"/>
+    </row>
+    <row r="24" spans="1:20">
+      <c r="A24" s="7">
+        <v>22</v>
+      </c>
+      <c r="B24" s="143"/>
+      <c r="C24" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="D24" s="88" t="s">
         <v>119</v>
       </c>
-      <c r="D23" s="94" t="s">
+      <c r="E24" s="89" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="89" t="s">
         <v>120</v>
       </c>
-      <c r="E23" s="95" t="s">
-        <v>68</v>
-      </c>
-      <c r="F23" s="95" t="s">
+      <c r="G24" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H24" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="G23" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="H23" s="22" t="s">
+      <c r="I24" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="J24" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="I23" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="J23" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="K23" s="20">
+      <c r="K24" s="18">
         <v>4</v>
       </c>
-      <c r="L23" s="44">
+      <c r="L24" s="42">
         <v>100</v>
       </c>
-      <c r="M23" s="32">
+      <c r="M24" s="30">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="N23" s="55" t="s">
+      <c r="N24" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="O23" s="47">
+      <c r="O24" s="45">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="P23" s="47">
+      <c r="P24" s="45">
         <f t="shared" si="4"/>
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="Q23" s="47">
+      <c r="Q24" s="45">
         <f t="shared" si="7"/>
         <v>0.11</v>
       </c>
-      <c r="R23" s="47">
+      <c r="R24" s="45">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="S23" s="47">
+      <c r="S24" s="45">
         <f t="shared" si="8"/>
         <v>2.2000000000000002E-2</v>
       </c>
-      <c r="T23" s="81"/>
-    </row>
-    <row r="24" spans="1:20" ht="15.75">
-      <c r="A24" s="7">
-        <v>18</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="C24" s="96" t="s">
-        <v>125</v>
-      </c>
-      <c r="D24" s="97" t="s">
-        <v>126</v>
-      </c>
-      <c r="E24" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F24" s="98" t="s">
-        <v>127</v>
-      </c>
-      <c r="G24" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="H24" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="I24" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="J24" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="K24" s="24">
-        <v>1</v>
-      </c>
-      <c r="L24" s="49">
-        <v>7</v>
-      </c>
-      <c r="M24" s="48">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="N24" s="57" t="s">
-        <v>79</v>
-      </c>
-      <c r="O24" s="52">
-        <v>0.318</v>
-      </c>
-      <c r="P24" s="52">
-        <f t="shared" si="4"/>
-        <v>0.318</v>
-      </c>
-      <c r="Q24" s="52">
-        <f t="shared" si="7"/>
-        <v>2.226</v>
-      </c>
-      <c r="R24" s="52">
-        <v>0.318</v>
-      </c>
-      <c r="S24" s="52">
-        <f t="shared" si="8"/>
-        <v>1.59</v>
-      </c>
-      <c r="T24" s="82"/>
+      <c r="T24" s="78"/>
     </row>
     <row r="25" spans="1:20" ht="16.5" thickBot="1">
       <c r="A25" s="7">
-        <v>19</v>
-      </c>
-      <c r="B25" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" s="90" t="s">
+        <v>124</v>
+      </c>
+      <c r="D25" s="91" t="s">
+        <v>125</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25" s="92" t="s">
+        <v>126</v>
+      </c>
+      <c r="G25" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="K25" s="22">
+        <v>1</v>
+      </c>
+      <c r="L25" s="47">
+        <v>7</v>
+      </c>
+      <c r="M25" s="46">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="N25" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="O25" s="50">
+        <v>0.318</v>
+      </c>
+      <c r="P25" s="50">
+        <f t="shared" si="4"/>
+        <v>0.318</v>
+      </c>
+      <c r="Q25" s="50">
+        <f t="shared" si="7"/>
+        <v>2.226</v>
+      </c>
+      <c r="R25" s="50">
+        <v>0.318</v>
+      </c>
+      <c r="S25" s="50">
+        <f t="shared" si="8"/>
+        <v>1.59</v>
+      </c>
+      <c r="T25" s="79"/>
+    </row>
+    <row r="26" spans="1:20" ht="16.5" thickBot="1">
+      <c r="A26" s="7">
+        <v>24</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="C26" s="95" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="101" t="s">
+      <c r="D26" s="96" t="s">
         <v>129</v>
       </c>
-      <c r="D25" s="102" t="s">
+      <c r="E26" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="F26" s="96" t="s">
         <v>130</v>
       </c>
-      <c r="E25" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="F25" s="102" t="s">
+      <c r="G26" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="G25" s="30" t="s">
+      <c r="H26" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="H25" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="I25" s="58" t="s">
-        <v>35</v>
-      </c>
-      <c r="J25" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="K25" s="30">
+      <c r="I26" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="J26" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="K26" s="28">
         <v>2</v>
       </c>
-      <c r="L25" s="58">
+      <c r="L26" s="56">
         <v>12</v>
       </c>
-      <c r="M25" s="58">
+      <c r="M26" s="56">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="N25" s="59" t="s">
-        <v>29</v>
-      </c>
-      <c r="O25" s="60">
-        <v>0.41660000000000003</v>
-      </c>
-      <c r="P25" s="61">
-        <f t="shared" ref="P25:P31" si="9">O25*K25</f>
-        <v>0.83320000000000005</v>
-      </c>
-      <c r="Q25" s="61">
-        <f t="shared" ref="Q25:Q31" si="10">O25*L25</f>
-        <v>4.9992000000000001</v>
-      </c>
-      <c r="R25" s="61">
-        <v>0.41660000000000003</v>
-      </c>
-      <c r="S25" s="61">
-        <f t="shared" ref="S25:S31" si="11">R25*M25</f>
-        <v>4.1660000000000004</v>
-      </c>
-      <c r="T25" s="83"/>
-    </row>
-    <row r="26" spans="1:20" ht="15" customHeight="1" thickBot="1">
-      <c r="A26" s="7">
-        <v>20</v>
-      </c>
-      <c r="B26" s="113" t="s">
-        <v>134</v>
-      </c>
-      <c r="C26" s="99" t="s">
-        <v>135</v>
-      </c>
-      <c r="D26" s="90" t="s">
-        <v>136</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="F26" s="90" t="s">
-        <v>137</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="I26" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="J26" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="K26" s="26">
-        <v>1</v>
-      </c>
-      <c r="L26" s="62">
-        <v>6</v>
-      </c>
-      <c r="M26" s="36">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="N26" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="O26" s="39">
-        <v>5.1105</v>
-      </c>
-      <c r="P26" s="39">
-        <f t="shared" si="9"/>
-        <v>5.1105</v>
-      </c>
-      <c r="Q26" s="39">
-        <f t="shared" si="10"/>
-        <v>30.663</v>
-      </c>
-      <c r="R26" s="39">
-        <v>5.1105</v>
-      </c>
-      <c r="S26" s="39">
-        <f t="shared" si="11"/>
-        <v>25.552500000000002</v>
-      </c>
-      <c r="T26" s="84"/>
+      <c r="N26" s="147" t="s">
+        <v>199</v>
+      </c>
+      <c r="O26" s="57">
+        <v>0.55489999999999995</v>
+      </c>
+      <c r="P26" s="58">
+        <f t="shared" ref="P26:P31" si="9">O26*K26</f>
+        <v>1.1097999999999999</v>
+      </c>
+      <c r="Q26" s="58">
+        <f t="shared" ref="Q26:Q31" si="10">O26*L26</f>
+        <v>6.6587999999999994</v>
+      </c>
+      <c r="R26" s="58">
+        <v>0.55489999999999995</v>
+      </c>
+      <c r="S26" s="58">
+        <f t="shared" ref="S26:S31" si="11">R26*M26</f>
+        <v>5.5489999999999995</v>
+      </c>
+      <c r="T26" s="112" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="27" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A27" s="7">
-        <v>21</v>
-      </c>
-      <c r="B27" s="114"/>
-      <c r="C27" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="D27" s="93" t="s">
-        <v>141</v>
-      </c>
-      <c r="E27" s="93" t="s">
-        <v>142</v>
-      </c>
-      <c r="F27" s="93" t="s">
-        <v>143</v>
-      </c>
-      <c r="G27" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="H27" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="I27" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="J27" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="K27" s="15">
+        <v>25</v>
+      </c>
+      <c r="B27" s="141" t="s">
+        <v>133</v>
+      </c>
+      <c r="C27" s="93" t="s">
+        <v>134</v>
+      </c>
+      <c r="D27" s="84" t="s">
+        <v>135</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" s="84" t="s">
+        <v>191</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="I27" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="J27" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="K27" s="24">
         <v>1</v>
       </c>
-      <c r="L27" s="63">
+      <c r="L27" s="59">
         <v>6</v>
       </c>
-      <c r="M27" s="27">
+      <c r="M27" s="34">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N27" s="41" t="s">
+      <c r="N27" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="O27" s="43">
-        <v>0.25119999999999998</v>
-      </c>
-      <c r="P27" s="43">
+      <c r="O27" s="37">
+        <v>4.5010000000000003</v>
+      </c>
+      <c r="P27" s="37">
         <f t="shared" si="9"/>
-        <v>0.25119999999999998</v>
-      </c>
-      <c r="Q27" s="43">
+        <v>4.5010000000000003</v>
+      </c>
+      <c r="Q27" s="37">
         <f t="shared" si="10"/>
-        <v>1.5071999999999999</v>
-      </c>
-      <c r="R27" s="43">
-        <v>0.25119999999999998</v>
-      </c>
-      <c r="S27" s="43">
+        <v>27.006</v>
+      </c>
+      <c r="R27" s="37">
+        <v>4.5010000000000003</v>
+      </c>
+      <c r="S27" s="37">
         <f t="shared" si="11"/>
-        <v>1.2559999999999998</v>
-      </c>
-      <c r="T27" s="85"/>
+        <v>22.505000000000003</v>
+      </c>
+      <c r="T27" s="113" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="28" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A28" s="7">
-        <v>22</v>
-      </c>
-      <c r="B28" s="114"/>
+        <v>26</v>
+      </c>
+      <c r="B28" s="142"/>
       <c r="C28" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="D28" s="93" t="s">
-        <v>147</v>
-      </c>
-      <c r="E28" s="93" t="s">
-        <v>148</v>
-      </c>
-      <c r="F28" s="93" t="s">
-        <v>149</v>
-      </c>
-      <c r="G28" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="H28" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="I28" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="J28" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="K28" s="15">
+        <v>137</v>
+      </c>
+      <c r="D28" s="87" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" s="87" t="s">
+        <v>139</v>
+      </c>
+      <c r="F28" s="87" t="s">
+        <v>140</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="I28" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="J28" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="K28" s="14">
         <v>1</v>
       </c>
-      <c r="L28" s="63">
+      <c r="L28" s="60">
         <v>6</v>
       </c>
-      <c r="M28" s="27">
+      <c r="M28" s="25">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N28" s="41" t="s">
+      <c r="N28" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O28" s="43">
-        <v>1.65</v>
-      </c>
-      <c r="P28" s="43">
+      <c r="O28" s="41">
+        <v>0.25119999999999998</v>
+      </c>
+      <c r="P28" s="41">
         <f t="shared" si="9"/>
-        <v>1.65</v>
-      </c>
-      <c r="Q28" s="43">
+        <v>0.25119999999999998</v>
+      </c>
+      <c r="Q28" s="41">
         <f t="shared" si="10"/>
-        <v>9.8999999999999986</v>
-      </c>
-      <c r="R28" s="43">
-        <v>1.65</v>
-      </c>
-      <c r="S28" s="43">
+        <v>1.5071999999999999</v>
+      </c>
+      <c r="R28" s="41">
+        <v>0.25119999999999998</v>
+      </c>
+      <c r="S28" s="41">
         <f t="shared" si="11"/>
-        <v>8.25</v>
-      </c>
-      <c r="T28" s="85"/>
+        <v>1.2559999999999998</v>
+      </c>
+      <c r="T28" s="115"/>
     </row>
     <row r="29" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A29" s="7">
-        <v>23</v>
-      </c>
-      <c r="B29" s="115"/>
-      <c r="C29" s="103" t="s">
-        <v>152</v>
-      </c>
-      <c r="D29" s="95" t="s">
-        <v>153</v>
-      </c>
-      <c r="E29" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="F29" s="95" t="s">
-        <v>155</v>
-      </c>
-      <c r="G29" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="H29" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="I29" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="J29" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="K29" s="20">
+        <v>27</v>
+      </c>
+      <c r="B29" s="142"/>
+      <c r="C29" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="D29" s="87" t="s">
+        <v>144</v>
+      </c>
+      <c r="E29" s="87" t="s">
+        <v>145</v>
+      </c>
+      <c r="F29" s="87" t="s">
+        <v>146</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="I29" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="J29" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="K29" s="14">
         <v>1</v>
       </c>
-      <c r="L29" s="64">
+      <c r="L29" s="60">
         <v>6</v>
       </c>
-      <c r="M29" s="32">
+      <c r="M29" s="25">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N29" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="O29" s="47">
-        <v>3.1053000000000002</v>
-      </c>
-      <c r="P29" s="47">
+      <c r="N29" s="148" t="s">
+        <v>200</v>
+      </c>
+      <c r="O29" s="41">
+        <v>0.99</v>
+      </c>
+      <c r="P29" s="41">
         <f t="shared" si="9"/>
-        <v>3.1053000000000002</v>
-      </c>
-      <c r="Q29" s="47">
+        <v>0.99</v>
+      </c>
+      <c r="Q29" s="41">
         <f t="shared" si="10"/>
-        <v>18.631800000000002</v>
-      </c>
-      <c r="R29" s="86">
-        <v>3.1053000000000002</v>
-      </c>
-      <c r="S29" s="47">
+        <v>5.9399999999999995</v>
+      </c>
+      <c r="R29" s="41">
+        <v>0.99</v>
+      </c>
+      <c r="S29" s="41">
         <f t="shared" si="11"/>
-        <v>15.5265</v>
-      </c>
-      <c r="T29" s="87"/>
+        <v>4.95</v>
+      </c>
+      <c r="T29" s="116" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="30" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A30" s="7">
-        <v>7</v>
-      </c>
-      <c r="B30" s="118"/>
-      <c r="C30" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="E30" s="95" t="s">
-        <v>62</v>
-      </c>
-      <c r="F30" s="95" t="s">
-        <v>63</v>
-      </c>
-      <c r="G30" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="H30" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="I30" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="J30" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="K30" s="21">
+        <v>28</v>
+      </c>
+      <c r="B30" s="143"/>
+      <c r="C30" s="97" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" s="89" t="s">
+        <v>150</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="F30" s="89" t="s">
+        <v>152</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="H30" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="I30" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="J30" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K30" s="18">
         <v>1</v>
       </c>
-      <c r="L30" s="44">
-        <v>10</v>
-      </c>
-      <c r="M30" s="32">
-        <f>K30*5</f>
+      <c r="L30" s="61">
+        <v>6</v>
+      </c>
+      <c r="M30" s="30">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N30" s="55" t="s">
+      <c r="N30" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="O30" s="46">
-        <v>9.8400000000000001E-2</v>
-      </c>
-      <c r="P30" s="47">
-        <f>O30*K30</f>
-        <v>9.8400000000000001E-2</v>
-      </c>
-      <c r="Q30" s="47">
-        <f>O30*L30</f>
-        <v>0.98399999999999999</v>
-      </c>
-      <c r="R30" s="46">
-        <v>9.8400000000000001E-2</v>
-      </c>
-      <c r="S30" s="47">
-        <f>R30*M30</f>
-        <v>0.49199999999999999</v>
-      </c>
-      <c r="T30" s="73"/>
+      <c r="O30" s="45">
+        <v>3.1053000000000002</v>
+      </c>
+      <c r="P30" s="45">
+        <f t="shared" si="9"/>
+        <v>3.1053000000000002</v>
+      </c>
+      <c r="Q30" s="45">
+        <f t="shared" si="10"/>
+        <v>18.631800000000002</v>
+      </c>
+      <c r="R30" s="81">
+        <v>3.1053000000000002</v>
+      </c>
+      <c r="S30" s="45">
+        <f t="shared" si="11"/>
+        <v>15.5265</v>
+      </c>
+      <c r="T30" s="114" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="31" spans="1:20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A31" s="7">
-        <v>24</v>
-      </c>
-      <c r="B31" s="119" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="144" t="s">
+        <v>155</v>
+      </c>
+      <c r="C31" s="93" t="s">
+        <v>156</v>
+      </c>
+      <c r="D31" s="84" t="s">
+        <v>157</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" s="84" t="s">
         <v>158</v>
       </c>
-      <c r="C31" s="99" t="s">
+      <c r="G31" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="D31" s="90" t="s">
+      <c r="H31" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="E31" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="F31" s="90" t="s">
-        <v>161</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="H31" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="I31" s="36" t="s">
+      <c r="I31" s="34" t="s">
         <v>35</v>
       </c>
       <c r="J31" s="10" t="s">
@@ -3613,199 +3909,202 @@
       <c r="K31" s="9">
         <v>1</v>
       </c>
-      <c r="L31" s="65">
+      <c r="L31" s="62">
         <v>7</v>
       </c>
-      <c r="M31" s="36">
+      <c r="M31" s="34">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N31" s="37" t="s">
+      <c r="N31" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="O31" s="39">
+      <c r="O31" s="37">
         <v>0.22420000000000001</v>
       </c>
-      <c r="P31" s="39">
+      <c r="P31" s="37">
         <f t="shared" si="9"/>
         <v>0.22420000000000001</v>
       </c>
-      <c r="Q31" s="39">
+      <c r="Q31" s="37">
         <f t="shared" si="10"/>
         <v>1.5694000000000001</v>
       </c>
-      <c r="R31" s="39">
+      <c r="R31" s="37">
         <v>0.22420000000000001</v>
       </c>
-      <c r="S31" s="39">
+      <c r="S31" s="37">
         <f t="shared" si="11"/>
         <v>1.121</v>
       </c>
-      <c r="T31" s="84"/>
+      <c r="T31" s="80"/>
     </row>
     <row r="32" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A32" s="7">
-        <v>26</v>
-      </c>
-      <c r="B32" s="120"/>
-      <c r="C32" s="91" t="s">
-        <v>164</v>
-      </c>
-      <c r="D32" s="104" t="s">
-        <v>165</v>
-      </c>
-      <c r="E32" s="104" t="s">
-        <v>166</v>
-      </c>
-      <c r="F32" s="104" t="s">
-        <v>166</v>
-      </c>
-      <c r="G32" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="H32" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="I32" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="J32" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="K32" s="14">
+        <v>30</v>
+      </c>
+      <c r="B32" s="145"/>
+      <c r="C32" s="117" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="118" t="s">
+        <v>162</v>
+      </c>
+      <c r="E32" s="118" t="s">
+        <v>76</v>
+      </c>
+      <c r="F32" s="121" t="s">
+        <v>163</v>
+      </c>
+      <c r="G32" s="123" t="s">
+        <v>35</v>
+      </c>
+      <c r="H32" s="123" t="s">
+        <v>35</v>
+      </c>
+      <c r="I32" s="123" t="s">
+        <v>35</v>
+      </c>
+      <c r="J32" s="123" t="s">
+        <v>35</v>
+      </c>
+      <c r="K32" s="123">
         <v>1</v>
       </c>
-      <c r="L32" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="M32" s="27">
+      <c r="L32" s="123" t="s">
+        <v>35</v>
+      </c>
+      <c r="M32" s="124">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N32" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="O32" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="P32" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q32" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="R32" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="S32" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="T32" s="85"/>
+      <c r="N32" s="125" t="s">
+        <v>35</v>
+      </c>
+      <c r="O32" s="126" t="s">
+        <v>35</v>
+      </c>
+      <c r="P32" s="126" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q32" s="126" t="s">
+        <v>35</v>
+      </c>
+      <c r="R32" s="126" t="s">
+        <v>35</v>
+      </c>
+      <c r="S32" s="126" t="s">
+        <v>35</v>
+      </c>
+      <c r="T32" s="127"/>
     </row>
     <row r="33" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A33" s="7">
-        <v>27</v>
-      </c>
-      <c r="B33" s="121"/>
-      <c r="C33" s="105" t="s">
-        <v>167</v>
-      </c>
-      <c r="D33" s="95" t="s">
-        <v>168</v>
-      </c>
-      <c r="E33" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="146"/>
+      <c r="C33" s="119" t="s">
+        <v>164</v>
+      </c>
+      <c r="D33" s="120" t="s">
+        <v>165</v>
+      </c>
+      <c r="E33" s="120" t="s">
         <v>76</v>
       </c>
-      <c r="F33" s="95" t="s">
-        <v>169</v>
-      </c>
-      <c r="G33" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="H33" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="I33" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="J33" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="K33" s="19">
+      <c r="F33" s="122" t="s">
+        <v>166</v>
+      </c>
+      <c r="G33" s="128" t="s">
+        <v>35</v>
+      </c>
+      <c r="H33" s="129" t="s">
+        <v>35</v>
+      </c>
+      <c r="I33" s="129" t="s">
+        <v>35</v>
+      </c>
+      <c r="J33" s="129" t="s">
+        <v>35</v>
+      </c>
+      <c r="K33" s="129">
         <v>5</v>
       </c>
-      <c r="L33" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="M33" s="32">
+      <c r="L33" s="129" t="s">
+        <v>35</v>
+      </c>
+      <c r="M33" s="130">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="N33" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="O33" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="P33" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q33" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="R33" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="S33" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="T33" s="87"/>
+      <c r="N33" s="131" t="s">
+        <v>35</v>
+      </c>
+      <c r="O33" s="132" t="s">
+        <v>35</v>
+      </c>
+      <c r="P33" s="132" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q33" s="132" t="s">
+        <v>35</v>
+      </c>
+      <c r="R33" s="132" t="s">
+        <v>35</v>
+      </c>
+      <c r="S33" s="132" t="s">
+        <v>35</v>
+      </c>
+      <c r="T33" s="133"/>
     </row>
     <row r="34" spans="1:20" ht="19.5" thickBot="1">
-      <c r="K34" s="111" t="s">
-        <v>170</v>
-      </c>
-      <c r="L34" s="111"/>
-      <c r="M34" s="111"/>
-      <c r="N34" s="111"/>
-      <c r="O34" s="66">
+      <c r="K34" s="139" t="s">
+        <v>167</v>
+      </c>
+      <c r="L34" s="139"/>
+      <c r="M34" s="139"/>
+      <c r="N34" s="139"/>
+      <c r="O34" s="63">
         <f>SUM(O3:O33)</f>
-        <v>12.146099999999999</v>
-      </c>
-      <c r="P34" s="67"/>
-      <c r="Q34" s="66">
+        <v>11.4419</v>
+      </c>
+      <c r="P34" s="64"/>
+      <c r="Q34" s="63">
         <f>SUM(Q3:Q33)</f>
-        <v>80.759</v>
+        <v>79.631099999999989</v>
       </c>
     </row>
     <row r="35" spans="1:20" ht="18.75">
-      <c r="K35" s="112" t="s">
-        <v>171</v>
-      </c>
-      <c r="L35" s="112"/>
-      <c r="M35" s="112"/>
-      <c r="N35" s="112"/>
-      <c r="O35" s="68">
+      <c r="K35" s="140" t="s">
+        <v>168</v>
+      </c>
+      <c r="L35" s="140"/>
+      <c r="M35" s="140"/>
+      <c r="N35" s="140"/>
+      <c r="O35" s="65">
         <f>SUM(O33:O34)</f>
-        <v>12.146099999999999</v>
-      </c>
-      <c r="P35" s="67"/>
-      <c r="Q35" s="68">
+        <v>11.4419</v>
+      </c>
+      <c r="P35" s="64"/>
+      <c r="Q35" s="65">
         <f>Q34/5</f>
-        <v>16.151800000000001</v>
+        <v>15.926219999999997</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="9">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="K34:N34"/>
     <mergeCell ref="K35:N35"/>
-    <mergeCell ref="B14:B23"/>
-    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B15:B24"/>
+    <mergeCell ref="B27:B30"/>
     <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="B31:B33"/>
   </mergeCells>
   <conditionalFormatting sqref="P6">
-    <cfRule type="dataBar" priority="19">
+    <cfRule type="dataBar" priority="28">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3819,7 +4118,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S6">
-    <cfRule type="dataBar" priority="20">
+    <cfRule type="dataBar" priority="29">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3833,7 +4132,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P7:P11">
-    <cfRule type="dataBar" priority="17">
+    <cfRule type="dataBar" priority="26">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3847,7 +4146,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S7:S11">
-    <cfRule type="dataBar" priority="18">
+    <cfRule type="dataBar" priority="27">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3860,8 +4159,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P25">
-    <cfRule type="dataBar" priority="9">
+  <conditionalFormatting sqref="P26">
+    <cfRule type="dataBar" priority="18">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3874,8 +4173,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S25">
-    <cfRule type="dataBar" priority="10">
+  <conditionalFormatting sqref="S26">
+    <cfRule type="dataBar" priority="19">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3888,8 +4187,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P26">
-    <cfRule type="dataBar" priority="7">
+  <conditionalFormatting sqref="P27">
+    <cfRule type="dataBar" priority="16">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3902,8 +4201,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S26">
-    <cfRule type="dataBar" priority="8">
+  <conditionalFormatting sqref="S27">
+    <cfRule type="dataBar" priority="17">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3917,7 +4216,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O35">
-    <cfRule type="dataBar" priority="2">
+    <cfRule type="dataBar" priority="11">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3931,7 +4230,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q35">
-    <cfRule type="dataBar" priority="1">
+    <cfRule type="dataBar" priority="10">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3945,7 +4244,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3:P5">
-    <cfRule type="dataBar" priority="21">
+    <cfRule type="dataBar" priority="30">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3958,8 +4257,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P14:P15">
-    <cfRule type="dataBar" priority="13">
+  <conditionalFormatting sqref="P15:P16">
+    <cfRule type="dataBar" priority="22">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3972,8 +4271,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P16:P24">
-    <cfRule type="dataBar" priority="11">
+  <conditionalFormatting sqref="P17:P25">
+    <cfRule type="dataBar" priority="20">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3986,8 +4285,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P27:P29">
-    <cfRule type="dataBar" priority="5">
+  <conditionalFormatting sqref="P28:P30">
+    <cfRule type="dataBar" priority="14">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4001,7 +4300,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3:S5">
-    <cfRule type="dataBar" priority="22">
+    <cfRule type="dataBar" priority="31">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4014,8 +4313,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S14:S15">
-    <cfRule type="dataBar" priority="14">
+  <conditionalFormatting sqref="S15:S16">
+    <cfRule type="dataBar" priority="23">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4028,8 +4327,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S16:S24">
-    <cfRule type="dataBar" priority="12">
+  <conditionalFormatting sqref="S17:S25">
+    <cfRule type="dataBar" priority="21">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4042,8 +4341,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S27:S29">
-    <cfRule type="dataBar" priority="6">
+  <conditionalFormatting sqref="S28:S30">
+    <cfRule type="dataBar" priority="15">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4056,8 +4355,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T15:T16 T18">
-    <cfRule type="dataBar" priority="49">
+  <conditionalFormatting sqref="T16:T17 T19">
+    <cfRule type="dataBar" priority="58">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4070,8 +4369,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P12:P13 P30">
-    <cfRule type="dataBar" priority="53">
+  <conditionalFormatting sqref="P12:P14">
+    <cfRule type="dataBar" priority="62">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4084,8 +4383,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S12:S13 S30">
-    <cfRule type="dataBar" priority="55">
+  <conditionalFormatting sqref="S12:S14">
+    <cfRule type="dataBar" priority="64">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4098,8 +4397,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3:M33">
-    <cfRule type="colorScale" priority="56">
+  <conditionalFormatting sqref="M3:M31">
+    <cfRule type="colorScale" priority="65">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4111,7 +4410,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P31">
-    <cfRule type="dataBar" priority="58">
+    <cfRule type="dataBar" priority="67">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4125,7 +4424,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S31">
-    <cfRule type="dataBar" priority="59">
+    <cfRule type="dataBar" priority="68">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4138,29 +4437,110 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="T33">
+    <cfRule type="dataBar" priority="7">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFD6007B"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{CA4099CF-C98C-4F21-A54C-48538B23DC95}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M33">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T32">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFD6007B"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{D5DC141D-F6F3-41EC-BE3F-83A9D3929A2A}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M32">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M32">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M33">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="N6" r:id="rId1"/>
     <hyperlink ref="N7" r:id="rId2"/>
     <hyperlink ref="N12" r:id="rId3"/>
-    <hyperlink ref="N14" r:id="rId4"/>
-    <hyperlink ref="N16" r:id="rId5"/>
-    <hyperlink ref="N18" r:id="rId6"/>
-    <hyperlink ref="N17" r:id="rId7"/>
-    <hyperlink ref="N25" r:id="rId8"/>
-    <hyperlink ref="N26" r:id="rId9"/>
-    <hyperlink ref="N27" r:id="rId10"/>
-    <hyperlink ref="N28" r:id="rId11"/>
-    <hyperlink ref="N31" r:id="rId12"/>
-    <hyperlink ref="N3" r:id="rId13"/>
-    <hyperlink ref="N5" r:id="rId14"/>
-    <hyperlink ref="N13" r:id="rId15"/>
-    <hyperlink ref="N30" r:id="rId16"/>
-    <hyperlink ref="N21" r:id="rId17"/>
-    <hyperlink ref="N23" r:id="rId18"/>
-    <hyperlink ref="N19" r:id="rId19"/>
-    <hyperlink ref="N20" r:id="rId20"/>
-    <hyperlink ref="N22" r:id="rId21"/>
-    <hyperlink ref="N29" r:id="rId22"/>
+    <hyperlink ref="N15" r:id="rId4"/>
+    <hyperlink ref="N17" r:id="rId5"/>
+    <hyperlink ref="N19" r:id="rId6"/>
+    <hyperlink ref="N18" r:id="rId7"/>
+    <hyperlink ref="N27" r:id="rId8"/>
+    <hyperlink ref="N28" r:id="rId9"/>
+    <hyperlink ref="N31" r:id="rId10"/>
+    <hyperlink ref="N3" r:id="rId11"/>
+    <hyperlink ref="N5" r:id="rId12"/>
+    <hyperlink ref="N13" r:id="rId13"/>
+    <hyperlink ref="N14" r:id="rId14"/>
+    <hyperlink ref="N22" r:id="rId15"/>
+    <hyperlink ref="N24" r:id="rId16"/>
+    <hyperlink ref="N20" r:id="rId17"/>
+    <hyperlink ref="N21" r:id="rId18"/>
+    <hyperlink ref="N23" r:id="rId19"/>
+    <hyperlink ref="N30" r:id="rId20"/>
+    <hyperlink ref="N4" r:id="rId21"/>
+    <hyperlink ref="N8" r:id="rId22"/>
+    <hyperlink ref="N9" r:id="rId23"/>
+    <hyperlink ref="N10" r:id="rId24"/>
+    <hyperlink ref="N11" r:id="rId25"/>
+    <hyperlink ref="N26" r:id="rId26"/>
+    <hyperlink ref="N29" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -4230,7 +4610,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P25</xm:sqref>
+          <xm:sqref>P26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{158646A7-FB27-493B-A7FF-54D604BAD301}">
@@ -4243,7 +4623,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>S25</xm:sqref>
+          <xm:sqref>S26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{1136FB38-D2F8-4EA9-A367-22B6430B29D9}">
@@ -4256,7 +4636,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P26</xm:sqref>
+          <xm:sqref>P27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{D4A5CF13-CF84-4591-9FCC-49FF52F9F1C4}">
@@ -4269,7 +4649,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>S26</xm:sqref>
+          <xm:sqref>S27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{235FEB0C-EE6B-4A59-BD6E-7A0589E24A48}">
@@ -4321,7 +4701,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P14:P15</xm:sqref>
+          <xm:sqref>P15:P16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{9858B0C3-D0F8-40AB-A4EB-B7FA3CD44C37}">
@@ -4334,7 +4714,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P16:P24</xm:sqref>
+          <xm:sqref>P17:P25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{AA3267BB-7DF4-4184-A49B-E7450B91D10B}">
@@ -4347,7 +4727,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P27:P29</xm:sqref>
+          <xm:sqref>P28:P30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{5D986308-F274-4102-BE29-1D0CF74D077B}">
@@ -4373,7 +4753,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>S14:S15</xm:sqref>
+          <xm:sqref>S15:S16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{FF02F8A1-A0AB-48BA-BC5D-837B4F090483}">
@@ -4386,7 +4766,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>S16:S24</xm:sqref>
+          <xm:sqref>S17:S25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{A4531ED6-7A23-45F2-BE31-301BD5EA9251}">
@@ -4399,7 +4779,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>S27:S29</xm:sqref>
+          <xm:sqref>S28:S30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{08CE510F-E31E-46C1-B283-C5A0291B5E7C}">
@@ -4412,7 +4792,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>T15:T16 T18</xm:sqref>
+          <xm:sqref>T16:T17 T19</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{9387EE67-D922-4EDD-9DA9-92A432BDB36F}">
@@ -4425,7 +4805,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P12:P13 P30</xm:sqref>
+          <xm:sqref>P12:P14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{85D471B6-7BA0-466D-8A61-5132FF9B9E71}">
@@ -4438,7 +4818,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>S12:S13 S30</xm:sqref>
+          <xm:sqref>S12:S14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{BFAB5B23-2BBB-4D00-9329-1FC3154F45B1}">
@@ -4466,6 +4846,32 @@
           </x14:cfRule>
           <xm:sqref>S31</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{CA4099CF-C98C-4F21-A54C-48538B23DC95}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFD6007B"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>T33</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{D5DC141D-F6F3-41EC-BE3F-83A9D3929A2A}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFD6007B"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>T32</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/Hardware-Designing/Deliverables/BOM/LCSC BOM.xlsx
+++ b/Hardware-Designing/Deliverables/BOM/LCSC BOM.xlsx
@@ -1,25 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Github\ShockSensor-George\Hardware-Designing\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\ShockSensor-George\Hardware-Designing\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16EFC4DF-5B35-411D-9C71-FC0D6A30C766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12495"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="203">
   <si>
     <t>Bill of Material (BOM) for  Martin Transmitter</t>
   </si>
@@ -648,12 +658,18 @@
   </si>
   <si>
     <t>Chipsfind</t>
+  </si>
+  <si>
+    <t>Mouser</t>
+  </si>
+  <si>
+    <t>DONOT MOUNT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00000"/>
     <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
@@ -819,7 +835,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -1296,6 +1312,51 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1304,7 +1365,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1510,9 +1571,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1569,9 +1627,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1687,6 +1742,15 @@
     <xf numFmtId="165" fontId="17" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1726,11 +1790,26 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2007,7 +2086,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -2032,26 +2111,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="16.5" thickBot="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="135" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
-      <c r="L1" s="136"/>
-      <c r="M1" s="136"/>
-      <c r="N1" s="136"/>
-      <c r="O1" s="136"/>
-      <c r="P1" s="136"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="138"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="138"/>
+      <c r="R1" s="139"/>
       <c r="S1" s="3"/>
       <c r="T1" s="66"/>
     </row>
@@ -2121,19 +2200,19 @@
       <c r="A3" s="7">
         <v>1</v>
       </c>
-      <c r="B3" s="141" t="s">
+      <c r="B3" s="142" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="106" t="s">
+      <c r="D3" s="104" t="s">
         <v>185</v>
       </c>
-      <c r="E3" s="83" t="s">
+      <c r="E3" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="83" t="s">
+      <c r="F3" s="82" t="s">
         <v>24</v>
       </c>
       <c r="G3" s="10" t="s">
@@ -2145,7 +2224,7 @@
       <c r="I3" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="84" t="s">
+      <c r="J3" s="83" t="s">
         <v>28</v>
       </c>
       <c r="K3" s="10">
@@ -2154,11 +2233,11 @@
       <c r="L3" s="33">
         <v>50</v>
       </c>
-      <c r="M3" s="110">
+      <c r="M3" s="108">
         <f>K3*5</f>
         <v>30</v>
       </c>
-      <c r="N3" s="111" t="s">
+      <c r="N3" s="109" t="s">
         <v>29</v>
       </c>
       <c r="O3" s="36">
@@ -2185,35 +2264,35 @@
       <c r="A4" s="7">
         <v>2</v>
       </c>
-      <c r="B4" s="142"/>
-      <c r="C4" s="85" t="s">
+      <c r="B4" s="143"/>
+      <c r="C4" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="D4" s="86" t="s">
+      <c r="D4" s="85" t="s">
         <v>183</v>
       </c>
-      <c r="E4" s="87" t="s">
+      <c r="E4" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="105" t="s">
+      <c r="F4" s="103" t="s">
         <v>184</v>
       </c>
       <c r="G4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="99" t="s">
+      <c r="H4" s="97" t="s">
         <v>186</v>
       </c>
-      <c r="I4" s="102" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="100" t="s">
+      <c r="I4" s="100" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="98" t="s">
         <v>187</v>
       </c>
-      <c r="K4" s="98">
+      <c r="K4" s="96">
         <v>1</v>
       </c>
-      <c r="L4" s="101">
+      <c r="L4" s="99">
         <v>7</v>
       </c>
       <c r="M4" s="25">
@@ -2223,7 +2302,7 @@
       <c r="N4" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O4" s="103">
+      <c r="O4" s="101">
         <v>0.19919999999999999</v>
       </c>
       <c r="P4" s="37">
@@ -2234,30 +2313,30 @@
         <f t="shared" si="1"/>
         <v>1.3943999999999999</v>
       </c>
-      <c r="R4" s="103">
+      <c r="R4" s="101">
         <v>0.19919999999999999</v>
       </c>
       <c r="S4" s="37">
         <f t="shared" si="2"/>
         <v>0.996</v>
       </c>
-      <c r="T4" s="104"/>
+      <c r="T4" s="102"/>
     </row>
     <row r="5" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A5" s="7">
         <v>3</v>
       </c>
-      <c r="B5" s="142"/>
-      <c r="C5" s="85" t="s">
+      <c r="B5" s="143"/>
+      <c r="C5" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="86" t="s">
+      <c r="D5" s="85" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="87" t="s">
+      <c r="E5" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="87" t="s">
+      <c r="F5" s="86" t="s">
         <v>32</v>
       </c>
       <c r="G5" s="15" t="s">
@@ -2309,17 +2388,17 @@
       <c r="A6" s="7">
         <v>4</v>
       </c>
-      <c r="B6" s="143"/>
+      <c r="B6" s="144"/>
       <c r="C6" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="88" t="s">
+      <c r="D6" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="89" t="s">
+      <c r="E6" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="89" t="s">
+      <c r="F6" s="88" t="s">
         <v>39</v>
       </c>
       <c r="G6" s="19" t="s">
@@ -2331,7 +2410,7 @@
       <c r="I6" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="89" t="s">
+      <c r="J6" s="88" t="s">
         <v>41</v>
       </c>
       <c r="K6" s="19">
@@ -2371,19 +2450,19 @@
       <c r="A7" s="7">
         <v>5</v>
       </c>
-      <c r="B7" s="141" t="s">
+      <c r="B7" s="142" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="108" t="s">
+      <c r="C7" s="106" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="107" t="s">
+      <c r="D7" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E7" s="92" t="s">
+      <c r="E7" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="92" t="s">
+      <c r="F7" s="91" t="s">
         <v>45</v>
       </c>
       <c r="G7" s="22" t="s">
@@ -2425,27 +2504,27 @@
       <c r="R7" s="49">
         <v>5.3199999999999997E-2</v>
       </c>
-      <c r="S7" s="50">
+      <c r="S7" s="37">
         <f t="shared" si="2"/>
         <v>1.0640000000000001</v>
       </c>
-      <c r="T7" s="71"/>
+      <c r="T7" s="68"/>
     </row>
     <row r="8" spans="1:20" ht="16.5" customHeight="1" thickBot="1">
       <c r="A8" s="7">
         <v>6</v>
       </c>
-      <c r="B8" s="142"/>
-      <c r="C8" s="85" t="s">
+      <c r="B8" s="143"/>
+      <c r="C8" s="84" t="s">
         <v>169</v>
       </c>
-      <c r="D8" s="86" t="s">
+      <c r="D8" s="85" t="s">
         <v>170</v>
       </c>
-      <c r="E8" s="87" t="s">
+      <c r="E8" s="86" t="s">
         <v>171</v>
       </c>
-      <c r="F8" s="87" t="s">
+      <c r="F8" s="86" t="s">
         <v>172</v>
       </c>
       <c r="G8" s="15" t="s">
@@ -2487,27 +2566,27 @@
       <c r="R8" s="40">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="S8" s="50">
+      <c r="S8" s="41">
         <f t="shared" si="2"/>
         <v>0.21499999999999997</v>
       </c>
-      <c r="T8" s="71"/>
+      <c r="T8" s="69"/>
     </row>
     <row r="9" spans="1:20" ht="16.5" customHeight="1" thickBot="1">
       <c r="A9" s="7">
         <v>7</v>
       </c>
-      <c r="B9" s="142"/>
-      <c r="C9" s="109" t="s">
+      <c r="B9" s="143"/>
+      <c r="C9" s="107" t="s">
         <v>190</v>
       </c>
-      <c r="D9" s="86" t="s">
+      <c r="D9" s="85" t="s">
         <v>174</v>
       </c>
-      <c r="E9" s="87" t="s">
+      <c r="E9" s="86" t="s">
         <v>171</v>
       </c>
-      <c r="F9" s="87" t="s">
+      <c r="F9" s="86" t="s">
         <v>175</v>
       </c>
       <c r="G9" s="15" t="s">
@@ -2549,27 +2628,27 @@
       <c r="R9" s="40">
         <v>4.5100000000000001E-2</v>
       </c>
-      <c r="S9" s="50">
+      <c r="S9" s="41">
         <f t="shared" si="2"/>
         <v>0.22550000000000001</v>
       </c>
-      <c r="T9" s="71"/>
+      <c r="T9" s="69"/>
     </row>
     <row r="10" spans="1:20" ht="16.5" customHeight="1" thickBot="1">
       <c r="A10" s="7">
         <v>8</v>
       </c>
-      <c r="B10" s="142"/>
-      <c r="C10" s="85" t="s">
+      <c r="B10" s="143"/>
+      <c r="C10" s="84" t="s">
         <v>176</v>
       </c>
-      <c r="D10" s="86" t="s">
+      <c r="D10" s="85" t="s">
         <v>177</v>
       </c>
-      <c r="E10" s="87" t="s">
+      <c r="E10" s="86" t="s">
         <v>171</v>
       </c>
-      <c r="F10" s="87" t="s">
+      <c r="F10" s="86" t="s">
         <v>178</v>
       </c>
       <c r="G10" s="15" t="s">
@@ -2611,27 +2690,27 @@
       <c r="R10" s="40">
         <v>5.4800000000000001E-2</v>
       </c>
-      <c r="S10" s="50">
+      <c r="S10" s="41">
         <f t="shared" si="2"/>
         <v>0.27400000000000002</v>
       </c>
-      <c r="T10" s="71"/>
+      <c r="T10" s="69"/>
     </row>
     <row r="11" spans="1:20" ht="16.5" customHeight="1" thickBot="1">
       <c r="A11" s="7">
         <v>9</v>
       </c>
-      <c r="B11" s="143"/>
-      <c r="C11" s="97" t="s">
+      <c r="B11" s="144"/>
+      <c r="C11" s="95" t="s">
         <v>179</v>
       </c>
-      <c r="D11" s="88" t="s">
+      <c r="D11" s="87" t="s">
         <v>180</v>
       </c>
-      <c r="E11" s="89" t="s">
+      <c r="E11" s="88" t="s">
         <v>171</v>
       </c>
-      <c r="F11" s="89" t="s">
+      <c r="F11" s="88" t="s">
         <v>181</v>
       </c>
       <c r="G11" s="19" t="s">
@@ -2673,29 +2752,29 @@
       <c r="R11" s="49">
         <v>7.5200000000000003E-2</v>
       </c>
-      <c r="S11" s="50">
+      <c r="S11" s="45">
         <f t="shared" si="2"/>
         <v>0.376</v>
       </c>
-      <c r="T11" s="71"/>
+      <c r="T11" s="70"/>
     </row>
     <row r="12" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A12" s="7">
         <v>10</v>
       </c>
-      <c r="B12" s="141" t="s">
+      <c r="B12" s="142" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="93" t="s">
+      <c r="C12" s="92" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="82" t="s">
+      <c r="D12" s="81" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="84" t="s">
+      <c r="E12" s="83" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="84" t="s">
+      <c r="F12" s="83" t="s">
         <v>53</v>
       </c>
       <c r="G12" s="10" t="s">
@@ -2747,17 +2826,17 @@
       <c r="A13" s="7">
         <v>11</v>
       </c>
-      <c r="B13" s="142"/>
+      <c r="B13" s="143"/>
       <c r="C13" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="86" t="s">
+      <c r="D13" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="87" t="s">
+      <c r="E13" s="86" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="87" t="s">
+      <c r="F13" s="86" t="s">
         <v>59</v>
       </c>
       <c r="G13" s="15" t="s">
@@ -2809,17 +2888,17 @@
       <c r="A14" s="7">
         <v>12</v>
       </c>
-      <c r="B14" s="143"/>
+      <c r="B14" s="144"/>
       <c r="C14" s="17" t="s">
         <v>61</v>
       </c>
       <c r="D14" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="E14" s="89" t="s">
+      <c r="E14" s="88" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="89" t="s">
+      <c r="F14" s="88" t="s">
         <v>63</v>
       </c>
       <c r="G14" s="19" t="s">
@@ -2871,19 +2950,19 @@
       <c r="A15" s="7">
         <v>13</v>
       </c>
-      <c r="B15" s="141" t="s">
+      <c r="B15" s="148" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="149" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="82" t="s">
+      <c r="D15" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="84" t="s">
+      <c r="E15" s="83" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="84" t="s">
+      <c r="F15" s="83" t="s">
         <v>69</v>
       </c>
       <c r="G15" s="10" t="s">
@@ -2895,7 +2974,7 @@
       <c r="I15" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="J15" s="84" t="s">
+      <c r="J15" s="83" t="s">
         <v>73</v>
       </c>
       <c r="K15" s="24">
@@ -2931,21 +3010,21 @@
       </c>
       <c r="T15" s="68"/>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:20" ht="15.75" thickBot="1">
       <c r="A16" s="7">
         <v>14</v>
       </c>
-      <c r="B16" s="142"/>
-      <c r="C16" s="94" t="s">
+      <c r="B16" s="150"/>
+      <c r="C16" s="151" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="86" t="s">
+      <c r="D16" s="85" t="s">
         <v>75</v>
       </c>
       <c r="E16" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="87" t="s">
+      <c r="F16" s="86" t="s">
         <v>77</v>
       </c>
       <c r="G16" s="15" t="s">
@@ -2957,7 +3036,7 @@
       <c r="I16" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="J16" s="87" t="s">
+      <c r="J16" s="86" t="s">
         <v>73</v>
       </c>
       <c r="K16" s="14">
@@ -2976,38 +3055,38 @@
       <c r="O16" s="41">
         <v>0.47620000000000001</v>
       </c>
-      <c r="P16" s="37">
+      <c r="P16" s="41">
         <f>O16*K16</f>
         <v>0.47620000000000001</v>
       </c>
-      <c r="Q16" s="37">
+      <c r="Q16" s="41">
         <f>O16*L16</f>
         <v>3.3334000000000001</v>
       </c>
       <c r="R16" s="41">
         <v>0.47620000000000001</v>
       </c>
-      <c r="S16" s="37">
+      <c r="S16" s="41">
         <f>R16*M16</f>
         <v>2.3810000000000002</v>
       </c>
-      <c r="T16" s="72"/>
+      <c r="T16" s="71"/>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:20" ht="15.75" thickBot="1">
       <c r="A17" s="7">
         <v>15</v>
       </c>
-      <c r="B17" s="142"/>
-      <c r="C17" s="94" t="s">
+      <c r="B17" s="150"/>
+      <c r="C17" s="151" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="86" t="s">
+      <c r="D17" s="85" t="s">
         <v>81</v>
       </c>
-      <c r="E17" s="87" t="s">
+      <c r="E17" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="87" t="s">
+      <c r="F17" s="86" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="15" t="s">
@@ -3019,7 +3098,7 @@
       <c r="I17" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="J17" s="87" t="s">
+      <c r="J17" s="86" t="s">
         <v>85</v>
       </c>
       <c r="K17" s="14">
@@ -3053,23 +3132,23 @@
         <f t="shared" si="6"/>
         <v>1.9E-2</v>
       </c>
-      <c r="T17" s="72"/>
+      <c r="T17" s="71"/>
     </row>
-    <row r="18" spans="1:20">
+    <row r="18" spans="1:20" ht="15.75" thickBot="1">
       <c r="A18" s="7">
         <v>16</v>
       </c>
-      <c r="B18" s="142"/>
-      <c r="C18" s="13" t="s">
+      <c r="B18" s="150"/>
+      <c r="C18" s="152" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="86" t="s">
+      <c r="D18" s="85" t="s">
         <v>87</v>
       </c>
-      <c r="E18" s="87" t="s">
+      <c r="E18" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="F18" s="87" t="s">
+      <c r="F18" s="86" t="s">
         <v>88</v>
       </c>
       <c r="G18" s="15" t="s">
@@ -3081,7 +3160,7 @@
       <c r="I18" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="J18" s="87" t="s">
+      <c r="J18" s="86" t="s">
         <v>91</v>
       </c>
       <c r="K18" s="14">
@@ -3115,23 +3194,23 @@
         <f t="shared" si="6"/>
         <v>2.9999999999999996E-3</v>
       </c>
-      <c r="T18" s="73"/>
+      <c r="T18" s="72"/>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" spans="1:20" ht="15.75" thickBot="1">
       <c r="A19" s="7">
         <v>17</v>
       </c>
-      <c r="B19" s="142"/>
-      <c r="C19" s="13" t="s">
+      <c r="B19" s="150"/>
+      <c r="C19" s="152" t="s">
         <v>92</v>
       </c>
-      <c r="D19" s="86" t="s">
+      <c r="D19" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="E19" s="87" t="s">
+      <c r="E19" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="F19" s="87" t="s">
+      <c r="F19" s="86" t="s">
         <v>94</v>
       </c>
       <c r="G19" s="15" t="s">
@@ -3143,7 +3222,7 @@
       <c r="I19" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="J19" s="87" t="s">
+      <c r="J19" s="86" t="s">
         <v>96</v>
       </c>
       <c r="K19" s="14">
@@ -3177,23 +3256,23 @@
         <f t="shared" si="6"/>
         <v>2.8500000000000001E-2</v>
       </c>
-      <c r="T19" s="74"/>
+      <c r="T19" s="73"/>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" spans="1:20" ht="15.75" thickBot="1">
       <c r="A20" s="7">
         <v>18</v>
       </c>
-      <c r="B20" s="142"/>
-      <c r="C20" s="94" t="s">
+      <c r="B20" s="150"/>
+      <c r="C20" s="151" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="86" t="s">
+      <c r="D20" s="85" t="s">
         <v>98</v>
       </c>
-      <c r="E20" s="87" t="s">
+      <c r="E20" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="F20" s="87" t="s">
+      <c r="F20" s="86" t="s">
         <v>99</v>
       </c>
       <c r="G20" s="15" t="s">
@@ -3239,23 +3318,23 @@
         <f t="shared" ref="S20:S25" si="8">R20*M20</f>
         <v>6.4999999999999997E-3</v>
       </c>
-      <c r="T20" s="75"/>
+      <c r="T20" s="74"/>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="1:20" ht="15.75" thickBot="1">
       <c r="A21" s="7">
         <v>19</v>
       </c>
-      <c r="B21" s="142"/>
-      <c r="C21" s="94" t="s">
+      <c r="B21" s="150"/>
+      <c r="C21" s="151" t="s">
         <v>103</v>
       </c>
-      <c r="D21" s="86" t="s">
+      <c r="D21" s="85" t="s">
         <v>104</v>
       </c>
-      <c r="E21" s="87" t="s">
+      <c r="E21" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="F21" s="87" t="s">
+      <c r="F21" s="86" t="s">
         <v>105</v>
       </c>
       <c r="G21" s="15" t="s">
@@ -3301,23 +3380,23 @@
         <f t="shared" si="8"/>
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="T21" s="75"/>
+      <c r="T21" s="74"/>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:20" ht="15.75" thickBot="1">
       <c r="A22" s="7">
         <v>20</v>
       </c>
-      <c r="B22" s="142"/>
-      <c r="C22" s="13" t="s">
+      <c r="B22" s="150"/>
+      <c r="C22" s="152" t="s">
         <v>109</v>
       </c>
-      <c r="D22" s="86" t="s">
+      <c r="D22" s="85" t="s">
         <v>110</v>
       </c>
-      <c r="E22" s="87" t="s">
+      <c r="E22" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="87" t="s">
+      <c r="F22" s="86" t="s">
         <v>111</v>
       </c>
       <c r="G22" s="15" t="s">
@@ -3363,23 +3442,23 @@
         <f t="shared" si="8"/>
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="T22" s="76"/>
+      <c r="T22" s="75"/>
     </row>
-    <row r="23" spans="1:20">
+    <row r="23" spans="1:20" ht="15.75" thickBot="1">
       <c r="A23" s="7">
         <v>21</v>
       </c>
-      <c r="B23" s="142"/>
-      <c r="C23" s="94" t="s">
+      <c r="B23" s="150"/>
+      <c r="C23" s="151" t="s">
         <v>113</v>
       </c>
-      <c r="D23" s="86" t="s">
+      <c r="D23" s="85" t="s">
         <v>114</v>
       </c>
-      <c r="E23" s="87" t="s">
+      <c r="E23" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="87" t="s">
+      <c r="F23" s="86" t="s">
         <v>115</v>
       </c>
       <c r="G23" s="15" t="s">
@@ -3425,23 +3504,23 @@
         <f t="shared" si="8"/>
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="T23" s="77"/>
+      <c r="T23" s="76"/>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="1:20" ht="15.75" thickBot="1">
       <c r="A24" s="7">
         <v>22</v>
       </c>
-      <c r="B24" s="143"/>
-      <c r="C24" s="17" t="s">
+      <c r="B24" s="153"/>
+      <c r="C24" s="154" t="s">
         <v>118</v>
       </c>
-      <c r="D24" s="88" t="s">
+      <c r="D24" s="87" t="s">
         <v>119</v>
       </c>
-      <c r="E24" s="89" t="s">
+      <c r="E24" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="F24" s="89" t="s">
+      <c r="F24" s="88" t="s">
         <v>120</v>
       </c>
       <c r="G24" s="19" t="s">
@@ -3487,7 +3566,7 @@
         <f t="shared" si="8"/>
         <v>2.2000000000000002E-2</v>
       </c>
-      <c r="T24" s="78"/>
+      <c r="T24" s="77"/>
     </row>
     <row r="25" spans="1:20" ht="16.5" thickBot="1">
       <c r="A25" s="7">
@@ -3496,16 +3575,16 @@
       <c r="B25" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="C25" s="90" t="s">
+      <c r="C25" s="89" t="s">
         <v>124</v>
       </c>
-      <c r="D25" s="91" t="s">
+      <c r="D25" s="90" t="s">
         <v>125</v>
       </c>
       <c r="E25" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="F25" s="92" t="s">
+      <c r="F25" s="91" t="s">
         <v>126</v>
       </c>
       <c r="G25" s="22" t="s">
@@ -3551,7 +3630,7 @@
         <f t="shared" si="8"/>
         <v>1.59</v>
       </c>
-      <c r="T25" s="79"/>
+      <c r="T25" s="78"/>
     </row>
     <row r="26" spans="1:20" ht="16.5" thickBot="1">
       <c r="A26" s="7">
@@ -3560,16 +3639,16 @@
       <c r="B26" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="95" t="s">
+      <c r="C26" s="93" t="s">
         <v>128</v>
       </c>
-      <c r="D26" s="96" t="s">
+      <c r="D26" s="94" t="s">
         <v>129</v>
       </c>
       <c r="E26" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="F26" s="96" t="s">
+      <c r="F26" s="94" t="s">
         <v>130</v>
       </c>
       <c r="G26" s="28" t="s">
@@ -3594,19 +3673,19 @@
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="N26" s="147" t="s">
+      <c r="N26" s="132" t="s">
         <v>199</v>
       </c>
       <c r="O26" s="57">
-        <v>0.55489999999999995</v>
+        <v>0.49941000000000002</v>
       </c>
       <c r="P26" s="58">
         <f t="shared" ref="P26:P31" si="9">O26*K26</f>
-        <v>1.1097999999999999</v>
+        <v>0.99882000000000004</v>
       </c>
       <c r="Q26" s="58">
         <f t="shared" ref="Q26:Q31" si="10">O26*L26</f>
-        <v>6.6587999999999994</v>
+        <v>5.9929199999999998</v>
       </c>
       <c r="R26" s="58">
         <v>0.55489999999999995</v>
@@ -3615,7 +3694,7 @@
         <f t="shared" ref="S26:S31" si="11">R26*M26</f>
         <v>5.5489999999999995</v>
       </c>
-      <c r="T26" s="112" t="s">
+      <c r="T26" s="110" t="s">
         <v>197</v>
       </c>
     </row>
@@ -3623,19 +3702,19 @@
       <c r="A27" s="7">
         <v>25</v>
       </c>
-      <c r="B27" s="141" t="s">
+      <c r="B27" s="142" t="s">
         <v>133</v>
       </c>
-      <c r="C27" s="93" t="s">
+      <c r="C27" s="92" t="s">
         <v>134</v>
       </c>
-      <c r="D27" s="84" t="s">
+      <c r="D27" s="83" t="s">
         <v>135</v>
       </c>
       <c r="E27" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="F27" s="84" t="s">
+      <c r="F27" s="83" t="s">
         <v>191</v>
       </c>
       <c r="G27" s="10" t="s">
@@ -3660,28 +3739,28 @@
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N27" s="35" t="s">
-        <v>29</v>
+      <c r="N27" s="134" t="s">
+        <v>201</v>
       </c>
       <c r="O27" s="37">
-        <v>4.5010000000000003</v>
+        <v>2.88</v>
       </c>
       <c r="P27" s="37">
         <f t="shared" si="9"/>
-        <v>4.5010000000000003</v>
+        <v>2.88</v>
       </c>
       <c r="Q27" s="37">
         <f t="shared" si="10"/>
-        <v>27.006</v>
+        <v>17.28</v>
       </c>
       <c r="R27" s="37">
-        <v>4.5010000000000003</v>
+        <v>2.88</v>
       </c>
       <c r="S27" s="37">
         <f t="shared" si="11"/>
-        <v>22.505000000000003</v>
-      </c>
-      <c r="T27" s="113" t="s">
+        <v>14.399999999999999</v>
+      </c>
+      <c r="T27" s="111" t="s">
         <v>197</v>
       </c>
     </row>
@@ -3689,17 +3768,17 @@
       <c r="A28" s="7">
         <v>26</v>
       </c>
-      <c r="B28" s="142"/>
+      <c r="B28" s="143"/>
       <c r="C28" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="D28" s="87" t="s">
+      <c r="D28" s="86" t="s">
         <v>138</v>
       </c>
-      <c r="E28" s="87" t="s">
+      <c r="E28" s="86" t="s">
         <v>139</v>
       </c>
-      <c r="F28" s="87" t="s">
+      <c r="F28" s="86" t="s">
         <v>140</v>
       </c>
       <c r="G28" s="15" t="s">
@@ -3745,23 +3824,23 @@
         <f t="shared" si="11"/>
         <v>1.2559999999999998</v>
       </c>
-      <c r="T28" s="115"/>
+      <c r="T28" s="113"/>
     </row>
     <row r="29" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A29" s="7">
         <v>27</v>
       </c>
-      <c r="B29" s="142"/>
+      <c r="B29" s="143"/>
       <c r="C29" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="D29" s="87" t="s">
+      <c r="D29" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="E29" s="87" t="s">
+      <c r="E29" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="F29" s="87" t="s">
+      <c r="F29" s="86" t="s">
         <v>146</v>
       </c>
       <c r="G29" s="15" t="s">
@@ -3786,7 +3865,7 @@
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N29" s="148" t="s">
+      <c r="N29" s="133" t="s">
         <v>200</v>
       </c>
       <c r="O29" s="41">
@@ -3807,7 +3886,7 @@
         <f t="shared" si="11"/>
         <v>4.95</v>
       </c>
-      <c r="T29" s="116" t="s">
+      <c r="T29" s="114" t="s">
         <v>197</v>
       </c>
     </row>
@@ -3815,17 +3894,17 @@
       <c r="A30" s="7">
         <v>28</v>
       </c>
-      <c r="B30" s="143"/>
-      <c r="C30" s="97" t="s">
+      <c r="B30" s="144"/>
+      <c r="C30" s="95" t="s">
         <v>149</v>
       </c>
-      <c r="D30" s="89" t="s">
+      <c r="D30" s="88" t="s">
         <v>150</v>
       </c>
       <c r="E30" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="F30" s="89" t="s">
+      <c r="F30" s="88" t="s">
         <v>152</v>
       </c>
       <c r="G30" s="19" t="s">
@@ -3864,14 +3943,14 @@
         <f t="shared" si="10"/>
         <v>18.631800000000002</v>
       </c>
-      <c r="R30" s="81">
+      <c r="R30" s="80">
         <v>3.1053000000000002</v>
       </c>
       <c r="S30" s="45">
         <f t="shared" si="11"/>
         <v>15.5265</v>
       </c>
-      <c r="T30" s="114" t="s">
+      <c r="T30" s="112" t="s">
         <v>197</v>
       </c>
     </row>
@@ -3879,19 +3958,19 @@
       <c r="A31" s="7">
         <v>29</v>
       </c>
-      <c r="B31" s="144" t="s">
+      <c r="B31" s="145" t="s">
         <v>155</v>
       </c>
-      <c r="C31" s="93" t="s">
+      <c r="C31" s="92" t="s">
         <v>156</v>
       </c>
-      <c r="D31" s="84" t="s">
+      <c r="D31" s="83" t="s">
         <v>157</v>
       </c>
       <c r="E31" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="F31" s="84" t="s">
+      <c r="F31" s="83" t="s">
         <v>158</v>
       </c>
       <c r="G31" s="10" t="s">
@@ -3937,158 +4016,162 @@
         <f t="shared" si="11"/>
         <v>1.121</v>
       </c>
-      <c r="T31" s="80"/>
+      <c r="T31" s="79"/>
     </row>
     <row r="32" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A32" s="7">
         <v>30</v>
       </c>
-      <c r="B32" s="145"/>
-      <c r="C32" s="117" t="s">
+      <c r="B32" s="146"/>
+      <c r="C32" s="115" t="s">
         <v>161</v>
       </c>
-      <c r="D32" s="118" t="s">
+      <c r="D32" s="116" t="s">
         <v>162</v>
       </c>
-      <c r="E32" s="118" t="s">
+      <c r="E32" s="116" t="s">
         <v>76</v>
       </c>
-      <c r="F32" s="121" t="s">
+      <c r="F32" s="119" t="s">
         <v>163</v>
       </c>
-      <c r="G32" s="123" t="s">
-        <v>35</v>
-      </c>
-      <c r="H32" s="123" t="s">
-        <v>35</v>
-      </c>
-      <c r="I32" s="123" t="s">
-        <v>35</v>
-      </c>
-      <c r="J32" s="123" t="s">
-        <v>35</v>
-      </c>
-      <c r="K32" s="123">
+      <c r="G32" s="121" t="s">
+        <v>35</v>
+      </c>
+      <c r="H32" s="121" t="s">
+        <v>35</v>
+      </c>
+      <c r="I32" s="121" t="s">
+        <v>35</v>
+      </c>
+      <c r="J32" s="121" t="s">
+        <v>35</v>
+      </c>
+      <c r="K32" s="121">
         <v>1</v>
       </c>
-      <c r="L32" s="123" t="s">
-        <v>35</v>
-      </c>
-      <c r="M32" s="124">
+      <c r="L32" s="121" t="s">
+        <v>35</v>
+      </c>
+      <c r="M32" s="122">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N32" s="125" t="s">
-        <v>35</v>
-      </c>
-      <c r="O32" s="126" t="s">
-        <v>35</v>
-      </c>
-      <c r="P32" s="126" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q32" s="126" t="s">
-        <v>35</v>
-      </c>
-      <c r="R32" s="126" t="s">
-        <v>35</v>
-      </c>
-      <c r="S32" s="126" t="s">
-        <v>35</v>
-      </c>
-      <c r="T32" s="127"/>
+      <c r="N32" s="123" t="s">
+        <v>35</v>
+      </c>
+      <c r="O32" s="124" t="s">
+        <v>35</v>
+      </c>
+      <c r="P32" s="124" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q32" s="124" t="s">
+        <v>35</v>
+      </c>
+      <c r="R32" s="124" t="s">
+        <v>35</v>
+      </c>
+      <c r="S32" s="124" t="s">
+        <v>35</v>
+      </c>
+      <c r="T32" s="125" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="33" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A33" s="7">
         <v>31</v>
       </c>
-      <c r="B33" s="146"/>
-      <c r="C33" s="119" t="s">
+      <c r="B33" s="147"/>
+      <c r="C33" s="117" t="s">
         <v>164</v>
       </c>
-      <c r="D33" s="120" t="s">
+      <c r="D33" s="118" t="s">
         <v>165</v>
       </c>
-      <c r="E33" s="120" t="s">
+      <c r="E33" s="118" t="s">
         <v>76</v>
       </c>
-      <c r="F33" s="122" t="s">
+      <c r="F33" s="120" t="s">
         <v>166</v>
       </c>
-      <c r="G33" s="128" t="s">
-        <v>35</v>
-      </c>
-      <c r="H33" s="129" t="s">
-        <v>35</v>
-      </c>
-      <c r="I33" s="129" t="s">
-        <v>35</v>
-      </c>
-      <c r="J33" s="129" t="s">
-        <v>35</v>
-      </c>
-      <c r="K33" s="129">
+      <c r="G33" s="126" t="s">
+        <v>35</v>
+      </c>
+      <c r="H33" s="127" t="s">
+        <v>35</v>
+      </c>
+      <c r="I33" s="127" t="s">
+        <v>35</v>
+      </c>
+      <c r="J33" s="127" t="s">
+        <v>35</v>
+      </c>
+      <c r="K33" s="127">
         <v>5</v>
       </c>
-      <c r="L33" s="129" t="s">
-        <v>35</v>
-      </c>
-      <c r="M33" s="130">
+      <c r="L33" s="127" t="s">
+        <v>35</v>
+      </c>
+      <c r="M33" s="128">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="N33" s="131" t="s">
-        <v>35</v>
-      </c>
-      <c r="O33" s="132" t="s">
-        <v>35</v>
-      </c>
-      <c r="P33" s="132" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q33" s="132" t="s">
-        <v>35</v>
-      </c>
-      <c r="R33" s="132" t="s">
-        <v>35</v>
-      </c>
-      <c r="S33" s="132" t="s">
-        <v>35</v>
-      </c>
-      <c r="T33" s="133"/>
+      <c r="N33" s="129" t="s">
+        <v>35</v>
+      </c>
+      <c r="O33" s="130" t="s">
+        <v>35</v>
+      </c>
+      <c r="P33" s="130" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q33" s="130" t="s">
+        <v>35</v>
+      </c>
+      <c r="R33" s="130" t="s">
+        <v>35</v>
+      </c>
+      <c r="S33" s="130" t="s">
+        <v>35</v>
+      </c>
+      <c r="T33" s="131" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="34" spans="1:20" ht="19.5" thickBot="1">
-      <c r="K34" s="139" t="s">
+      <c r="K34" s="140" t="s">
         <v>167</v>
       </c>
-      <c r="L34" s="139"/>
-      <c r="M34" s="139"/>
-      <c r="N34" s="139"/>
+      <c r="L34" s="140"/>
+      <c r="M34" s="140"/>
+      <c r="N34" s="140"/>
       <c r="O34" s="63">
-        <f>SUM(O3:O33)</f>
-        <v>11.4419</v>
+        <f>SUM(O3:O31)</f>
+        <v>9.765410000000001</v>
       </c>
       <c r="P34" s="64"/>
       <c r="Q34" s="63">
-        <f>SUM(Q3:Q33)</f>
-        <v>79.631099999999989</v>
+        <f>SUM(Q3:Q31)</f>
+        <v>69.239220000000003</v>
       </c>
     </row>
     <row r="35" spans="1:20" ht="18.75">
-      <c r="K35" s="140" t="s">
+      <c r="K35" s="141" t="s">
         <v>168</v>
       </c>
-      <c r="L35" s="140"/>
-      <c r="M35" s="140"/>
-      <c r="N35" s="140"/>
+      <c r="L35" s="141"/>
+      <c r="M35" s="141"/>
+      <c r="N35" s="141"/>
       <c r="O35" s="65">
         <f>SUM(O33:O34)</f>
-        <v>11.4419</v>
+        <v>9.765410000000001</v>
       </c>
       <c r="P35" s="64"/>
       <c r="Q35" s="65">
         <f>Q34/5</f>
-        <v>15.926219999999997</v>
+        <v>13.847844</v>
       </c>
     </row>
   </sheetData>
@@ -4104,7 +4187,7 @@
     <mergeCell ref="B31:B33"/>
   </mergeCells>
   <conditionalFormatting sqref="P6">
-    <cfRule type="dataBar" priority="28">
+    <cfRule type="dataBar" priority="29">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4118,7 +4201,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S6">
-    <cfRule type="dataBar" priority="29">
+    <cfRule type="dataBar" priority="30">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4132,7 +4215,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P7:P11">
-    <cfRule type="dataBar" priority="26">
+    <cfRule type="dataBar" priority="27">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4146,7 +4229,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S7:S11">
-    <cfRule type="dataBar" priority="27">
+    <cfRule type="dataBar" priority="28">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4160,7 +4243,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P26">
-    <cfRule type="dataBar" priority="18">
+    <cfRule type="dataBar" priority="19">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4174,7 +4257,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S26">
-    <cfRule type="dataBar" priority="19">
+    <cfRule type="dataBar" priority="20">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4188,7 +4271,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P27">
-    <cfRule type="dataBar" priority="16">
+    <cfRule type="dataBar" priority="17">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4202,7 +4285,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S27">
-    <cfRule type="dataBar" priority="17">
+    <cfRule type="dataBar" priority="18">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4216,7 +4299,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O35">
-    <cfRule type="dataBar" priority="11">
+    <cfRule type="dataBar" priority="12">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4230,7 +4313,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q35">
-    <cfRule type="dataBar" priority="10">
+    <cfRule type="dataBar" priority="11">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4244,7 +4327,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3:P5">
-    <cfRule type="dataBar" priority="30">
+    <cfRule type="dataBar" priority="31">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4258,7 +4341,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P15:P16">
-    <cfRule type="dataBar" priority="22">
+    <cfRule type="dataBar" priority="23">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4272,7 +4355,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P17:P25">
-    <cfRule type="dataBar" priority="20">
+    <cfRule type="dataBar" priority="21">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4286,7 +4369,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P28:P30">
-    <cfRule type="dataBar" priority="14">
+    <cfRule type="dataBar" priority="15">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4300,7 +4383,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3:S5">
-    <cfRule type="dataBar" priority="31">
+    <cfRule type="dataBar" priority="32">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4314,7 +4397,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S15:S16">
-    <cfRule type="dataBar" priority="23">
+    <cfRule type="dataBar" priority="24">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4328,7 +4411,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S17:S25">
-    <cfRule type="dataBar" priority="21">
+    <cfRule type="dataBar" priority="22">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4342,7 +4425,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S28:S30">
-    <cfRule type="dataBar" priority="15">
+    <cfRule type="dataBar" priority="16">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4356,7 +4439,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T16:T17 T19">
-    <cfRule type="dataBar" priority="58">
+    <cfRule type="dataBar" priority="59">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4370,7 +4453,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P12:P14">
-    <cfRule type="dataBar" priority="62">
+    <cfRule type="dataBar" priority="63">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4384,7 +4467,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S12:S14">
-    <cfRule type="dataBar" priority="64">
+    <cfRule type="dataBar" priority="65">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4398,7 +4481,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3:M31">
-    <cfRule type="colorScale" priority="65">
+    <cfRule type="colorScale" priority="66">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4410,7 +4493,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P31">
-    <cfRule type="dataBar" priority="67">
+    <cfRule type="dataBar" priority="68">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4424,7 +4507,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S31">
-    <cfRule type="dataBar" priority="68">
+    <cfRule type="dataBar" priority="69">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4438,7 +4521,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T33">
-    <cfRule type="dataBar" priority="7">
+    <cfRule type="dataBar" priority="8">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4452,7 +4535,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M33">
-    <cfRule type="colorScale" priority="9">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4464,7 +4547,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T32">
-    <cfRule type="dataBar" priority="4">
+    <cfRule type="dataBar" priority="5">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4478,6 +4561,30 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M32">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M32">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M33">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -4489,19 +4596,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M32">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M33">
+  <conditionalFormatting sqref="K3:K33">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -4514,36 +4609,36 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="N6" r:id="rId1"/>
-    <hyperlink ref="N7" r:id="rId2"/>
-    <hyperlink ref="N12" r:id="rId3"/>
-    <hyperlink ref="N15" r:id="rId4"/>
-    <hyperlink ref="N17" r:id="rId5"/>
-    <hyperlink ref="N19" r:id="rId6"/>
-    <hyperlink ref="N18" r:id="rId7"/>
-    <hyperlink ref="N27" r:id="rId8"/>
-    <hyperlink ref="N28" r:id="rId9"/>
-    <hyperlink ref="N31" r:id="rId10"/>
-    <hyperlink ref="N3" r:id="rId11"/>
-    <hyperlink ref="N5" r:id="rId12"/>
-    <hyperlink ref="N13" r:id="rId13"/>
-    <hyperlink ref="N14" r:id="rId14"/>
-    <hyperlink ref="N22" r:id="rId15"/>
-    <hyperlink ref="N24" r:id="rId16"/>
-    <hyperlink ref="N20" r:id="rId17"/>
-    <hyperlink ref="N21" r:id="rId18"/>
-    <hyperlink ref="N23" r:id="rId19"/>
-    <hyperlink ref="N30" r:id="rId20"/>
-    <hyperlink ref="N4" r:id="rId21"/>
-    <hyperlink ref="N8" r:id="rId22"/>
-    <hyperlink ref="N9" r:id="rId23"/>
-    <hyperlink ref="N10" r:id="rId24"/>
-    <hyperlink ref="N11" r:id="rId25"/>
-    <hyperlink ref="N26" r:id="rId26"/>
-    <hyperlink ref="N29" r:id="rId27"/>
+    <hyperlink ref="N6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="N7" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N12" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="N15" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="N17" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="N19" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N18" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="N28" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="N31" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="N3" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="N5" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="N13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="N14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="N22" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="N24" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="N20" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N21" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="N23" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="N30" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="N4" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="N8" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="N9" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="N10" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="N11" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="N26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="N27" r:id="rId26" xr:uid="{3A02A36A-76E7-4940-9597-3F3FE3538FCB}"/>
+    <hyperlink ref="N29" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId28"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>

--- a/Hardware-Designing/Deliverables/BOM/LCSC BOM.xlsx
+++ b/Hardware-Designing/Deliverables/BOM/LCSC BOM.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\ShockSensor-George\Hardware-Designing\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Github\ShockSensor-George\Hardware-Designing\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16EFC4DF-5B35-411D-9C71-FC0D6A30C766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="202">
   <si>
     <t>Bill of Material (BOM) for  Martin Transmitter</t>
   </si>
@@ -450,9 +449,6 @@
     <t>IC</t>
   </si>
   <si>
-    <t>RX TXRX MOD WIFI TRACE ANT SMD</t>
-  </si>
-  <si>
     <t>U1</t>
   </si>
   <si>
@@ -629,9 +625,6 @@
 </t>
   </si>
   <si>
-    <t>ESP32-WROOM-32E(4MB)</t>
-  </si>
-  <si>
     <t>C282135</t>
   </si>
   <si>
@@ -650,32 +643,36 @@
     <t>Non Stock in LCSC</t>
   </si>
   <si>
-    <t xml:space="preserve">C231329
+    <t>Utsource</t>
+  </si>
+  <si>
+    <t>Chipsfind</t>
+  </si>
+  <si>
+    <t>DONOT MOUNT</t>
+  </si>
+  <si>
+    <t>ESP32-S2-WROOM-I(4M)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18x31x3.3mm WiFi Modules ROHS
 </t>
   </si>
   <si>
-    <t>Utsource</t>
-  </si>
-  <si>
-    <t>Chipsfind</t>
-  </si>
-  <si>
-    <t>Mouser</t>
-  </si>
-  <si>
-    <t>DONOT MOUNT</t>
+    <t xml:space="preserve">C967026
+</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00000"/>
     <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.0000"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -739,13 +736,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -835,7 +825,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="41">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -1313,11 +1303,35 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
       <top style="medium">
         <color auto="1"/>
@@ -1329,10 +1343,10 @@
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
       <top style="thin">
         <color auto="1"/>
@@ -1344,10 +1358,10 @@
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
       <top style="thin">
         <color auto="1"/>
@@ -1360,12 +1374,12 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="155">
+  <cellXfs count="170">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1392,15 +1406,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1469,69 +1477,54 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1550,12 +1543,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1579,15 +1569,14 @@
     <xf numFmtId="164" fontId="6" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1624,9 +1613,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1660,9 +1646,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1675,80 +1658,64 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1766,10 +1733,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1781,35 +1748,127 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2086,7 +2145,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -2111,28 +2170,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="16.5" thickBot="1">
-      <c r="A1" s="135" t="s">
+      <c r="A1" s="118" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
-      <c r="F1" s="137"/>
-      <c r="G1" s="137"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="138"/>
-      <c r="R1" s="139"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="122"/>
       <c r="S1" s="3"/>
-      <c r="T1" s="66"/>
+      <c r="T1" s="58"/>
     </row>
     <row r="2" spans="1:20" ht="16.5" thickBot="1">
       <c r="A2" s="4" t="s">
@@ -2144,7 +2203,7 @@
       <c r="C2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="6" t="s">
@@ -2174,7 +2233,7 @@
       <c r="M2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="31" t="s">
+      <c r="N2" s="29" t="s">
         <v>14</v>
       </c>
       <c r="O2" s="6" t="s">
@@ -2189,7 +2248,7 @@
       <c r="R2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="67" t="s">
+      <c r="S2" s="59" t="s">
         <v>19</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -2200,1978 +2259,1976 @@
       <c r="A3" s="7">
         <v>1</v>
       </c>
-      <c r="B3" s="142" t="s">
+      <c r="B3" s="125" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="104" t="s">
-        <v>185</v>
-      </c>
-      <c r="E3" s="82" t="s">
+      <c r="D3" s="134" t="s">
+        <v>184</v>
+      </c>
+      <c r="E3" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="82" t="s">
+      <c r="F3" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="I3" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="83" t="s">
+      <c r="J3" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="10">
+      <c r="K3" s="9">
         <v>6</v>
       </c>
-      <c r="L3" s="33">
+      <c r="L3" s="31">
         <v>50</v>
       </c>
-      <c r="M3" s="108">
+      <c r="M3" s="97">
         <f>K3*5</f>
         <v>30</v>
       </c>
-      <c r="N3" s="109" t="s">
+      <c r="N3" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="36">
+      <c r="O3" s="33">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="P3" s="37">
+      <c r="P3" s="34">
         <f t="shared" ref="P3:P13" si="0">O3*K3</f>
         <v>5.6999999999999995E-2</v>
       </c>
-      <c r="Q3" s="37">
+      <c r="Q3" s="34">
         <f t="shared" ref="Q3:Q13" si="1">O3*L3</f>
         <v>0.47499999999999998</v>
       </c>
-      <c r="R3" s="36">
+      <c r="R3" s="33">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="S3" s="37">
+      <c r="S3" s="34">
         <f t="shared" ref="S3:S13" si="2">R3*M3</f>
         <v>0.28499999999999998</v>
       </c>
-      <c r="T3" s="68"/>
+      <c r="T3" s="60"/>
     </row>
     <row r="4" spans="1:20" ht="15.75" thickBot="1">
       <c r="A4" s="7">
         <v>2</v>
       </c>
-      <c r="B4" s="143"/>
-      <c r="C4" s="84" t="s">
+      <c r="B4" s="126"/>
+      <c r="C4" s="75" t="s">
+        <v>181</v>
+      </c>
+      <c r="D4" s="76" t="s">
         <v>182</v>
       </c>
-      <c r="D4" s="85" t="s">
+      <c r="E4" s="77" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="93" t="s">
         <v>183</v>
       </c>
-      <c r="E4" s="86" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="103" t="s">
-        <v>184</v>
-      </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="97" t="s">
+      <c r="H4" s="87" t="s">
+        <v>185</v>
+      </c>
+      <c r="I4" s="90" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="88" t="s">
         <v>186</v>
       </c>
-      <c r="I4" s="100" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="98" t="s">
-        <v>187</v>
-      </c>
-      <c r="K4" s="96">
+      <c r="K4" s="86">
         <v>1</v>
       </c>
-      <c r="L4" s="99">
+      <c r="L4" s="89">
         <v>7</v>
       </c>
-      <c r="M4" s="25">
+      <c r="M4" s="23">
         <f>K4*5</f>
         <v>5</v>
       </c>
-      <c r="N4" s="39" t="s">
+      <c r="N4" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="O4" s="101">
+      <c r="O4" s="91">
         <v>0.19919999999999999</v>
       </c>
-      <c r="P4" s="37">
+      <c r="P4" s="34">
         <f t="shared" si="0"/>
         <v>0.19919999999999999</v>
       </c>
-      <c r="Q4" s="37">
+      <c r="Q4" s="34">
         <f t="shared" si="1"/>
         <v>1.3943999999999999</v>
       </c>
-      <c r="R4" s="101">
+      <c r="R4" s="91">
         <v>0.19919999999999999</v>
       </c>
-      <c r="S4" s="37">
+      <c r="S4" s="34">
         <f t="shared" si="2"/>
         <v>0.996</v>
       </c>
-      <c r="T4" s="102"/>
+      <c r="T4" s="92"/>
     </row>
     <row r="5" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A5" s="7">
         <v>3</v>
       </c>
-      <c r="B5" s="143"/>
-      <c r="C5" s="84" t="s">
+      <c r="B5" s="126"/>
+      <c r="C5" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="85" t="s">
+      <c r="D5" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="86" t="s">
+      <c r="E5" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="86" t="s">
+      <c r="F5" s="77" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="14" t="s">
+      <c r="I5" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="13">
         <v>2</v>
       </c>
-      <c r="L5" s="38">
+      <c r="L5" s="35">
         <v>20</v>
       </c>
-      <c r="M5" s="25">
+      <c r="M5" s="23">
         <f t="shared" ref="M5:M33" si="3">K5*5</f>
         <v>10</v>
       </c>
-      <c r="N5" s="39" t="s">
+      <c r="N5" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="36">
         <v>5.7599999999999998E-2</v>
       </c>
-      <c r="P5" s="41">
+      <c r="P5" s="37">
         <f t="shared" si="0"/>
         <v>0.1152</v>
       </c>
-      <c r="Q5" s="41">
+      <c r="Q5" s="37">
         <f t="shared" si="1"/>
         <v>1.1519999999999999</v>
       </c>
-      <c r="R5" s="40">
+      <c r="R5" s="36">
         <v>5.7599999999999998E-2</v>
       </c>
-      <c r="S5" s="41">
+      <c r="S5" s="37">
         <f t="shared" si="2"/>
         <v>0.57599999999999996</v>
       </c>
-      <c r="T5" s="69"/>
+      <c r="T5" s="61"/>
     </row>
     <row r="6" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A6" s="7">
         <v>4</v>
       </c>
-      <c r="B6" s="144"/>
-      <c r="C6" s="17" t="s">
+      <c r="B6" s="127"/>
+      <c r="C6" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="87" t="s">
+      <c r="D6" s="78" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="88" t="s">
+      <c r="E6" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="88" t="s">
+      <c r="F6" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="20" t="s">
+      <c r="H6" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" s="88" t="s">
+      <c r="I6" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="79" t="s">
         <v>41</v>
       </c>
-      <c r="K6" s="19">
+      <c r="K6" s="17">
         <v>2</v>
       </c>
-      <c r="L6" s="42">
+      <c r="L6" s="38">
         <v>50</v>
       </c>
-      <c r="M6" s="30">
+      <c r="M6" s="28">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="N6" s="43" t="s">
+      <c r="N6" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O6" s="44">
+      <c r="O6" s="40">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="P6" s="45">
+      <c r="P6" s="41">
         <f t="shared" si="0"/>
         <v>1.0200000000000001E-2</v>
       </c>
-      <c r="Q6" s="45">
+      <c r="Q6" s="41">
         <f t="shared" si="1"/>
         <v>0.255</v>
       </c>
-      <c r="R6" s="44">
+      <c r="R6" s="40">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="S6" s="45">
+      <c r="S6" s="41">
         <f t="shared" si="2"/>
         <v>5.1000000000000004E-2</v>
       </c>
-      <c r="T6" s="70"/>
+      <c r="T6" s="62"/>
     </row>
     <row r="7" spans="1:20" ht="16.5" customHeight="1" thickBot="1">
       <c r="A7" s="7">
         <v>5</v>
       </c>
-      <c r="B7" s="142" t="s">
+      <c r="B7" s="125" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="106" t="s">
+      <c r="C7" s="95" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="105" t="s">
-        <v>188</v>
-      </c>
-      <c r="E7" s="91" t="s">
+      <c r="D7" s="94" t="s">
+        <v>187</v>
+      </c>
+      <c r="E7" s="137" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="91" t="s">
+      <c r="F7" s="137" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="22" t="s">
+      <c r="G7" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="46" t="s">
+      <c r="I7" s="97" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7" s="22">
+      <c r="J7" s="138" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="138">
         <v>4</v>
       </c>
-      <c r="L7" s="47">
+      <c r="L7" s="140">
         <v>30</v>
       </c>
-      <c r="M7" s="46">
+      <c r="M7" s="97">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="N7" s="48" t="s">
+      <c r="N7" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="O7" s="49">
+      <c r="O7" s="141">
         <v>5.3199999999999997E-2</v>
       </c>
-      <c r="P7" s="50">
+      <c r="P7" s="142">
         <f t="shared" si="0"/>
         <v>0.21279999999999999</v>
       </c>
-      <c r="Q7" s="50">
+      <c r="Q7" s="142">
         <f t="shared" si="1"/>
         <v>1.5959999999999999</v>
       </c>
-      <c r="R7" s="49">
+      <c r="R7" s="141">
         <v>5.3199999999999997E-2</v>
       </c>
-      <c r="S7" s="37">
+      <c r="S7" s="34">
         <f t="shared" si="2"/>
         <v>1.0640000000000001</v>
       </c>
-      <c r="T7" s="68"/>
+      <c r="T7" s="60"/>
     </row>
     <row r="8" spans="1:20" ht="16.5" customHeight="1" thickBot="1">
       <c r="A8" s="7">
         <v>6</v>
       </c>
-      <c r="B8" s="143"/>
-      <c r="C8" s="84" t="s">
+      <c r="B8" s="126"/>
+      <c r="C8" s="75" t="s">
+        <v>168</v>
+      </c>
+      <c r="D8" s="76" t="s">
         <v>169</v>
       </c>
-      <c r="D8" s="85" t="s">
+      <c r="E8" s="77" t="s">
         <v>170</v>
       </c>
-      <c r="E8" s="86" t="s">
+      <c r="F8" s="77" t="s">
         <v>171</v>
       </c>
-      <c r="F8" s="86" t="s">
+      <c r="G8" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="G8" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="I8" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="15">
+      <c r="H8" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="13">
         <v>1</v>
       </c>
-      <c r="L8" s="38">
+      <c r="L8" s="35">
         <v>20</v>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="23">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N8" s="52" t="s">
+      <c r="N8" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="O8" s="40">
+      <c r="O8" s="36">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="P8" s="41">
+      <c r="P8" s="37">
         <f t="shared" si="0"/>
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="Q8" s="41">
+      <c r="Q8" s="37">
         <f t="shared" si="1"/>
         <v>0.85999999999999988</v>
       </c>
-      <c r="R8" s="40">
+      <c r="R8" s="36">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="S8" s="41">
+      <c r="S8" s="37">
         <f t="shared" si="2"/>
         <v>0.21499999999999997</v>
       </c>
-      <c r="T8" s="69"/>
+      <c r="T8" s="61"/>
     </row>
     <row r="9" spans="1:20" ht="16.5" customHeight="1" thickBot="1">
       <c r="A9" s="7">
         <v>7</v>
       </c>
-      <c r="B9" s="143"/>
-      <c r="C9" s="107" t="s">
-        <v>190</v>
-      </c>
-      <c r="D9" s="85" t="s">
+      <c r="B9" s="126"/>
+      <c r="C9" s="96" t="s">
+        <v>189</v>
+      </c>
+      <c r="D9" s="76" t="s">
+        <v>173</v>
+      </c>
+      <c r="E9" s="77" t="s">
+        <v>170</v>
+      </c>
+      <c r="F9" s="77" t="s">
         <v>174</v>
       </c>
-      <c r="E9" s="86" t="s">
-        <v>171</v>
-      </c>
-      <c r="F9" s="86" t="s">
-        <v>175</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="I9" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="K9" s="15">
+      <c r="G9" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="13">
         <v>1</v>
       </c>
-      <c r="L9" s="38">
+      <c r="L9" s="35">
         <v>10</v>
       </c>
-      <c r="M9" s="25">
+      <c r="M9" s="23">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N9" s="52" t="s">
+      <c r="N9" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="O9" s="40">
+      <c r="O9" s="36">
         <v>4.5100000000000001E-2</v>
       </c>
-      <c r="P9" s="41">
+      <c r="P9" s="37">
         <f t="shared" si="0"/>
         <v>4.5100000000000001E-2</v>
       </c>
-      <c r="Q9" s="41">
+      <c r="Q9" s="37">
         <f t="shared" si="1"/>
         <v>0.45100000000000001</v>
       </c>
-      <c r="R9" s="40">
+      <c r="R9" s="36">
         <v>4.5100000000000001E-2</v>
       </c>
-      <c r="S9" s="41">
+      <c r="S9" s="37">
         <f t="shared" si="2"/>
         <v>0.22550000000000001</v>
       </c>
-      <c r="T9" s="69"/>
+      <c r="T9" s="61"/>
     </row>
     <row r="10" spans="1:20" ht="16.5" customHeight="1" thickBot="1">
       <c r="A10" s="7">
         <v>8</v>
       </c>
-      <c r="B10" s="143"/>
-      <c r="C10" s="84" t="s">
+      <c r="B10" s="126"/>
+      <c r="C10" s="75" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" s="76" t="s">
         <v>176</v>
       </c>
-      <c r="D10" s="85" t="s">
+      <c r="E10" s="77" t="s">
+        <v>170</v>
+      </c>
+      <c r="F10" s="77" t="s">
         <v>177</v>
       </c>
-      <c r="E10" s="86" t="s">
-        <v>171</v>
-      </c>
-      <c r="F10" s="86" t="s">
-        <v>178</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="I10" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="K10" s="15">
+      <c r="G10" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" s="13">
         <v>1</v>
       </c>
-      <c r="L10" s="38">
+      <c r="L10" s="35">
         <v>10</v>
       </c>
-      <c r="M10" s="25">
+      <c r="M10" s="23">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N10" s="52" t="s">
+      <c r="N10" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="O10" s="40">
+      <c r="O10" s="36">
         <v>5.4800000000000001E-2</v>
       </c>
-      <c r="P10" s="41">
+      <c r="P10" s="37">
         <f t="shared" si="0"/>
         <v>5.4800000000000001E-2</v>
       </c>
-      <c r="Q10" s="41">
+      <c r="Q10" s="37">
         <f t="shared" si="1"/>
         <v>0.54800000000000004</v>
       </c>
-      <c r="R10" s="40">
+      <c r="R10" s="36">
         <v>5.4800000000000001E-2</v>
       </c>
-      <c r="S10" s="41">
+      <c r="S10" s="37">
         <f t="shared" si="2"/>
         <v>0.27400000000000002</v>
       </c>
-      <c r="T10" s="69"/>
+      <c r="T10" s="61"/>
     </row>
     <row r="11" spans="1:20" ht="16.5" customHeight="1" thickBot="1">
       <c r="A11" s="7">
         <v>9</v>
       </c>
-      <c r="B11" s="144"/>
-      <c r="C11" s="95" t="s">
+      <c r="B11" s="127"/>
+      <c r="C11" s="85" t="s">
+        <v>178</v>
+      </c>
+      <c r="D11" s="78" t="s">
         <v>179</v>
       </c>
-      <c r="D11" s="87" t="s">
+      <c r="E11" s="79" t="s">
+        <v>170</v>
+      </c>
+      <c r="F11" s="79" t="s">
         <v>180</v>
       </c>
-      <c r="E11" s="88" t="s">
-        <v>171</v>
-      </c>
-      <c r="F11" s="88" t="s">
-        <v>181</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="H11" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="I11" s="46" t="s">
-        <v>35</v>
-      </c>
-      <c r="J11" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="K11" s="22">
+      <c r="G11" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="H11" s="143" t="s">
+        <v>193</v>
+      </c>
+      <c r="I11" s="144" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="145" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" s="145">
         <v>1</v>
       </c>
-      <c r="L11" s="47">
+      <c r="L11" s="146">
         <v>10</v>
       </c>
-      <c r="M11" s="46">
+      <c r="M11" s="144">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N11" s="52" t="s">
+      <c r="N11" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O11" s="49">
+      <c r="O11" s="147">
         <v>7.5200000000000003E-2</v>
       </c>
-      <c r="P11" s="50">
+      <c r="P11" s="148">
         <f t="shared" si="0"/>
         <v>7.5200000000000003E-2</v>
       </c>
-      <c r="Q11" s="50">
+      <c r="Q11" s="148">
         <f t="shared" si="1"/>
         <v>0.752</v>
       </c>
-      <c r="R11" s="49">
+      <c r="R11" s="147">
         <v>7.5200000000000003E-2</v>
       </c>
-      <c r="S11" s="45">
+      <c r="S11" s="41">
         <f t="shared" si="2"/>
         <v>0.376</v>
       </c>
-      <c r="T11" s="70"/>
+      <c r="T11" s="62"/>
     </row>
     <row r="12" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A12" s="7">
         <v>10</v>
       </c>
-      <c r="B12" s="142" t="s">
+      <c r="B12" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="92" t="s">
+      <c r="C12" s="135" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="81" t="s">
+      <c r="D12" s="136" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="83" t="s">
+      <c r="E12" s="88" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="83" t="s">
+      <c r="F12" s="88" t="s">
         <v>53</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="86" t="s">
         <v>54</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="87" t="s">
         <v>55</v>
       </c>
-      <c r="I12" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="K12" s="10">
+      <c r="I12" s="86" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12" s="86" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" s="86">
         <v>1</v>
       </c>
-      <c r="L12" s="33">
+      <c r="L12" s="89">
         <v>7</v>
       </c>
-      <c r="M12" s="34">
+      <c r="M12" s="90">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N12" s="51" t="s">
+      <c r="N12" s="132" t="s">
         <v>29</v>
       </c>
-      <c r="O12" s="36">
+      <c r="O12" s="91">
         <v>0.33329999999999999</v>
       </c>
-      <c r="P12" s="37">
+      <c r="P12" s="133">
         <f t="shared" si="0"/>
         <v>0.33329999999999999</v>
       </c>
-      <c r="Q12" s="37">
+      <c r="Q12" s="133">
         <f t="shared" si="1"/>
         <v>2.3331</v>
       </c>
-      <c r="R12" s="36">
+      <c r="R12" s="91">
         <v>0.33329999999999999</v>
       </c>
-      <c r="S12" s="37">
+      <c r="S12" s="133">
         <f t="shared" si="2"/>
         <v>1.6664999999999999</v>
       </c>
-      <c r="T12" s="68"/>
+      <c r="T12" s="92"/>
     </row>
     <row r="13" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A13" s="7">
         <v>11</v>
       </c>
-      <c r="B13" s="143"/>
-      <c r="C13" s="13" t="s">
+      <c r="B13" s="126"/>
+      <c r="C13" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="85" t="s">
+      <c r="D13" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="86" t="s">
+      <c r="E13" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="86" t="s">
+      <c r="F13" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="H13" s="16" t="s">
+      <c r="H13" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="J13" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="K13" s="15">
+      <c r="I13" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="13">
         <v>2</v>
       </c>
-      <c r="L13" s="38">
+      <c r="L13" s="35">
         <v>20</v>
       </c>
-      <c r="M13" s="25">
+      <c r="M13" s="23">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="N13" s="52" t="s">
+      <c r="N13" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="O13" s="40">
+      <c r="O13" s="36">
         <v>3.39E-2</v>
       </c>
-      <c r="P13" s="41">
+      <c r="P13" s="37">
         <f t="shared" si="0"/>
         <v>6.7799999999999999E-2</v>
       </c>
-      <c r="Q13" s="41">
+      <c r="Q13" s="37">
         <f t="shared" si="1"/>
         <v>0.67799999999999994</v>
       </c>
-      <c r="R13" s="40">
+      <c r="R13" s="36">
         <v>3.39E-2</v>
       </c>
-      <c r="S13" s="41">
+      <c r="S13" s="37">
         <f t="shared" si="2"/>
         <v>0.33899999999999997</v>
       </c>
-      <c r="T13" s="69"/>
+      <c r="T13" s="61"/>
     </row>
     <row r="14" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A14" s="7">
         <v>12</v>
       </c>
-      <c r="B14" s="144"/>
-      <c r="C14" s="17" t="s">
+      <c r="B14" s="126"/>
+      <c r="C14" s="149" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="E14" s="88" t="s">
+      <c r="D14" s="150" t="s">
+        <v>188</v>
+      </c>
+      <c r="E14" s="93" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="88" t="s">
+      <c r="F14" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="151" t="s">
         <v>54</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="152" t="s">
         <v>64</v>
       </c>
-      <c r="I14" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="J14" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K14" s="19">
+      <c r="I14" s="153" t="s">
+        <v>35</v>
+      </c>
+      <c r="J14" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14" s="151">
         <v>1</v>
       </c>
-      <c r="L14" s="42">
+      <c r="L14" s="154">
         <v>10</v>
       </c>
-      <c r="M14" s="30">
+      <c r="M14" s="153">
         <f>K14*5</f>
         <v>5</v>
       </c>
-      <c r="N14" s="53" t="s">
+      <c r="N14" s="155" t="s">
         <v>29</v>
       </c>
-      <c r="O14" s="44">
+      <c r="O14" s="156">
         <v>9.8400000000000001E-2</v>
       </c>
-      <c r="P14" s="45">
+      <c r="P14" s="157">
         <f>O14*K14</f>
         <v>9.8400000000000001E-2</v>
       </c>
-      <c r="Q14" s="45">
+      <c r="Q14" s="157">
         <f>O14*L14</f>
         <v>0.98399999999999999</v>
       </c>
-      <c r="R14" s="44">
+      <c r="R14" s="156">
         <v>9.8400000000000001E-2</v>
       </c>
-      <c r="S14" s="45">
+      <c r="S14" s="157">
         <f>R14*M14</f>
         <v>0.49199999999999999</v>
       </c>
-      <c r="T14" s="70"/>
+      <c r="T14" s="158"/>
     </row>
     <row r="15" spans="1:20" ht="15.75" thickBot="1">
       <c r="A15" s="7">
         <v>13</v>
       </c>
-      <c r="B15" s="148" t="s">
+      <c r="B15" s="160" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="149" t="s">
+      <c r="C15" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="81" t="s">
+      <c r="D15" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="83" t="s">
+      <c r="E15" s="74" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="83" t="s">
+      <c r="F15" s="74" t="s">
         <v>69</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="I15" s="34" t="s">
+      <c r="I15" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="J15" s="83" t="s">
+      <c r="J15" s="74" t="s">
         <v>73</v>
       </c>
-      <c r="K15" s="24">
+      <c r="K15" s="22">
         <v>5</v>
       </c>
-      <c r="L15" s="33">
+      <c r="L15" s="31">
         <v>100</v>
       </c>
-      <c r="M15" s="34">
+      <c r="M15" s="32">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="N15" s="51" t="s">
+      <c r="N15" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="O15" s="36">
+      <c r="O15" s="33">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="P15" s="37">
+      <c r="P15" s="34">
         <f t="shared" ref="P15:P25" si="4">O15*K15</f>
         <v>5.9999999999999993E-3</v>
       </c>
-      <c r="Q15" s="37">
+      <c r="Q15" s="34">
         <f t="shared" ref="Q15:Q19" si="5">O15*L15</f>
         <v>0.12</v>
       </c>
-      <c r="R15" s="36">
+      <c r="R15" s="33">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="S15" s="37">
+      <c r="S15" s="34">
         <f t="shared" ref="S15:S19" si="6">R15*M15</f>
         <v>0.03</v>
       </c>
-      <c r="T15" s="68"/>
+      <c r="T15" s="60"/>
     </row>
     <row r="16" spans="1:20" ht="15.75" thickBot="1">
       <c r="A16" s="7">
         <v>14</v>
       </c>
-      <c r="B16" s="150"/>
-      <c r="C16" s="151" t="s">
+      <c r="B16" s="161"/>
+      <c r="C16" s="159" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="85" t="s">
+      <c r="D16" s="76" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="86" t="s">
+      <c r="F16" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="H16" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="J16" s="86" t="s">
+      <c r="H16" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="J16" s="77" t="s">
         <v>73</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="12">
         <v>1</v>
       </c>
-      <c r="L16" s="38">
+      <c r="L16" s="35">
         <v>7</v>
       </c>
-      <c r="M16" s="25">
+      <c r="M16" s="23">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N16" s="39" t="s">
+      <c r="N16" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="O16" s="41">
+      <c r="O16" s="37">
         <v>0.47620000000000001</v>
       </c>
-      <c r="P16" s="41">
+      <c r="P16" s="37">
         <f>O16*K16</f>
         <v>0.47620000000000001</v>
       </c>
-      <c r="Q16" s="41">
+      <c r="Q16" s="37">
         <f>O16*L16</f>
         <v>3.3334000000000001</v>
       </c>
-      <c r="R16" s="41">
+      <c r="R16" s="37">
         <v>0.47620000000000001</v>
       </c>
-      <c r="S16" s="41">
+      <c r="S16" s="37">
         <f>R16*M16</f>
         <v>2.3810000000000002</v>
       </c>
-      <c r="T16" s="71"/>
+      <c r="T16" s="63"/>
     </row>
     <row r="17" spans="1:20" ht="15.75" thickBot="1">
       <c r="A17" s="7">
         <v>15</v>
       </c>
-      <c r="B17" s="150"/>
-      <c r="C17" s="151" t="s">
+      <c r="B17" s="161"/>
+      <c r="C17" s="159" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="85" t="s">
+      <c r="D17" s="76" t="s">
         <v>81</v>
       </c>
-      <c r="E17" s="86" t="s">
+      <c r="E17" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="86" t="s">
+      <c r="F17" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="G17" s="15" t="s">
+      <c r="G17" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="H17" s="16" t="s">
+      <c r="H17" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="I17" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="J17" s="86" t="s">
+      <c r="I17" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="K17" s="14">
+      <c r="K17" s="12">
         <v>2</v>
       </c>
-      <c r="L17" s="54">
+      <c r="L17" s="48">
         <v>100</v>
       </c>
-      <c r="M17" s="25">
+      <c r="M17" s="23">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="N17" s="52" t="s">
+      <c r="N17" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="O17" s="40">
+      <c r="O17" s="36">
         <v>1.9E-3</v>
       </c>
-      <c r="P17" s="41">
+      <c r="P17" s="37">
         <f t="shared" si="4"/>
         <v>3.8E-3</v>
       </c>
-      <c r="Q17" s="41">
+      <c r="Q17" s="37">
         <f t="shared" si="5"/>
         <v>0.19</v>
       </c>
-      <c r="R17" s="40">
+      <c r="R17" s="36">
         <v>1.9E-3</v>
       </c>
-      <c r="S17" s="41">
+      <c r="S17" s="37">
         <f t="shared" si="6"/>
         <v>1.9E-2</v>
       </c>
-      <c r="T17" s="71"/>
+      <c r="T17" s="63"/>
     </row>
     <row r="18" spans="1:20" ht="15.75" thickBot="1">
       <c r="A18" s="7">
         <v>16</v>
       </c>
-      <c r="B18" s="150"/>
-      <c r="C18" s="152" t="s">
+      <c r="B18" s="161"/>
+      <c r="C18" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="85" t="s">
+      <c r="D18" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="E18" s="86" t="s">
+      <c r="E18" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="F18" s="86" t="s">
+      <c r="F18" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="G18" s="15" t="s">
+      <c r="G18" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="H18" s="16" t="s">
+      <c r="H18" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="I18" s="16" t="s">
+      <c r="I18" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="J18" s="86" t="s">
+      <c r="J18" s="77" t="s">
         <v>91</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="12">
         <v>1</v>
       </c>
-      <c r="L18" s="54">
+      <c r="L18" s="48">
         <v>100</v>
       </c>
-      <c r="M18" s="25">
+      <c r="M18" s="23">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N18" s="52" t="s">
+      <c r="N18" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="O18" s="40">
+      <c r="O18" s="36">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="P18" s="41">
+      <c r="P18" s="37">
         <f t="shared" si="4"/>
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="Q18" s="41">
+      <c r="Q18" s="37">
         <f t="shared" si="5"/>
         <v>0.06</v>
       </c>
-      <c r="R18" s="40">
+      <c r="R18" s="36">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="S18" s="41">
+      <c r="S18" s="37">
         <f t="shared" si="6"/>
         <v>2.9999999999999996E-3</v>
       </c>
-      <c r="T18" s="72"/>
+      <c r="T18" s="64"/>
     </row>
     <row r="19" spans="1:20" ht="15.75" thickBot="1">
       <c r="A19" s="7">
         <v>17</v>
       </c>
-      <c r="B19" s="150"/>
-      <c r="C19" s="152" t="s">
+      <c r="B19" s="161"/>
+      <c r="C19" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="D19" s="85" t="s">
+      <c r="D19" s="76" t="s">
         <v>93</v>
       </c>
-      <c r="E19" s="86" t="s">
+      <c r="E19" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="F19" s="86" t="s">
+      <c r="F19" s="77" t="s">
         <v>94</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="H19" s="25" t="s">
+      <c r="H19" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="I19" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="J19" s="86" t="s">
+      <c r="I19" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="J19" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="12">
         <v>3</v>
       </c>
-      <c r="L19" s="54">
+      <c r="L19" s="48">
         <v>100</v>
       </c>
-      <c r="M19" s="25">
+      <c r="M19" s="23">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="N19" s="52" t="s">
+      <c r="N19" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="O19" s="41">
+      <c r="O19" s="37">
         <v>1.9E-3</v>
       </c>
-      <c r="P19" s="41">
+      <c r="P19" s="37">
         <f t="shared" si="4"/>
         <v>5.7000000000000002E-3</v>
       </c>
-      <c r="Q19" s="41">
+      <c r="Q19" s="37">
         <f t="shared" si="5"/>
         <v>0.19</v>
       </c>
-      <c r="R19" s="41">
+      <c r="R19" s="37">
         <v>1.9E-3</v>
       </c>
-      <c r="S19" s="41">
+      <c r="S19" s="37">
         <f t="shared" si="6"/>
         <v>2.8500000000000001E-2</v>
       </c>
-      <c r="T19" s="73"/>
+      <c r="T19" s="65"/>
     </row>
     <row r="20" spans="1:20" ht="15.75" thickBot="1">
       <c r="A20" s="7">
         <v>18</v>
       </c>
-      <c r="B20" s="150"/>
-      <c r="C20" s="151" t="s">
+      <c r="B20" s="161"/>
+      <c r="C20" s="159" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="85" t="s">
+      <c r="D20" s="76" t="s">
         <v>98</v>
       </c>
-      <c r="E20" s="86" t="s">
+      <c r="E20" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="F20" s="86" t="s">
+      <c r="F20" s="77" t="s">
         <v>99</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="H20" s="25" t="s">
+      <c r="H20" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="I20" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="J20" s="14" t="s">
+      <c r="I20" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="J20" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="12">
         <v>1</v>
       </c>
-      <c r="L20" s="38">
+      <c r="L20" s="35">
         <v>100</v>
       </c>
-      <c r="M20" s="25">
+      <c r="M20" s="23">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N20" s="52" t="s">
+      <c r="N20" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="O20" s="41">
+      <c r="O20" s="37">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="P20" s="41">
+      <c r="P20" s="37">
         <f t="shared" si="4"/>
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q20" s="41">
+      <c r="Q20" s="37">
         <f t="shared" ref="Q20:Q25" si="7">O20*L20</f>
         <v>0.13</v>
       </c>
-      <c r="R20" s="41">
+      <c r="R20" s="37">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="S20" s="41">
+      <c r="S20" s="37">
         <f t="shared" ref="S20:S25" si="8">R20*M20</f>
         <v>6.4999999999999997E-3</v>
       </c>
-      <c r="T20" s="74"/>
+      <c r="T20" s="66"/>
     </row>
     <row r="21" spans="1:20" ht="15.75" thickBot="1">
       <c r="A21" s="7">
         <v>19</v>
       </c>
-      <c r="B21" s="150"/>
-      <c r="C21" s="151" t="s">
+      <c r="B21" s="161"/>
+      <c r="C21" s="159" t="s">
         <v>103</v>
       </c>
-      <c r="D21" s="85" t="s">
+      <c r="D21" s="76" t="s">
         <v>104</v>
       </c>
-      <c r="E21" s="86" t="s">
+      <c r="E21" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="F21" s="86" t="s">
+      <c r="F21" s="77" t="s">
         <v>105</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="H21" s="25" t="s">
+      <c r="H21" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="I21" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="J21" s="14" t="s">
+      <c r="I21" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="J21" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="K21" s="14">
+      <c r="K21" s="12">
         <v>1</v>
       </c>
-      <c r="L21" s="38">
+      <c r="L21" s="35">
         <v>100</v>
       </c>
-      <c r="M21" s="25">
+      <c r="M21" s="23">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N21" s="52" t="s">
+      <c r="N21" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="O21" s="41">
+      <c r="O21" s="37">
         <v>1.4E-3</v>
       </c>
-      <c r="P21" s="41">
+      <c r="P21" s="37">
         <f t="shared" si="4"/>
         <v>1.4E-3</v>
       </c>
-      <c r="Q21" s="41">
+      <c r="Q21" s="37">
         <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="R21" s="41">
+      <c r="R21" s="37">
         <v>1.4E-3</v>
       </c>
-      <c r="S21" s="41">
+      <c r="S21" s="37">
         <f t="shared" si="8"/>
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="T21" s="74"/>
+      <c r="T21" s="66"/>
     </row>
     <row r="22" spans="1:20" ht="15.75" thickBot="1">
       <c r="A22" s="7">
         <v>20</v>
       </c>
-      <c r="B22" s="150"/>
-      <c r="C22" s="152" t="s">
+      <c r="B22" s="161"/>
+      <c r="C22" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D22" s="85" t="s">
+      <c r="D22" s="76" t="s">
         <v>110</v>
       </c>
-      <c r="E22" s="86" t="s">
+      <c r="E22" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="86" t="s">
+      <c r="F22" s="77" t="s">
         <v>111</v>
       </c>
-      <c r="G22" s="15" t="s">
+      <c r="G22" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="H22" s="16" t="s">
+      <c r="H22" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="I22" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="J22" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="K22" s="14">
+      <c r="I22" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="K22" s="12">
         <v>1</v>
       </c>
-      <c r="L22" s="38">
+      <c r="L22" s="35">
         <v>100</v>
       </c>
-      <c r="M22" s="25">
+      <c r="M22" s="23">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N22" s="39" t="s">
+      <c r="N22" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="O22" s="41">
+      <c r="O22" s="37">
         <v>1.8E-3</v>
       </c>
-      <c r="P22" s="41">
+      <c r="P22" s="37">
         <f t="shared" si="4"/>
         <v>1.8E-3</v>
       </c>
-      <c r="Q22" s="41">
+      <c r="Q22" s="37">
         <f t="shared" si="7"/>
         <v>0.18</v>
       </c>
-      <c r="R22" s="41">
+      <c r="R22" s="37">
         <v>1.8E-3</v>
       </c>
-      <c r="S22" s="41">
+      <c r="S22" s="37">
         <f t="shared" si="8"/>
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="T22" s="75"/>
+      <c r="T22" s="67"/>
     </row>
     <row r="23" spans="1:20" ht="15.75" thickBot="1">
       <c r="A23" s="7">
         <v>21</v>
       </c>
-      <c r="B23" s="150"/>
-      <c r="C23" s="151" t="s">
+      <c r="B23" s="161"/>
+      <c r="C23" s="159" t="s">
         <v>113</v>
       </c>
-      <c r="D23" s="85" t="s">
+      <c r="D23" s="76" t="s">
         <v>114</v>
       </c>
-      <c r="E23" s="86" t="s">
+      <c r="E23" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="86" t="s">
+      <c r="F23" s="77" t="s">
         <v>115</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="H23" s="16" t="s">
+      <c r="H23" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="I23" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="J23" s="14" t="s">
+      <c r="I23" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="J23" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K23" s="14">
+      <c r="K23" s="12">
         <v>1</v>
       </c>
-      <c r="L23" s="38">
+      <c r="L23" s="35">
         <v>100</v>
       </c>
-      <c r="M23" s="25">
+      <c r="M23" s="23">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N23" s="39" t="s">
+      <c r="N23" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="O23" s="41">
+      <c r="O23" s="37">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="P23" s="41">
+      <c r="P23" s="37">
         <f t="shared" si="4"/>
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="Q23" s="41">
+      <c r="Q23" s="37">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
-      <c r="R23" s="41">
+      <c r="R23" s="37">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="S23" s="41">
+      <c r="S23" s="37">
         <f t="shared" si="8"/>
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="T23" s="76"/>
+      <c r="T23" s="68"/>
     </row>
     <row r="24" spans="1:20" ht="15.75" thickBot="1">
       <c r="A24" s="7">
         <v>22</v>
       </c>
-      <c r="B24" s="153"/>
-      <c r="C24" s="154" t="s">
+      <c r="B24" s="162"/>
+      <c r="C24" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D24" s="87" t="s">
+      <c r="D24" s="78" t="s">
         <v>119</v>
       </c>
-      <c r="E24" s="88" t="s">
+      <c r="E24" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="F24" s="88" t="s">
+      <c r="F24" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="G24" s="19" t="s">
+      <c r="G24" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="H24" s="20" t="s">
+      <c r="H24" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="I24" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="J24" s="18" t="s">
+      <c r="I24" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="J24" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="K24" s="18">
+      <c r="K24" s="16">
         <v>4</v>
       </c>
-      <c r="L24" s="42">
+      <c r="L24" s="38">
         <v>100</v>
       </c>
-      <c r="M24" s="30">
+      <c r="M24" s="28">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="N24" s="53" t="s">
+      <c r="N24" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O24" s="45">
+      <c r="O24" s="41">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="P24" s="45">
+      <c r="P24" s="41">
         <f t="shared" si="4"/>
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="Q24" s="45">
+      <c r="Q24" s="41">
         <f t="shared" si="7"/>
         <v>0.11</v>
       </c>
-      <c r="R24" s="45">
+      <c r="R24" s="41">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="S24" s="45">
+      <c r="S24" s="41">
         <f t="shared" si="8"/>
         <v>2.2000000000000002E-2</v>
       </c>
-      <c r="T24" s="77"/>
+      <c r="T24" s="69"/>
     </row>
     <row r="25" spans="1:20" ht="16.5" thickBot="1">
       <c r="A25" s="7">
         <v>23</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="117" t="s">
         <v>123</v>
       </c>
-      <c r="C25" s="89" t="s">
+      <c r="C25" s="80" t="s">
         <v>124</v>
       </c>
-      <c r="D25" s="90" t="s">
+      <c r="D25" s="81" t="s">
         <v>125</v>
       </c>
-      <c r="E25" s="21" t="s">
+      <c r="E25" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="F25" s="91" t="s">
+      <c r="F25" s="82" t="s">
         <v>126</v>
       </c>
-      <c r="G25" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="H25" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="I25" s="46" t="s">
-        <v>35</v>
-      </c>
-      <c r="J25" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="K25" s="22">
+      <c r="G25" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="H25" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="K25" s="20">
         <v>1</v>
       </c>
-      <c r="L25" s="47">
+      <c r="L25" s="43">
         <v>7</v>
       </c>
-      <c r="M25" s="46">
+      <c r="M25" s="42">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N25" s="55" t="s">
+      <c r="N25" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="O25" s="50">
+      <c r="O25" s="45">
         <v>0.318</v>
       </c>
-      <c r="P25" s="50">
+      <c r="P25" s="45">
         <f t="shared" si="4"/>
         <v>0.318</v>
       </c>
-      <c r="Q25" s="50">
+      <c r="Q25" s="45">
         <f t="shared" si="7"/>
         <v>2.226</v>
       </c>
-      <c r="R25" s="50">
+      <c r="R25" s="45">
         <v>0.318</v>
       </c>
-      <c r="S25" s="50">
+      <c r="S25" s="45">
         <f t="shared" si="8"/>
         <v>1.59</v>
       </c>
-      <c r="T25" s="78"/>
+      <c r="T25" s="70"/>
     </row>
     <row r="26" spans="1:20" ht="16.5" thickBot="1">
       <c r="A26" s="7">
         <v>24</v>
       </c>
-      <c r="B26" s="26" t="s">
+      <c r="B26" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="93" t="s">
+      <c r="C26" s="83" t="s">
         <v>128</v>
       </c>
-      <c r="D26" s="94" t="s">
+      <c r="D26" s="84" t="s">
         <v>129</v>
       </c>
-      <c r="E26" s="27" t="s">
+      <c r="E26" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="F26" s="94" t="s">
+      <c r="F26" s="84" t="s">
         <v>130</v>
       </c>
-      <c r="G26" s="28" t="s">
+      <c r="G26" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="H26" s="29" t="s">
+      <c r="H26" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="I26" s="56" t="s">
-        <v>35</v>
-      </c>
-      <c r="J26" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="K26" s="28">
+      <c r="I26" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="J26" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="K26" s="26">
         <v>2</v>
       </c>
-      <c r="L26" s="56">
+      <c r="L26" s="49">
         <v>12</v>
       </c>
-      <c r="M26" s="56">
+      <c r="M26" s="49">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="N26" s="132" t="s">
-        <v>199</v>
-      </c>
-      <c r="O26" s="57">
+      <c r="N26" s="169" t="s">
+        <v>196</v>
+      </c>
+      <c r="O26" s="50">
         <v>0.49941000000000002</v>
       </c>
-      <c r="P26" s="58">
+      <c r="P26" s="51">
         <f t="shared" ref="P26:P31" si="9">O26*K26</f>
         <v>0.99882000000000004</v>
       </c>
-      <c r="Q26" s="58">
+      <c r="Q26" s="51">
         <f t="shared" ref="Q26:Q31" si="10">O26*L26</f>
         <v>5.9929199999999998</v>
       </c>
-      <c r="R26" s="58">
+      <c r="R26" s="51">
         <v>0.55489999999999995</v>
       </c>
-      <c r="S26" s="58">
+      <c r="S26" s="51">
         <f t="shared" ref="S26:S31" si="11">R26*M26</f>
         <v>5.5489999999999995</v>
       </c>
-      <c r="T26" s="110" t="s">
-        <v>197</v>
+      <c r="T26" s="98" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A27" s="7">
         <v>25</v>
       </c>
-      <c r="B27" s="142" t="s">
+      <c r="B27" s="125" t="s">
         <v>133</v>
       </c>
-      <c r="C27" s="92" t="s">
+      <c r="C27" s="130" t="s">
+        <v>200</v>
+      </c>
+      <c r="D27" s="74" t="s">
         <v>134</v>
       </c>
-      <c r="D27" s="83" t="s">
+      <c r="E27" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="G27" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="E27" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="F27" s="83" t="s">
-        <v>191</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="H27" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="I27" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="J27" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="K27" s="24">
+      <c r="H27" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="I27" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="J27" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="K27" s="22">
         <v>1</v>
       </c>
-      <c r="L27" s="59">
+      <c r="L27" s="52">
         <v>6</v>
       </c>
-      <c r="M27" s="34">
+      <c r="M27" s="32">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N27" s="134" t="s">
-        <v>201</v>
-      </c>
-      <c r="O27" s="37">
-        <v>2.88</v>
-      </c>
-      <c r="P27" s="37">
+      <c r="N27" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="O27" s="34">
+        <v>2.9754999999999998</v>
+      </c>
+      <c r="P27" s="34">
         <f t="shared" si="9"/>
-        <v>2.88</v>
-      </c>
-      <c r="Q27" s="37">
+        <v>2.9754999999999998</v>
+      </c>
+      <c r="Q27" s="34">
         <f t="shared" si="10"/>
-        <v>17.28</v>
-      </c>
-      <c r="R27" s="37">
-        <v>2.88</v>
-      </c>
-      <c r="S27" s="37">
+        <v>17.852999999999998</v>
+      </c>
+      <c r="R27" s="34">
+        <v>2.9754999999999998</v>
+      </c>
+      <c r="S27" s="34">
         <f t="shared" si="11"/>
-        <v>14.399999999999999</v>
-      </c>
-      <c r="T27" s="111" t="s">
-        <v>197</v>
-      </c>
+        <v>14.8775</v>
+      </c>
+      <c r="T27" s="131"/>
     </row>
     <row r="28" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A28" s="7">
         <v>26</v>
       </c>
-      <c r="B28" s="143"/>
-      <c r="C28" s="13" t="s">
+      <c r="B28" s="126"/>
+      <c r="C28" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D28" s="77" t="s">
         <v>137</v>
       </c>
-      <c r="D28" s="86" t="s">
+      <c r="E28" s="77" t="s">
         <v>138</v>
       </c>
-      <c r="E28" s="86" t="s">
+      <c r="F28" s="77" t="s">
         <v>139</v>
       </c>
-      <c r="F28" s="86" t="s">
+      <c r="G28" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="G28" s="15" t="s">
+      <c r="H28" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="H28" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="I28" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="J28" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="K28" s="14">
+      <c r="I28" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="J28" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="K28" s="12">
         <v>1</v>
       </c>
-      <c r="L28" s="60">
+      <c r="L28" s="53">
         <v>6</v>
       </c>
-      <c r="M28" s="25">
+      <c r="M28" s="23">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N28" s="39" t="s">
+      <c r="N28" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="O28" s="41">
+      <c r="O28" s="37">
         <v>0.25119999999999998</v>
       </c>
-      <c r="P28" s="41">
+      <c r="P28" s="37">
         <f t="shared" si="9"/>
         <v>0.25119999999999998</v>
       </c>
-      <c r="Q28" s="41">
+      <c r="Q28" s="37">
         <f t="shared" si="10"/>
         <v>1.5071999999999999</v>
       </c>
-      <c r="R28" s="41">
+      <c r="R28" s="37">
         <v>0.25119999999999998</v>
       </c>
-      <c r="S28" s="41">
+      <c r="S28" s="37">
         <f t="shared" si="11"/>
         <v>1.2559999999999998</v>
       </c>
-      <c r="T28" s="113"/>
+      <c r="T28" s="167"/>
     </row>
     <row r="29" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A29" s="7">
         <v>27</v>
       </c>
-      <c r="B29" s="143"/>
-      <c r="C29" s="13" t="s">
+      <c r="B29" s="126"/>
+      <c r="C29" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D29" s="77" t="s">
         <v>143</v>
       </c>
-      <c r="D29" s="86" t="s">
+      <c r="E29" s="77" t="s">
         <v>144</v>
       </c>
-      <c r="E29" s="86" t="s">
+      <c r="F29" s="77" t="s">
         <v>145</v>
       </c>
-      <c r="F29" s="86" t="s">
+      <c r="G29" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="G29" s="15" t="s">
+      <c r="H29" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="H29" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="I29" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="J29" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="K29" s="14">
+      <c r="I29" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="J29" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="K29" s="12">
         <v>1</v>
       </c>
-      <c r="L29" s="60">
+      <c r="L29" s="53">
         <v>6</v>
       </c>
-      <c r="M29" s="25">
+      <c r="M29" s="23">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N29" s="133" t="s">
-        <v>200</v>
-      </c>
-      <c r="O29" s="41">
+      <c r="N29" s="47" t="s">
+        <v>197</v>
+      </c>
+      <c r="O29" s="37">
         <v>0.99</v>
       </c>
-      <c r="P29" s="41">
+      <c r="P29" s="37">
         <f t="shared" si="9"/>
         <v>0.99</v>
       </c>
-      <c r="Q29" s="41">
+      <c r="Q29" s="37">
         <f t="shared" si="10"/>
         <v>5.9399999999999995</v>
       </c>
-      <c r="R29" s="41">
+      <c r="R29" s="37">
         <v>0.99</v>
       </c>
-      <c r="S29" s="41">
+      <c r="S29" s="37">
         <f t="shared" si="11"/>
         <v>4.95</v>
       </c>
-      <c r="T29" s="114" t="s">
-        <v>197</v>
+      <c r="T29" s="168" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A30" s="7">
         <v>28</v>
       </c>
-      <c r="B30" s="144"/>
-      <c r="C30" s="95" t="s">
+      <c r="B30" s="127"/>
+      <c r="C30" s="85" t="s">
+        <v>148</v>
+      </c>
+      <c r="D30" s="79" t="s">
         <v>149</v>
       </c>
-      <c r="D30" s="88" t="s">
+      <c r="E30" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="E30" s="18" t="s">
+      <c r="F30" s="79" t="s">
         <v>151</v>
       </c>
-      <c r="F30" s="88" t="s">
+      <c r="G30" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="G30" s="19" t="s">
+      <c r="H30" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="H30" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="I30" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="J30" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K30" s="18">
+      <c r="I30" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="J30" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="K30" s="16">
         <v>1</v>
       </c>
-      <c r="L30" s="61">
+      <c r="L30" s="54">
         <v>6</v>
       </c>
-      <c r="M30" s="30">
+      <c r="M30" s="28">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N30" s="53" t="s">
+      <c r="N30" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O30" s="45">
+      <c r="O30" s="41">
         <v>3.1053000000000002</v>
       </c>
-      <c r="P30" s="45">
+      <c r="P30" s="41">
         <f t="shared" si="9"/>
         <v>3.1053000000000002</v>
       </c>
-      <c r="Q30" s="45">
+      <c r="Q30" s="41">
         <f t="shared" si="10"/>
         <v>18.631800000000002</v>
       </c>
-      <c r="R30" s="80">
+      <c r="R30" s="71">
         <v>3.1053000000000002</v>
       </c>
-      <c r="S30" s="45">
+      <c r="S30" s="41">
         <f t="shared" si="11"/>
         <v>15.5265</v>
       </c>
-      <c r="T30" s="112" t="s">
-        <v>197</v>
+      <c r="T30" s="99" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A31" s="7">
         <v>29</v>
       </c>
-      <c r="B31" s="145" t="s">
+      <c r="B31" s="128" t="s">
+        <v>154</v>
+      </c>
+      <c r="C31" s="135" t="s">
         <v>155</v>
       </c>
-      <c r="C31" s="92" t="s">
+      <c r="D31" s="88" t="s">
         <v>156</v>
       </c>
-      <c r="D31" s="83" t="s">
+      <c r="E31" s="163" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" s="88" t="s">
         <v>157</v>
       </c>
-      <c r="E31" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="F31" s="83" t="s">
+      <c r="G31" s="86" t="s">
         <v>158</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="H31" s="87" t="s">
         <v>159</v>
       </c>
-      <c r="H31" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="I31" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="J31" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="K31" s="9">
+      <c r="I31" s="90" t="s">
+        <v>35</v>
+      </c>
+      <c r="J31" s="86" t="s">
+        <v>35</v>
+      </c>
+      <c r="K31" s="164">
         <v>1</v>
       </c>
-      <c r="L31" s="62">
+      <c r="L31" s="165">
         <v>7</v>
       </c>
-      <c r="M31" s="34">
+      <c r="M31" s="90">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N31" s="35" t="s">
+      <c r="N31" s="132" t="s">
         <v>29</v>
       </c>
-      <c r="O31" s="37">
+      <c r="O31" s="133">
         <v>0.22420000000000001</v>
       </c>
-      <c r="P31" s="37">
+      <c r="P31" s="133">
         <f t="shared" si="9"/>
         <v>0.22420000000000001</v>
       </c>
-      <c r="Q31" s="37">
+      <c r="Q31" s="133">
         <f t="shared" si="10"/>
         <v>1.5694000000000001</v>
       </c>
-      <c r="R31" s="37">
+      <c r="R31" s="133">
         <v>0.22420000000000001</v>
       </c>
-      <c r="S31" s="37">
+      <c r="S31" s="133">
         <f t="shared" si="11"/>
         <v>1.121</v>
       </c>
-      <c r="T31" s="79"/>
+      <c r="T31" s="166"/>
     </row>
     <row r="32" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A32" s="7">
         <v>30</v>
       </c>
-      <c r="B32" s="146"/>
-      <c r="C32" s="115" t="s">
+      <c r="B32" s="128"/>
+      <c r="C32" s="100" t="s">
+        <v>160</v>
+      </c>
+      <c r="D32" s="101" t="s">
         <v>161</v>
       </c>
-      <c r="D32" s="116" t="s">
+      <c r="E32" s="101" t="s">
+        <v>76</v>
+      </c>
+      <c r="F32" s="104" t="s">
         <v>162</v>
       </c>
-      <c r="E32" s="116" t="s">
-        <v>76</v>
-      </c>
-      <c r="F32" s="119" t="s">
-        <v>163</v>
-      </c>
-      <c r="G32" s="121" t="s">
-        <v>35</v>
-      </c>
-      <c r="H32" s="121" t="s">
-        <v>35</v>
-      </c>
-      <c r="I32" s="121" t="s">
-        <v>35</v>
-      </c>
-      <c r="J32" s="121" t="s">
-        <v>35</v>
-      </c>
-      <c r="K32" s="121">
+      <c r="G32" s="106" t="s">
+        <v>35</v>
+      </c>
+      <c r="H32" s="106" t="s">
+        <v>35</v>
+      </c>
+      <c r="I32" s="106" t="s">
+        <v>35</v>
+      </c>
+      <c r="J32" s="106" t="s">
+        <v>35</v>
+      </c>
+      <c r="K32" s="106">
         <v>1</v>
       </c>
-      <c r="L32" s="121" t="s">
-        <v>35</v>
-      </c>
-      <c r="M32" s="122">
+      <c r="L32" s="106" t="s">
+        <v>35</v>
+      </c>
+      <c r="M32" s="107">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N32" s="123" t="s">
-        <v>35</v>
-      </c>
-      <c r="O32" s="124" t="s">
-        <v>35</v>
-      </c>
-      <c r="P32" s="124" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q32" s="124" t="s">
-        <v>35</v>
-      </c>
-      <c r="R32" s="124" t="s">
-        <v>35</v>
-      </c>
-      <c r="S32" s="124" t="s">
-        <v>35</v>
-      </c>
-      <c r="T32" s="125" t="s">
-        <v>202</v>
+      <c r="N32" s="108" t="s">
+        <v>35</v>
+      </c>
+      <c r="O32" s="109" t="s">
+        <v>35</v>
+      </c>
+      <c r="P32" s="109" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q32" s="109" t="s">
+        <v>35</v>
+      </c>
+      <c r="R32" s="109" t="s">
+        <v>35</v>
+      </c>
+      <c r="S32" s="109" t="s">
+        <v>35</v>
+      </c>
+      <c r="T32" s="110" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="33" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A33" s="7">
         <v>31</v>
       </c>
-      <c r="B33" s="147"/>
-      <c r="C33" s="117" t="s">
+      <c r="B33" s="129"/>
+      <c r="C33" s="102" t="s">
+        <v>163</v>
+      </c>
+      <c r="D33" s="103" t="s">
         <v>164</v>
       </c>
-      <c r="D33" s="118" t="s">
+      <c r="E33" s="103" t="s">
+        <v>76</v>
+      </c>
+      <c r="F33" s="105" t="s">
         <v>165</v>
       </c>
-      <c r="E33" s="118" t="s">
-        <v>76</v>
-      </c>
-      <c r="F33" s="120" t="s">
-        <v>166</v>
-      </c>
-      <c r="G33" s="126" t="s">
-        <v>35</v>
-      </c>
-      <c r="H33" s="127" t="s">
-        <v>35</v>
-      </c>
-      <c r="I33" s="127" t="s">
-        <v>35</v>
-      </c>
-      <c r="J33" s="127" t="s">
-        <v>35</v>
-      </c>
-      <c r="K33" s="127">
+      <c r="G33" s="111" t="s">
+        <v>35</v>
+      </c>
+      <c r="H33" s="112" t="s">
+        <v>35</v>
+      </c>
+      <c r="I33" s="112" t="s">
+        <v>35</v>
+      </c>
+      <c r="J33" s="112" t="s">
+        <v>35</v>
+      </c>
+      <c r="K33" s="112">
         <v>5</v>
       </c>
-      <c r="L33" s="127" t="s">
-        <v>35</v>
-      </c>
-      <c r="M33" s="128">
+      <c r="L33" s="112" t="s">
+        <v>35</v>
+      </c>
+      <c r="M33" s="113">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="N33" s="129" t="s">
-        <v>35</v>
-      </c>
-      <c r="O33" s="130" t="s">
-        <v>35</v>
-      </c>
-      <c r="P33" s="130" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q33" s="130" t="s">
-        <v>35</v>
-      </c>
-      <c r="R33" s="130" t="s">
-        <v>35</v>
-      </c>
-      <c r="S33" s="130" t="s">
-        <v>35</v>
-      </c>
-      <c r="T33" s="131" t="s">
-        <v>202</v>
+      <c r="N33" s="114" t="s">
+        <v>35</v>
+      </c>
+      <c r="O33" s="115" t="s">
+        <v>35</v>
+      </c>
+      <c r="P33" s="115" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q33" s="115" t="s">
+        <v>35</v>
+      </c>
+      <c r="R33" s="115" t="s">
+        <v>35</v>
+      </c>
+      <c r="S33" s="115" t="s">
+        <v>35</v>
+      </c>
+      <c r="T33" s="116" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="34" spans="1:20" ht="19.5" thickBot="1">
-      <c r="K34" s="140" t="s">
-        <v>167</v>
-      </c>
-      <c r="L34" s="140"/>
-      <c r="M34" s="140"/>
-      <c r="N34" s="140"/>
-      <c r="O34" s="63">
+      <c r="K34" s="123" t="s">
+        <v>166</v>
+      </c>
+      <c r="L34" s="123"/>
+      <c r="M34" s="123"/>
+      <c r="N34" s="123"/>
+      <c r="O34" s="55">
         <f>SUM(O3:O31)</f>
-        <v>9.765410000000001</v>
-      </c>
-      <c r="P34" s="64"/>
-      <c r="Q34" s="63">
+        <v>9.8609100000000005</v>
+      </c>
+      <c r="P34" s="56"/>
+      <c r="Q34" s="55">
         <f>SUM(Q3:Q31)</f>
-        <v>69.239220000000003</v>
+        <v>69.812219999999996</v>
       </c>
     </row>
     <row r="35" spans="1:20" ht="18.75">
-      <c r="K35" s="141" t="s">
-        <v>168</v>
-      </c>
-      <c r="L35" s="141"/>
-      <c r="M35" s="141"/>
-      <c r="N35" s="141"/>
-      <c r="O35" s="65">
+      <c r="K35" s="124" t="s">
+        <v>167</v>
+      </c>
+      <c r="L35" s="124"/>
+      <c r="M35" s="124"/>
+      <c r="N35" s="124"/>
+      <c r="O35" s="57">
         <f>SUM(O33:O34)</f>
-        <v>9.765410000000001</v>
-      </c>
-      <c r="P35" s="64"/>
-      <c r="Q35" s="65">
+        <v>9.8609100000000005</v>
+      </c>
+      <c r="P35" s="56"/>
+      <c r="Q35" s="57">
         <f>Q34/5</f>
-        <v>13.847844</v>
+        <v>13.962444</v>
       </c>
     </row>
   </sheetData>
@@ -4609,33 +4666,33 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="N6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="N7" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="N12" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="N15" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="N17" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="N19" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="N18" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="N28" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="N31" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="N3" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="N5" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="N13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="N14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="N22" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="N24" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="N20" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="N21" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="N23" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="N30" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="N4" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="N8" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="N9" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="N10" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="N11" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="N26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="N27" r:id="rId26" xr:uid="{3A02A36A-76E7-4940-9597-3F3FE3538FCB}"/>
-    <hyperlink ref="N29" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="N6" r:id="rId1"/>
+    <hyperlink ref="N7" r:id="rId2"/>
+    <hyperlink ref="N12" r:id="rId3"/>
+    <hyperlink ref="N15" r:id="rId4"/>
+    <hyperlink ref="N17" r:id="rId5"/>
+    <hyperlink ref="N19" r:id="rId6"/>
+    <hyperlink ref="N18" r:id="rId7"/>
+    <hyperlink ref="N28" r:id="rId8"/>
+    <hyperlink ref="N31" r:id="rId9"/>
+    <hyperlink ref="N3" r:id="rId10"/>
+    <hyperlink ref="N5" r:id="rId11"/>
+    <hyperlink ref="N13" r:id="rId12"/>
+    <hyperlink ref="N14" r:id="rId13"/>
+    <hyperlink ref="N22" r:id="rId14"/>
+    <hyperlink ref="N24" r:id="rId15"/>
+    <hyperlink ref="N20" r:id="rId16"/>
+    <hyperlink ref="N21" r:id="rId17"/>
+    <hyperlink ref="N23" r:id="rId18"/>
+    <hyperlink ref="N30" r:id="rId19"/>
+    <hyperlink ref="N4" r:id="rId20"/>
+    <hyperlink ref="N8" r:id="rId21"/>
+    <hyperlink ref="N9" r:id="rId22"/>
+    <hyperlink ref="N10" r:id="rId23"/>
+    <hyperlink ref="N11" r:id="rId24"/>
+    <hyperlink ref="N26" r:id="rId25"/>
+    <hyperlink ref="N29" r:id="rId26"/>
+    <hyperlink ref="N27" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId28"/>

--- a/Hardware-Designing/Deliverables/BOM/LCSC BOM.xlsx
+++ b/Hardware-Designing/Deliverables/BOM/LCSC BOM.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="202">
   <si>
     <t>Bill of Material (BOM) for  Martin Transmitter</t>
   </si>
@@ -643,9 +643,6 @@
     <t>Non Stock in LCSC</t>
   </si>
   <si>
-    <t>Utsource</t>
-  </si>
-  <si>
     <t>Chipsfind</t>
   </si>
   <si>
@@ -661,6 +658,9 @@
   <si>
     <t xml:space="preserve">C967026
 </t>
+  </si>
+  <si>
+    <t>Chipmall</t>
   </si>
 </sst>
 </file>
@@ -672,7 +672,7 @@
     <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.0000"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -792,6 +792,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -825,7 +833,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -1174,17 +1182,6 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1314,19 +1311,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -1379,7 +1363,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1435,15 +1419,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1453,9 +1428,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1504,18 +1476,6 @@
     <xf numFmtId="164" fontId="7" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1538,9 +1498,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1576,10 +1533,6 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1604,46 +1557,31 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1652,16 +1590,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1688,34 +1626,108 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1739,6 +1751,15 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1754,121 +1775,146 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="31" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2170,28 +2216,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="16.5" thickBot="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="128" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="122"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
+      <c r="L1" s="130"/>
+      <c r="M1" s="130"/>
+      <c r="N1" s="130"/>
+      <c r="O1" s="130"/>
+      <c r="P1" s="130"/>
+      <c r="Q1" s="131"/>
+      <c r="R1" s="132"/>
       <c r="S1" s="3"/>
-      <c r="T1" s="58"/>
+      <c r="T1" s="49"/>
     </row>
     <row r="2" spans="1:20" ht="16.5" thickBot="1">
       <c r="A2" s="4" t="s">
@@ -2233,7 +2279,7 @@
       <c r="M2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="29" t="s">
+      <c r="N2" s="25" t="s">
         <v>14</v>
       </c>
       <c r="O2" s="6" t="s">
@@ -2248,7 +2294,7 @@
       <c r="R2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="59" t="s">
+      <c r="S2" s="50" t="s">
         <v>19</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -2259,19 +2305,19 @@
       <c r="A3" s="7">
         <v>1</v>
       </c>
-      <c r="B3" s="125" t="s">
+      <c r="B3" s="138" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="134" t="s">
+      <c r="D3" s="106" t="s">
         <v>184</v>
       </c>
-      <c r="E3" s="73" t="s">
+      <c r="E3" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="73" t="s">
+      <c r="F3" s="144" t="s">
         <v>24</v>
       </c>
       <c r="G3" s="9" t="s">
@@ -2280,122 +2326,122 @@
       <c r="H3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="30" t="s">
+      <c r="I3" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="74" t="s">
+      <c r="J3" s="63" t="s">
         <v>28</v>
       </c>
       <c r="K3" s="9">
         <v>6</v>
       </c>
-      <c r="L3" s="31">
+      <c r="L3" s="27">
         <v>50</v>
       </c>
-      <c r="M3" s="97">
+      <c r="M3" s="81">
         <f>K3*5</f>
         <v>30</v>
       </c>
-      <c r="N3" s="46" t="s">
+      <c r="N3" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="33">
-        <v>9.4999999999999998E-3</v>
-      </c>
-      <c r="P3" s="34">
+      <c r="O3" s="29">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="P3" s="30">
         <f t="shared" ref="P3:P13" si="0">O3*K3</f>
-        <v>5.6999999999999995E-2</v>
-      </c>
-      <c r="Q3" s="34">
+        <v>5.5199999999999999E-2</v>
+      </c>
+      <c r="Q3" s="30">
         <f t="shared" ref="Q3:Q13" si="1">O3*L3</f>
-        <v>0.47499999999999998</v>
-      </c>
-      <c r="R3" s="33">
-        <v>9.4999999999999998E-3</v>
-      </c>
-      <c r="S3" s="34">
+        <v>0.45999999999999996</v>
+      </c>
+      <c r="R3" s="29">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="S3" s="30">
         <f t="shared" ref="S3:S13" si="2">R3*M3</f>
-        <v>0.28499999999999998</v>
-      </c>
-      <c r="T3" s="60"/>
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="T3" s="51"/>
     </row>
     <row r="4" spans="1:20" ht="15.75" thickBot="1">
       <c r="A4" s="7">
         <v>2</v>
       </c>
-      <c r="B4" s="126"/>
-      <c r="C4" s="75" t="s">
+      <c r="B4" s="139"/>
+      <c r="C4" s="64" t="s">
         <v>181</v>
       </c>
-      <c r="D4" s="76" t="s">
+      <c r="D4" s="65" t="s">
         <v>182</v>
       </c>
-      <c r="E4" s="77" t="s">
+      <c r="E4" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="93" t="s">
+      <c r="F4" s="77" t="s">
         <v>183</v>
       </c>
       <c r="G4" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="87" t="s">
+      <c r="H4" s="71" t="s">
         <v>185</v>
       </c>
-      <c r="I4" s="90" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="88" t="s">
+      <c r="I4" s="74" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="72" t="s">
         <v>186</v>
       </c>
-      <c r="K4" s="86">
+      <c r="K4" s="70">
         <v>1</v>
       </c>
-      <c r="L4" s="89">
+      <c r="L4" s="73">
         <v>7</v>
       </c>
-      <c r="M4" s="23">
+      <c r="M4" s="20">
         <f>K4*5</f>
         <v>5</v>
       </c>
-      <c r="N4" s="47" t="s">
+      <c r="N4" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O4" s="91">
+      <c r="O4" s="75">
         <v>0.19919999999999999</v>
       </c>
-      <c r="P4" s="34">
+      <c r="P4" s="30">
         <f t="shared" si="0"/>
         <v>0.19919999999999999</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="30">
         <f t="shared" si="1"/>
         <v>1.3943999999999999</v>
       </c>
-      <c r="R4" s="91">
+      <c r="R4" s="75">
         <v>0.19919999999999999</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="30">
         <f t="shared" si="2"/>
         <v>0.996</v>
       </c>
-      <c r="T4" s="92"/>
+      <c r="T4" s="76"/>
     </row>
     <row r="5" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A5" s="7">
         <v>3</v>
       </c>
-      <c r="B5" s="126"/>
-      <c r="C5" s="75" t="s">
+      <c r="B5" s="139"/>
+      <c r="C5" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="76" t="s">
+      <c r="D5" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="77" t="s">
+      <c r="E5" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="77" t="s">
+      <c r="F5" s="66" t="s">
         <v>32</v>
       </c>
       <c r="G5" s="13" t="s">
@@ -2404,7 +2450,7 @@
       <c r="H5" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="20" t="s">
         <v>35</v>
       </c>
       <c r="J5" s="12" t="s">
@@ -2413,51 +2459,51 @@
       <c r="K5" s="13">
         <v>2</v>
       </c>
-      <c r="L5" s="35">
+      <c r="L5" s="31">
         <v>20</v>
       </c>
-      <c r="M5" s="23">
+      <c r="M5" s="20">
         <f t="shared" ref="M5:M33" si="3">K5*5</f>
         <v>10</v>
       </c>
-      <c r="N5" s="47" t="s">
+      <c r="N5" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O5" s="36">
-        <v>5.7599999999999998E-2</v>
-      </c>
-      <c r="P5" s="37">
+      <c r="O5" s="32">
+        <v>5.9299999999999999E-2</v>
+      </c>
+      <c r="P5" s="33">
         <f t="shared" si="0"/>
-        <v>0.1152</v>
-      </c>
-      <c r="Q5" s="37">
+        <v>0.1186</v>
+      </c>
+      <c r="Q5" s="33">
         <f t="shared" si="1"/>
-        <v>1.1519999999999999</v>
-      </c>
-      <c r="R5" s="36">
-        <v>5.7599999999999998E-2</v>
-      </c>
-      <c r="S5" s="37">
+        <v>1.1859999999999999</v>
+      </c>
+      <c r="R5" s="32">
+        <v>5.9299999999999999E-2</v>
+      </c>
+      <c r="S5" s="33">
         <f t="shared" si="2"/>
-        <v>0.57599999999999996</v>
-      </c>
-      <c r="T5" s="61"/>
+        <v>0.59299999999999997</v>
+      </c>
+      <c r="T5" s="52"/>
     </row>
     <row r="6" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A6" s="7">
         <v>4</v>
       </c>
-      <c r="B6" s="127"/>
+      <c r="B6" s="140"/>
       <c r="C6" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="79" t="s">
+      <c r="E6" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="79" t="s">
+      <c r="F6" s="68" t="s">
         <v>39</v>
       </c>
       <c r="G6" s="17" t="s">
@@ -2466,124 +2512,124 @@
       <c r="H6" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" s="79" t="s">
+      <c r="I6" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="68" t="s">
         <v>41</v>
       </c>
       <c r="K6" s="17">
         <v>2</v>
       </c>
-      <c r="L6" s="38">
+      <c r="L6" s="34">
         <v>50</v>
       </c>
-      <c r="M6" s="28">
+      <c r="M6" s="24">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="N6" s="39" t="s">
+      <c r="N6" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="O6" s="40">
-        <v>5.1000000000000004E-3</v>
-      </c>
-      <c r="P6" s="41">
+      <c r="O6" s="36">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="P6" s="37">
         <f t="shared" si="0"/>
-        <v>1.0200000000000001E-2</v>
-      </c>
-      <c r="Q6" s="41">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="Q6" s="37">
         <f t="shared" si="1"/>
-        <v>0.255</v>
-      </c>
-      <c r="R6" s="40">
-        <v>5.1000000000000004E-3</v>
-      </c>
-      <c r="S6" s="41">
+        <v>0.18</v>
+      </c>
+      <c r="R6" s="36">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="S6" s="37">
         <f t="shared" si="2"/>
-        <v>5.1000000000000004E-2</v>
-      </c>
-      <c r="T6" s="62"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="T6" s="53"/>
     </row>
     <row r="7" spans="1:20" ht="16.5" customHeight="1" thickBot="1">
       <c r="A7" s="7">
         <v>5</v>
       </c>
-      <c r="B7" s="125" t="s">
+      <c r="B7" s="138" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="95" t="s">
+      <c r="C7" s="79" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="94" t="s">
+      <c r="D7" s="78" t="s">
         <v>187</v>
       </c>
-      <c r="E7" s="137" t="s">
+      <c r="E7" s="109" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="137" t="s">
+      <c r="F7" s="143" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="138" t="s">
+      <c r="G7" s="110" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="139" t="s">
+      <c r="H7" s="111" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="97" t="s">
+      <c r="I7" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="138" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7" s="138">
+      <c r="J7" s="110" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="110">
         <v>4</v>
       </c>
-      <c r="L7" s="140">
+      <c r="L7" s="112">
         <v>30</v>
       </c>
-      <c r="M7" s="97">
+      <c r="M7" s="81">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="N7" s="46" t="s">
+      <c r="N7" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="O7" s="141">
+      <c r="O7" s="113">
         <v>5.3199999999999997E-2</v>
       </c>
-      <c r="P7" s="142">
+      <c r="P7" s="114">
         <f t="shared" si="0"/>
         <v>0.21279999999999999</v>
       </c>
-      <c r="Q7" s="142">
+      <c r="Q7" s="114">
         <f t="shared" si="1"/>
         <v>1.5959999999999999</v>
       </c>
-      <c r="R7" s="141">
+      <c r="R7" s="113">
         <v>5.3199999999999997E-2</v>
       </c>
-      <c r="S7" s="34">
+      <c r="S7" s="30">
         <f t="shared" si="2"/>
         <v>1.0640000000000001</v>
       </c>
-      <c r="T7" s="60"/>
+      <c r="T7" s="51"/>
     </row>
     <row r="8" spans="1:20" ht="16.5" customHeight="1" thickBot="1">
       <c r="A8" s="7">
         <v>6</v>
       </c>
-      <c r="B8" s="126"/>
-      <c r="C8" s="75" t="s">
+      <c r="B8" s="139"/>
+      <c r="C8" s="64" t="s">
         <v>168</v>
       </c>
-      <c r="D8" s="76" t="s">
+      <c r="D8" s="65" t="s">
         <v>169</v>
       </c>
-      <c r="E8" s="77" t="s">
+      <c r="E8" s="66" t="s">
         <v>170</v>
       </c>
-      <c r="F8" s="77" t="s">
+      <c r="F8" s="66" t="s">
         <v>171</v>
       </c>
       <c r="G8" s="13" t="s">
@@ -2592,7 +2638,7 @@
       <c r="H8" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="I8" s="23" t="s">
+      <c r="I8" s="20" t="s">
         <v>35</v>
       </c>
       <c r="J8" s="13" t="s">
@@ -2601,51 +2647,51 @@
       <c r="K8" s="13">
         <v>1</v>
       </c>
-      <c r="L8" s="35">
+      <c r="L8" s="31">
         <v>20</v>
       </c>
-      <c r="M8" s="23">
+      <c r="M8" s="20">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N8" s="47" t="s">
+      <c r="N8" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O8" s="36">
+      <c r="O8" s="32">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="P8" s="37">
+      <c r="P8" s="33">
         <f t="shared" si="0"/>
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="Q8" s="37">
+      <c r="Q8" s="33">
         <f t="shared" si="1"/>
         <v>0.85999999999999988</v>
       </c>
-      <c r="R8" s="36">
+      <c r="R8" s="32">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="S8" s="37">
+      <c r="S8" s="33">
         <f t="shared" si="2"/>
         <v>0.21499999999999997</v>
       </c>
-      <c r="T8" s="61"/>
+      <c r="T8" s="52"/>
     </row>
     <row r="9" spans="1:20" ht="16.5" customHeight="1" thickBot="1">
       <c r="A9" s="7">
         <v>7</v>
       </c>
-      <c r="B9" s="126"/>
-      <c r="C9" s="96" t="s">
+      <c r="B9" s="139"/>
+      <c r="C9" s="80" t="s">
         <v>189</v>
       </c>
-      <c r="D9" s="76" t="s">
+      <c r="D9" s="65" t="s">
         <v>173</v>
       </c>
-      <c r="E9" s="77" t="s">
+      <c r="E9" s="66" t="s">
         <v>170</v>
       </c>
-      <c r="F9" s="77" t="s">
+      <c r="F9" s="66" t="s">
         <v>174</v>
       </c>
       <c r="G9" s="13" t="s">
@@ -2654,7 +2700,7 @@
       <c r="H9" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="I9" s="23" t="s">
+      <c r="I9" s="20" t="s">
         <v>35</v>
       </c>
       <c r="J9" s="13" t="s">
@@ -2663,51 +2709,51 @@
       <c r="K9" s="13">
         <v>1</v>
       </c>
-      <c r="L9" s="35">
+      <c r="L9" s="31">
         <v>10</v>
       </c>
-      <c r="M9" s="23">
+      <c r="M9" s="20">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N9" s="47" t="s">
+      <c r="N9" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O9" s="36">
+      <c r="O9" s="32">
         <v>4.5100000000000001E-2</v>
       </c>
-      <c r="P9" s="37">
+      <c r="P9" s="33">
         <f t="shared" si="0"/>
         <v>4.5100000000000001E-2</v>
       </c>
-      <c r="Q9" s="37">
+      <c r="Q9" s="33">
         <f t="shared" si="1"/>
         <v>0.45100000000000001</v>
       </c>
-      <c r="R9" s="36">
+      <c r="R9" s="32">
         <v>4.5100000000000001E-2</v>
       </c>
-      <c r="S9" s="37">
+      <c r="S9" s="33">
         <f t="shared" si="2"/>
         <v>0.22550000000000001</v>
       </c>
-      <c r="T9" s="61"/>
+      <c r="T9" s="52"/>
     </row>
     <row r="10" spans="1:20" ht="16.5" customHeight="1" thickBot="1">
       <c r="A10" s="7">
         <v>8</v>
       </c>
-      <c r="B10" s="126"/>
-      <c r="C10" s="75" t="s">
+      <c r="B10" s="139"/>
+      <c r="C10" s="64" t="s">
         <v>175</v>
       </c>
-      <c r="D10" s="76" t="s">
+      <c r="D10" s="65" t="s">
         <v>176</v>
       </c>
-      <c r="E10" s="77" t="s">
+      <c r="E10" s="66" t="s">
         <v>170</v>
       </c>
-      <c r="F10" s="77" t="s">
+      <c r="F10" s="66" t="s">
         <v>177</v>
       </c>
       <c r="G10" s="13" t="s">
@@ -2716,7 +2762,7 @@
       <c r="H10" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="I10" s="23" t="s">
+      <c r="I10" s="20" t="s">
         <v>35</v>
       </c>
       <c r="J10" s="13" t="s">
@@ -2725,177 +2771,177 @@
       <c r="K10" s="13">
         <v>1</v>
       </c>
-      <c r="L10" s="35">
+      <c r="L10" s="31">
         <v>10</v>
       </c>
-      <c r="M10" s="23">
+      <c r="M10" s="20">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N10" s="47" t="s">
+      <c r="N10" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O10" s="36">
-        <v>5.4800000000000001E-2</v>
-      </c>
-      <c r="P10" s="37">
+      <c r="O10" s="32">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="P10" s="33">
         <f t="shared" si="0"/>
-        <v>5.4800000000000001E-2</v>
-      </c>
-      <c r="Q10" s="37">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="Q10" s="33">
         <f t="shared" si="1"/>
-        <v>0.54800000000000004</v>
-      </c>
-      <c r="R10" s="36">
-        <v>5.4800000000000001E-2</v>
-      </c>
-      <c r="S10" s="37">
+        <v>0.55599999999999994</v>
+      </c>
+      <c r="R10" s="32">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="S10" s="33">
         <f t="shared" si="2"/>
-        <v>0.27400000000000002</v>
-      </c>
-      <c r="T10" s="61"/>
+        <v>0.27799999999999997</v>
+      </c>
+      <c r="T10" s="52"/>
     </row>
     <row r="11" spans="1:20" ht="16.5" customHeight="1" thickBot="1">
       <c r="A11" s="7">
         <v>9</v>
       </c>
-      <c r="B11" s="127"/>
-      <c r="C11" s="85" t="s">
+      <c r="B11" s="140"/>
+      <c r="C11" s="69" t="s">
         <v>178</v>
       </c>
-      <c r="D11" s="78" t="s">
+      <c r="D11" s="67" t="s">
         <v>179</v>
       </c>
-      <c r="E11" s="79" t="s">
+      <c r="E11" s="68" t="s">
         <v>170</v>
       </c>
-      <c r="F11" s="79" t="s">
+      <c r="F11" s="68" t="s">
         <v>180</v>
       </c>
       <c r="G11" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="H11" s="143" t="s">
+      <c r="H11" s="115" t="s">
         <v>193</v>
       </c>
-      <c r="I11" s="144" t="s">
-        <v>35</v>
-      </c>
-      <c r="J11" s="145" t="s">
-        <v>35</v>
-      </c>
-      <c r="K11" s="145">
+      <c r="I11" s="116" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="117" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" s="117">
         <v>1</v>
       </c>
-      <c r="L11" s="146">
+      <c r="L11" s="118">
         <v>10</v>
       </c>
-      <c r="M11" s="144">
+      <c r="M11" s="116">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N11" s="39" t="s">
+      <c r="N11" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="O11" s="147">
+      <c r="O11" s="119">
         <v>7.5200000000000003E-2</v>
       </c>
-      <c r="P11" s="148">
+      <c r="P11" s="120">
         <f t="shared" si="0"/>
         <v>7.5200000000000003E-2</v>
       </c>
-      <c r="Q11" s="148">
+      <c r="Q11" s="120">
         <f t="shared" si="1"/>
         <v>0.752</v>
       </c>
-      <c r="R11" s="147">
+      <c r="R11" s="119">
         <v>7.5200000000000003E-2</v>
       </c>
-      <c r="S11" s="41">
+      <c r="S11" s="37">
         <f t="shared" si="2"/>
         <v>0.376</v>
       </c>
-      <c r="T11" s="62"/>
+      <c r="T11" s="53"/>
     </row>
     <row r="12" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A12" s="7">
         <v>10</v>
       </c>
-      <c r="B12" s="126" t="s">
+      <c r="B12" s="139" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="135" t="s">
+      <c r="C12" s="107" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="136" t="s">
+      <c r="D12" s="108" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="88" t="s">
+      <c r="E12" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="88" t="s">
+      <c r="F12" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="G12" s="86" t="s">
+      <c r="G12" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="H12" s="87" t="s">
+      <c r="H12" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="I12" s="86" t="s">
-        <v>35</v>
-      </c>
-      <c r="J12" s="86" t="s">
-        <v>35</v>
-      </c>
-      <c r="K12" s="86">
+      <c r="I12" s="70" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12" s="70" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" s="70">
         <v>1</v>
       </c>
-      <c r="L12" s="89">
+      <c r="L12" s="73">
         <v>7</v>
       </c>
-      <c r="M12" s="90">
+      <c r="M12" s="74">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N12" s="132" t="s">
+      <c r="N12" s="104" t="s">
         <v>29</v>
       </c>
-      <c r="O12" s="91">
-        <v>0.33329999999999999</v>
-      </c>
-      <c r="P12" s="133">
+      <c r="O12" s="75">
+        <v>0.31109999999999999</v>
+      </c>
+      <c r="P12" s="105">
         <f t="shared" si="0"/>
-        <v>0.33329999999999999</v>
-      </c>
-      <c r="Q12" s="133">
+        <v>0.31109999999999999</v>
+      </c>
+      <c r="Q12" s="105">
         <f t="shared" si="1"/>
-        <v>2.3331</v>
-      </c>
-      <c r="R12" s="91">
-        <v>0.33329999999999999</v>
-      </c>
-      <c r="S12" s="133">
+        <v>2.1776999999999997</v>
+      </c>
+      <c r="R12" s="75">
+        <v>0.31109999999999999</v>
+      </c>
+      <c r="S12" s="105">
         <f t="shared" si="2"/>
-        <v>1.6664999999999999</v>
-      </c>
-      <c r="T12" s="92"/>
+        <v>1.5554999999999999</v>
+      </c>
+      <c r="T12" s="76"/>
     </row>
     <row r="13" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A13" s="7">
         <v>11</v>
       </c>
-      <c r="B13" s="126"/>
+      <c r="B13" s="139"/>
       <c r="C13" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="76" t="s">
+      <c r="D13" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="77" t="s">
+      <c r="E13" s="66" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="77" t="s">
+      <c r="F13" s="66" t="s">
         <v>59</v>
       </c>
       <c r="G13" s="13" t="s">
@@ -2913,115 +2959,117 @@
       <c r="K13" s="13">
         <v>2</v>
       </c>
-      <c r="L13" s="35">
+      <c r="L13" s="31">
         <v>20</v>
       </c>
-      <c r="M13" s="23">
+      <c r="M13" s="20">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="N13" s="47" t="s">
+      <c r="N13" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O13" s="36">
-        <v>3.39E-2</v>
-      </c>
-      <c r="P13" s="37">
+      <c r="O13" s="32">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="P13" s="33">
         <f t="shared" si="0"/>
-        <v>6.7799999999999999E-2</v>
-      </c>
-      <c r="Q13" s="37">
+        <v>7.0199999999999999E-2</v>
+      </c>
+      <c r="Q13" s="33">
         <f t="shared" si="1"/>
-        <v>0.67799999999999994</v>
-      </c>
-      <c r="R13" s="36">
-        <v>3.39E-2</v>
-      </c>
-      <c r="S13" s="37">
+        <v>0.70199999999999996</v>
+      </c>
+      <c r="R13" s="32">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="S13" s="33">
         <f t="shared" si="2"/>
-        <v>0.33899999999999997</v>
-      </c>
-      <c r="T13" s="61"/>
+        <v>0.35099999999999998</v>
+      </c>
+      <c r="T13" s="52"/>
     </row>
     <row r="14" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A14" s="7">
         <v>12</v>
       </c>
-      <c r="B14" s="126"/>
-      <c r="C14" s="149" t="s">
+      <c r="B14" s="139"/>
+      <c r="C14" s="147" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="150" t="s">
+      <c r="D14" s="148" t="s">
         <v>188</v>
       </c>
-      <c r="E14" s="93" t="s">
+      <c r="E14" s="149" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="93" t="s">
+      <c r="F14" s="149" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="151" t="s">
+      <c r="G14" s="150" t="s">
         <v>54</v>
       </c>
-      <c r="H14" s="152" t="s">
+      <c r="H14" s="151" t="s">
         <v>64</v>
       </c>
-      <c r="I14" s="153" t="s">
-        <v>35</v>
-      </c>
-      <c r="J14" s="151" t="s">
-        <v>35</v>
-      </c>
-      <c r="K14" s="151">
+      <c r="I14" s="152" t="s">
+        <v>35</v>
+      </c>
+      <c r="J14" s="150" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14" s="150">
         <v>1</v>
       </c>
-      <c r="L14" s="154">
-        <v>10</v>
-      </c>
-      <c r="M14" s="153">
+      <c r="L14" s="152">
+        <v>149</v>
+      </c>
+      <c r="M14" s="152">
         <f>K14*5</f>
         <v>5</v>
       </c>
-      <c r="N14" s="155" t="s">
-        <v>29</v>
-      </c>
-      <c r="O14" s="156">
-        <v>9.8400000000000001E-2</v>
-      </c>
-      <c r="P14" s="157">
+      <c r="N14" s="171" t="s">
+        <v>201</v>
+      </c>
+      <c r="O14" s="153">
+        <v>8.8099999999999998E-2</v>
+      </c>
+      <c r="P14" s="154">
         <f>O14*K14</f>
-        <v>9.8400000000000001E-2</v>
-      </c>
-      <c r="Q14" s="157">
+        <v>8.8099999999999998E-2</v>
+      </c>
+      <c r="Q14" s="154">
         <f>O14*L14</f>
-        <v>0.98399999999999999</v>
-      </c>
-      <c r="R14" s="156">
-        <v>9.8400000000000001E-2</v>
-      </c>
-      <c r="S14" s="157">
+        <v>13.126899999999999</v>
+      </c>
+      <c r="R14" s="153">
+        <v>8.8099999999999998E-2</v>
+      </c>
+      <c r="S14" s="154">
         <f>R14*M14</f>
-        <v>0.49199999999999999</v>
-      </c>
-      <c r="T14" s="158"/>
+        <v>0.4405</v>
+      </c>
+      <c r="T14" s="82" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="15" spans="1:20" ht="15.75" thickBot="1">
       <c r="A15" s="7">
         <v>13</v>
       </c>
-      <c r="B15" s="160" t="s">
+      <c r="B15" s="135" t="s">
         <v>65</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="72" t="s">
+      <c r="D15" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="74" t="s">
+      <c r="E15" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="74" t="s">
+      <c r="F15" s="145" t="s">
         <v>69</v>
       </c>
       <c r="G15" s="9" t="s">
@@ -3030,122 +3078,122 @@
       <c r="H15" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="I15" s="32" t="s">
+      <c r="I15" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="J15" s="74" t="s">
+      <c r="J15" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="K15" s="22">
+      <c r="K15" s="19">
         <v>5</v>
       </c>
-      <c r="L15" s="31">
+      <c r="L15" s="27">
         <v>100</v>
       </c>
-      <c r="M15" s="32">
+      <c r="M15" s="28">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="N15" s="46" t="s">
+      <c r="N15" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="O15" s="33">
+      <c r="O15" s="29">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="P15" s="34">
+      <c r="P15" s="30">
         <f t="shared" ref="P15:P25" si="4">O15*K15</f>
         <v>5.9999999999999993E-3</v>
       </c>
-      <c r="Q15" s="34">
+      <c r="Q15" s="30">
         <f t="shared" ref="Q15:Q19" si="5">O15*L15</f>
         <v>0.12</v>
       </c>
-      <c r="R15" s="33">
+      <c r="R15" s="29">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="S15" s="34">
+      <c r="S15" s="30">
         <f t="shared" ref="S15:S19" si="6">R15*M15</f>
         <v>0.03</v>
       </c>
-      <c r="T15" s="60"/>
+      <c r="T15" s="51"/>
     </row>
     <row r="16" spans="1:20" ht="15.75" thickBot="1">
       <c r="A16" s="7">
         <v>14</v>
       </c>
-      <c r="B16" s="161"/>
-      <c r="C16" s="159" t="s">
+      <c r="B16" s="136"/>
+      <c r="C16" s="155" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="76" t="s">
+      <c r="D16" s="156" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="157" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="77" t="s">
+      <c r="F16" s="156" t="s">
         <v>77</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="158" t="s">
         <v>78</v>
       </c>
-      <c r="H16" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="J16" s="77" t="s">
+      <c r="H16" s="159" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="159" t="s">
+        <v>35</v>
+      </c>
+      <c r="J16" s="156" t="s">
         <v>73</v>
       </c>
-      <c r="K16" s="12">
+      <c r="K16" s="157">
         <v>1</v>
       </c>
-      <c r="L16" s="35">
+      <c r="L16" s="159">
         <v>7</v>
       </c>
-      <c r="M16" s="23">
+      <c r="M16" s="159">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N16" s="47" t="s">
+      <c r="N16" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="O16" s="37">
+      <c r="O16" s="161">
         <v>0.47620000000000001</v>
       </c>
-      <c r="P16" s="37">
+      <c r="P16" s="161">
         <f>O16*K16</f>
         <v>0.47620000000000001</v>
       </c>
-      <c r="Q16" s="37">
+      <c r="Q16" s="161">
         <f>O16*L16</f>
         <v>3.3334000000000001</v>
       </c>
-      <c r="R16" s="37">
+      <c r="R16" s="161">
         <v>0.47620000000000001</v>
       </c>
-      <c r="S16" s="37">
+      <c r="S16" s="161">
         <f>R16*M16</f>
         <v>2.3810000000000002</v>
       </c>
-      <c r="T16" s="63"/>
+      <c r="T16" s="162"/>
     </row>
     <row r="17" spans="1:20" ht="15.75" thickBot="1">
       <c r="A17" s="7">
         <v>15</v>
       </c>
-      <c r="B17" s="161"/>
-      <c r="C17" s="159" t="s">
+      <c r="B17" s="136"/>
+      <c r="C17" s="121" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="76" t="s">
+      <c r="D17" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="E17" s="77" t="s">
+      <c r="E17" s="66" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="77" t="s">
+      <c r="F17" s="66" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="13" t="s">
@@ -3154,60 +3202,60 @@
       <c r="H17" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="I17" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="J17" s="77" t="s">
+      <c r="I17" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" s="66" t="s">
         <v>85</v>
       </c>
       <c r="K17" s="12">
         <v>2</v>
       </c>
-      <c r="L17" s="48">
+      <c r="L17" s="40">
         <v>100</v>
       </c>
-      <c r="M17" s="23">
+      <c r="M17" s="20">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="N17" s="47" t="s">
+      <c r="N17" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O17" s="36">
-        <v>1.9E-3</v>
-      </c>
-      <c r="P17" s="37">
+      <c r="O17" s="32">
+        <v>1.5E-3</v>
+      </c>
+      <c r="P17" s="33">
         <f t="shared" si="4"/>
-        <v>3.8E-3</v>
-      </c>
-      <c r="Q17" s="37">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="Q17" s="33">
         <f t="shared" si="5"/>
-        <v>0.19</v>
-      </c>
-      <c r="R17" s="36">
-        <v>1.9E-3</v>
-      </c>
-      <c r="S17" s="37">
+        <v>0.15</v>
+      </c>
+      <c r="R17" s="32">
+        <v>1.5E-3</v>
+      </c>
+      <c r="S17" s="33">
         <f t="shared" si="6"/>
-        <v>1.9E-2</v>
-      </c>
-      <c r="T17" s="63"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="T17" s="54"/>
     </row>
     <row r="18" spans="1:20" ht="15.75" thickBot="1">
       <c r="A18" s="7">
         <v>16</v>
       </c>
-      <c r="B18" s="161"/>
+      <c r="B18" s="136"/>
       <c r="C18" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="76" t="s">
+      <c r="D18" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="E18" s="77" t="s">
+      <c r="E18" s="66" t="s">
         <v>68</v>
       </c>
-      <c r="F18" s="77" t="s">
+      <c r="F18" s="146" t="s">
         <v>88</v>
       </c>
       <c r="G18" s="13" t="s">
@@ -3219,128 +3267,128 @@
       <c r="I18" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="J18" s="77" t="s">
+      <c r="J18" s="66" t="s">
         <v>91</v>
       </c>
       <c r="K18" s="12">
         <v>1</v>
       </c>
-      <c r="L18" s="48">
+      <c r="L18" s="40">
         <v>100</v>
       </c>
-      <c r="M18" s="23">
+      <c r="M18" s="20">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N18" s="47" t="s">
+      <c r="N18" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O18" s="36">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="P18" s="37">
+      <c r="O18" s="32">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="P18" s="33">
         <f t="shared" si="4"/>
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="Q18" s="37">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q18" s="33">
         <f t="shared" si="5"/>
-        <v>0.06</v>
-      </c>
-      <c r="R18" s="36">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="S18" s="37">
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R18" s="32">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="S18" s="33">
         <f t="shared" si="6"/>
-        <v>2.9999999999999996E-3</v>
-      </c>
-      <c r="T18" s="64"/>
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="T18" s="55"/>
     </row>
     <row r="19" spans="1:20" ht="15.75" thickBot="1">
       <c r="A19" s="7">
         <v>17</v>
       </c>
-      <c r="B19" s="161"/>
+      <c r="B19" s="136"/>
       <c r="C19" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="D19" s="76" t="s">
+      <c r="D19" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="E19" s="77" t="s">
+      <c r="E19" s="66" t="s">
         <v>68</v>
       </c>
-      <c r="F19" s="77" t="s">
+      <c r="F19" s="66" t="s">
         <v>94</v>
       </c>
       <c r="G19" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="H19" s="23" t="s">
+      <c r="H19" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="I19" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="J19" s="77" t="s">
+      <c r="I19" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="J19" s="66" t="s">
         <v>96</v>
       </c>
       <c r="K19" s="12">
         <v>3</v>
       </c>
-      <c r="L19" s="48">
+      <c r="L19" s="40">
         <v>100</v>
       </c>
-      <c r="M19" s="23">
+      <c r="M19" s="20">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="N19" s="47" t="s">
+      <c r="N19" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O19" s="37">
-        <v>1.9E-3</v>
-      </c>
-      <c r="P19" s="37">
+      <c r="O19" s="33">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="P19" s="33">
         <f t="shared" si="4"/>
-        <v>5.7000000000000002E-3</v>
-      </c>
-      <c r="Q19" s="37">
+        <v>4.8000000000000004E-3</v>
+      </c>
+      <c r="Q19" s="33">
         <f t="shared" si="5"/>
-        <v>0.19</v>
-      </c>
-      <c r="R19" s="37">
-        <v>1.9E-3</v>
-      </c>
-      <c r="S19" s="37">
+        <v>0.16</v>
+      </c>
+      <c r="R19" s="33">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="S19" s="33">
         <f t="shared" si="6"/>
-        <v>2.8500000000000001E-2</v>
-      </c>
-      <c r="T19" s="65"/>
+        <v>2.4E-2</v>
+      </c>
+      <c r="T19" s="56"/>
     </row>
     <row r="20" spans="1:20" ht="15.75" thickBot="1">
       <c r="A20" s="7">
         <v>18</v>
       </c>
-      <c r="B20" s="161"/>
-      <c r="C20" s="159" t="s">
+      <c r="B20" s="136"/>
+      <c r="C20" s="121" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="76" t="s">
+      <c r="D20" s="65" t="s">
         <v>98</v>
       </c>
-      <c r="E20" s="77" t="s">
+      <c r="E20" s="66" t="s">
         <v>68</v>
       </c>
-      <c r="F20" s="77" t="s">
+      <c r="F20" s="66" t="s">
         <v>99</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="H20" s="23" t="s">
+      <c r="H20" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="I20" s="23" t="s">
+      <c r="I20" s="20" t="s">
         <v>35</v>
       </c>
       <c r="J20" s="12" t="s">
@@ -3349,60 +3397,60 @@
       <c r="K20" s="12">
         <v>1</v>
       </c>
-      <c r="L20" s="35">
+      <c r="L20" s="31">
         <v>100</v>
       </c>
-      <c r="M20" s="23">
+      <c r="M20" s="20">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N20" s="47" t="s">
+      <c r="N20" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O20" s="37">
+      <c r="O20" s="33">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="P20" s="37">
+      <c r="P20" s="33">
         <f t="shared" si="4"/>
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q20" s="37">
+      <c r="Q20" s="33">
         <f t="shared" ref="Q20:Q25" si="7">O20*L20</f>
         <v>0.13</v>
       </c>
-      <c r="R20" s="37">
+      <c r="R20" s="33">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="S20" s="37">
+      <c r="S20" s="33">
         <f t="shared" ref="S20:S25" si="8">R20*M20</f>
         <v>6.4999999999999997E-3</v>
       </c>
-      <c r="T20" s="66"/>
+      <c r="T20" s="57"/>
     </row>
     <row r="21" spans="1:20" ht="15.75" thickBot="1">
       <c r="A21" s="7">
         <v>19</v>
       </c>
-      <c r="B21" s="161"/>
-      <c r="C21" s="159" t="s">
+      <c r="B21" s="136"/>
+      <c r="C21" s="121" t="s">
         <v>103</v>
       </c>
-      <c r="D21" s="76" t="s">
+      <c r="D21" s="65" t="s">
         <v>104</v>
       </c>
-      <c r="E21" s="77" t="s">
+      <c r="E21" s="66" t="s">
         <v>68</v>
       </c>
-      <c r="F21" s="77" t="s">
+      <c r="F21" s="66" t="s">
         <v>105</v>
       </c>
       <c r="G21" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="H21" s="23" t="s">
+      <c r="H21" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="I21" s="23" t="s">
+      <c r="I21" s="20" t="s">
         <v>35</v>
       </c>
       <c r="J21" s="12" t="s">
@@ -3411,51 +3459,51 @@
       <c r="K21" s="12">
         <v>1</v>
       </c>
-      <c r="L21" s="35">
+      <c r="L21" s="31">
         <v>100</v>
       </c>
-      <c r="M21" s="23">
+      <c r="M21" s="20">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N21" s="47" t="s">
+      <c r="N21" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O21" s="37">
+      <c r="O21" s="33">
         <v>1.4E-3</v>
       </c>
-      <c r="P21" s="37">
+      <c r="P21" s="33">
         <f t="shared" si="4"/>
         <v>1.4E-3</v>
       </c>
-      <c r="Q21" s="37">
+      <c r="Q21" s="33">
         <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="R21" s="37">
+      <c r="R21" s="33">
         <v>1.4E-3</v>
       </c>
-      <c r="S21" s="37">
+      <c r="S21" s="33">
         <f t="shared" si="8"/>
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="T21" s="66"/>
+      <c r="T21" s="57"/>
     </row>
     <row r="22" spans="1:20" ht="15.75" thickBot="1">
       <c r="A22" s="7">
         <v>20</v>
       </c>
-      <c r="B22" s="161"/>
+      <c r="B22" s="136"/>
       <c r="C22" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D22" s="76" t="s">
+      <c r="D22" s="65" t="s">
         <v>110</v>
       </c>
-      <c r="E22" s="77" t="s">
+      <c r="E22" s="66" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="77" t="s">
+      <c r="F22" s="66" t="s">
         <v>111</v>
       </c>
       <c r="G22" s="13" t="s">
@@ -3464,7 +3512,7 @@
       <c r="H22" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="I22" s="23" t="s">
+      <c r="I22" s="20" t="s">
         <v>35</v>
       </c>
       <c r="J22" s="12" t="s">
@@ -3473,51 +3521,51 @@
       <c r="K22" s="12">
         <v>1</v>
       </c>
-      <c r="L22" s="35">
+      <c r="L22" s="31">
         <v>100</v>
       </c>
-      <c r="M22" s="23">
+      <c r="M22" s="20">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N22" s="47" t="s">
+      <c r="N22" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O22" s="37">
-        <v>1.8E-3</v>
-      </c>
-      <c r="P22" s="37">
+      <c r="O22" s="33">
+        <v>2.3E-3</v>
+      </c>
+      <c r="P22" s="33">
         <f t="shared" si="4"/>
-        <v>1.8E-3</v>
-      </c>
-      <c r="Q22" s="37">
+        <v>2.3E-3</v>
+      </c>
+      <c r="Q22" s="33">
         <f t="shared" si="7"/>
-        <v>0.18</v>
-      </c>
-      <c r="R22" s="37">
-        <v>1.8E-3</v>
-      </c>
-      <c r="S22" s="37">
+        <v>0.22999999999999998</v>
+      </c>
+      <c r="R22" s="33">
+        <v>2.3E-3</v>
+      </c>
+      <c r="S22" s="33">
         <f t="shared" si="8"/>
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="T22" s="67"/>
+        <v>1.15E-2</v>
+      </c>
+      <c r="T22" s="58"/>
     </row>
     <row r="23" spans="1:20" ht="15.75" thickBot="1">
       <c r="A23" s="7">
         <v>21</v>
       </c>
-      <c r="B23" s="161"/>
-      <c r="C23" s="159" t="s">
+      <c r="B23" s="136"/>
+      <c r="C23" s="121" t="s">
         <v>113</v>
       </c>
-      <c r="D23" s="76" t="s">
+      <c r="D23" s="65" t="s">
         <v>114</v>
       </c>
-      <c r="E23" s="77" t="s">
+      <c r="E23" s="66" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="77" t="s">
+      <c r="F23" s="66" t="s">
         <v>115</v>
       </c>
       <c r="G23" s="13" t="s">
@@ -3526,7 +3574,7 @@
       <c r="H23" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="I23" s="23" t="s">
+      <c r="I23" s="20" t="s">
         <v>35</v>
       </c>
       <c r="J23" s="12" t="s">
@@ -3535,51 +3583,51 @@
       <c r="K23" s="12">
         <v>1</v>
       </c>
-      <c r="L23" s="35">
+      <c r="L23" s="31">
         <v>100</v>
       </c>
-      <c r="M23" s="23">
+      <c r="M23" s="20">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N23" s="47" t="s">
+      <c r="N23" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O23" s="37">
+      <c r="O23" s="33">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="P23" s="37">
+      <c r="P23" s="33">
         <f t="shared" si="4"/>
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="Q23" s="37">
+      <c r="Q23" s="33">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
-      <c r="R23" s="37">
+      <c r="R23" s="33">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="S23" s="37">
+      <c r="S23" s="33">
         <f t="shared" si="8"/>
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="T23" s="68"/>
+      <c r="T23" s="59"/>
     </row>
     <row r="24" spans="1:20" ht="15.75" thickBot="1">
       <c r="A24" s="7">
         <v>22</v>
       </c>
-      <c r="B24" s="162"/>
+      <c r="B24" s="137"/>
       <c r="C24" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D24" s="78" t="s">
+      <c r="D24" s="67" t="s">
         <v>119</v>
       </c>
-      <c r="E24" s="79" t="s">
+      <c r="E24" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="F24" s="79" t="s">
+      <c r="F24" s="68" t="s">
         <v>120</v>
       </c>
       <c r="G24" s="17" t="s">
@@ -3588,7 +3636,7 @@
       <c r="H24" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="I24" s="28" t="s">
+      <c r="I24" s="24" t="s">
         <v>35</v>
       </c>
       <c r="J24" s="16" t="s">
@@ -3597,245 +3645,245 @@
       <c r="K24" s="16">
         <v>4</v>
       </c>
-      <c r="L24" s="38">
+      <c r="L24" s="34">
         <v>100</v>
       </c>
-      <c r="M24" s="28">
+      <c r="M24" s="24">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="N24" s="39" t="s">
+      <c r="N24" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="O24" s="41">
+      <c r="O24" s="37">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="P24" s="41">
+      <c r="P24" s="37">
         <f t="shared" si="4"/>
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="Q24" s="41">
+      <c r="Q24" s="37">
         <f t="shared" si="7"/>
         <v>0.11</v>
       </c>
-      <c r="R24" s="41">
+      <c r="R24" s="37">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="S24" s="41">
+      <c r="S24" s="37">
         <f t="shared" si="8"/>
         <v>2.2000000000000002E-2</v>
       </c>
-      <c r="T24" s="69"/>
+      <c r="T24" s="60"/>
     </row>
     <row r="25" spans="1:20" ht="16.5" thickBot="1">
       <c r="A25" s="7">
         <v>23</v>
       </c>
-      <c r="B25" s="117" t="s">
+      <c r="B25" s="101" t="s">
         <v>123</v>
       </c>
-      <c r="C25" s="80" t="s">
+      <c r="C25" s="163" t="s">
         <v>124</v>
       </c>
-      <c r="D25" s="81" t="s">
+      <c r="D25" s="164" t="s">
         <v>125</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="E25" s="165" t="s">
         <v>76</v>
       </c>
-      <c r="F25" s="82" t="s">
+      <c r="F25" s="164" t="s">
         <v>126</v>
       </c>
-      <c r="G25" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="H25" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="I25" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="J25" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="K25" s="20">
+      <c r="G25" s="166" t="s">
+        <v>35</v>
+      </c>
+      <c r="H25" s="167" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25" s="168" t="s">
+        <v>35</v>
+      </c>
+      <c r="J25" s="166" t="s">
+        <v>35</v>
+      </c>
+      <c r="K25" s="166">
         <v>1</v>
       </c>
-      <c r="L25" s="43">
+      <c r="L25" s="168">
         <v>7</v>
       </c>
-      <c r="M25" s="42">
+      <c r="M25" s="168">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N25" s="44" t="s">
+      <c r="N25" s="169" t="s">
         <v>79</v>
       </c>
-      <c r="O25" s="45">
+      <c r="O25" s="170">
         <v>0.318</v>
       </c>
-      <c r="P25" s="45">
+      <c r="P25" s="170">
         <f t="shared" si="4"/>
         <v>0.318</v>
       </c>
-      <c r="Q25" s="45">
+      <c r="Q25" s="170">
         <f t="shared" si="7"/>
         <v>2.226</v>
       </c>
-      <c r="R25" s="45">
+      <c r="R25" s="170">
         <v>0.318</v>
       </c>
-      <c r="S25" s="45">
+      <c r="S25" s="170">
         <f t="shared" si="8"/>
         <v>1.59</v>
       </c>
-      <c r="T25" s="70"/>
+      <c r="T25" s="82" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="26" spans="1:20" ht="16.5" thickBot="1">
       <c r="A26" s="7">
         <v>24</v>
       </c>
-      <c r="B26" s="24" t="s">
+      <c r="B26" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="83" t="s">
+      <c r="C26" s="173" t="s">
         <v>128</v>
       </c>
-      <c r="D26" s="84" t="s">
+      <c r="D26" s="174" t="s">
         <v>129</v>
       </c>
-      <c r="E26" s="25" t="s">
+      <c r="E26" s="175" t="s">
         <v>76</v>
       </c>
-      <c r="F26" s="84" t="s">
+      <c r="F26" s="174" t="s">
         <v>130</v>
       </c>
-      <c r="G26" s="26" t="s">
+      <c r="G26" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="H26" s="27" t="s">
+      <c r="H26" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="I26" s="49" t="s">
-        <v>35</v>
-      </c>
-      <c r="J26" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="K26" s="26">
+      <c r="I26" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="K26" s="22">
         <v>2</v>
       </c>
-      <c r="L26" s="49">
+      <c r="L26" s="41">
         <v>12</v>
       </c>
-      <c r="M26" s="49">
+      <c r="M26" s="41">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="N26" s="169" t="s">
-        <v>196</v>
-      </c>
-      <c r="O26" s="50">
-        <v>0.49941000000000002</v>
-      </c>
-      <c r="P26" s="51">
+      <c r="N26" s="176" t="s">
+        <v>29</v>
+      </c>
+      <c r="O26" s="42">
+        <v>0.8115</v>
+      </c>
+      <c r="P26" s="43">
         <f t="shared" ref="P26:P31" si="9">O26*K26</f>
-        <v>0.99882000000000004</v>
-      </c>
-      <c r="Q26" s="51">
+        <v>1.623</v>
+      </c>
+      <c r="Q26" s="43">
         <f t="shared" ref="Q26:Q31" si="10">O26*L26</f>
-        <v>5.9929199999999998</v>
-      </c>
-      <c r="R26" s="51">
-        <v>0.55489999999999995</v>
-      </c>
-      <c r="S26" s="51">
+        <v>9.7379999999999995</v>
+      </c>
+      <c r="R26" s="43">
+        <v>0.8115</v>
+      </c>
+      <c r="S26" s="43">
         <f t="shared" ref="S26:S31" si="11">R26*M26</f>
-        <v>5.5489999999999995</v>
-      </c>
-      <c r="T26" s="98" t="s">
-        <v>195</v>
-      </c>
+        <v>8.1150000000000002</v>
+      </c>
+      <c r="T26" s="172"/>
     </row>
     <row r="27" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A27" s="7">
         <v>25</v>
       </c>
-      <c r="B27" s="125" t="s">
+      <c r="B27" s="138" t="s">
         <v>133</v>
       </c>
-      <c r="C27" s="130" t="s">
-        <v>200</v>
-      </c>
-      <c r="D27" s="74" t="s">
+      <c r="C27" s="102" t="s">
+        <v>199</v>
+      </c>
+      <c r="D27" s="63" t="s">
         <v>134</v>
       </c>
-      <c r="E27" s="22" t="s">
+      <c r="E27" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="F27" s="22" t="s">
-        <v>199</v>
+      <c r="F27" s="19" t="s">
+        <v>198</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>135</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="I27" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="J27" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="K27" s="22">
+        <v>200</v>
+      </c>
+      <c r="I27" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="J27" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="K27" s="19">
         <v>1</v>
       </c>
-      <c r="L27" s="52">
+      <c r="L27" s="44">
         <v>6</v>
       </c>
-      <c r="M27" s="32">
+      <c r="M27" s="28">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N27" s="46" t="s">
+      <c r="N27" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="O27" s="34">
+      <c r="O27" s="30">
         <v>2.9754999999999998</v>
       </c>
-      <c r="P27" s="34">
+      <c r="P27" s="30">
         <f t="shared" si="9"/>
         <v>2.9754999999999998</v>
       </c>
-      <c r="Q27" s="34">
+      <c r="Q27" s="30">
         <f t="shared" si="10"/>
         <v>17.852999999999998</v>
       </c>
-      <c r="R27" s="34">
+      <c r="R27" s="30">
         <v>2.9754999999999998</v>
       </c>
-      <c r="S27" s="34">
+      <c r="S27" s="30">
         <f t="shared" si="11"/>
         <v>14.8775</v>
       </c>
-      <c r="T27" s="131"/>
+      <c r="T27" s="103"/>
     </row>
     <row r="28" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A28" s="7">
         <v>26</v>
       </c>
-      <c r="B28" s="126"/>
+      <c r="B28" s="139"/>
       <c r="C28" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="D28" s="77" t="s">
+      <c r="D28" s="66" t="s">
         <v>137</v>
       </c>
-      <c r="E28" s="77" t="s">
+      <c r="E28" s="66" t="s">
         <v>138</v>
       </c>
-      <c r="F28" s="77" t="s">
+      <c r="F28" s="66" t="s">
         <v>139</v>
       </c>
       <c r="G28" s="13" t="s">
@@ -3844,106 +3892,106 @@
       <c r="H28" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="I28" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="J28" s="23" t="s">
+      <c r="I28" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="J28" s="20" t="s">
         <v>35</v>
       </c>
       <c r="K28" s="12">
         <v>1</v>
       </c>
-      <c r="L28" s="53">
+      <c r="L28" s="45">
         <v>6</v>
       </c>
-      <c r="M28" s="23">
+      <c r="M28" s="20">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N28" s="47" t="s">
+      <c r="N28" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O28" s="37">
+      <c r="O28" s="33">
         <v>0.25119999999999998</v>
       </c>
-      <c r="P28" s="37">
+      <c r="P28" s="33">
         <f t="shared" si="9"/>
         <v>0.25119999999999998</v>
       </c>
-      <c r="Q28" s="37">
+      <c r="Q28" s="33">
         <f t="shared" si="10"/>
         <v>1.5071999999999999</v>
       </c>
-      <c r="R28" s="37">
+      <c r="R28" s="33">
         <v>0.25119999999999998</v>
       </c>
-      <c r="S28" s="37">
+      <c r="S28" s="33">
         <f t="shared" si="11"/>
         <v>1.2559999999999998</v>
       </c>
-      <c r="T28" s="167"/>
+      <c r="T28" s="126"/>
     </row>
     <row r="29" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A29" s="7">
         <v>27</v>
       </c>
-      <c r="B29" s="126"/>
-      <c r="C29" s="11" t="s">
+      <c r="B29" s="139"/>
+      <c r="C29" s="177" t="s">
         <v>142</v>
       </c>
-      <c r="D29" s="77" t="s">
+      <c r="D29" s="156" t="s">
         <v>143</v>
       </c>
-      <c r="E29" s="77" t="s">
+      <c r="E29" s="156" t="s">
         <v>144</v>
       </c>
-      <c r="F29" s="77" t="s">
+      <c r="F29" s="156" t="s">
         <v>145</v>
       </c>
-      <c r="G29" s="13" t="s">
+      <c r="G29" s="158" t="s">
         <v>146</v>
       </c>
-      <c r="H29" s="14" t="s">
+      <c r="H29" s="178" t="s">
         <v>147</v>
       </c>
-      <c r="I29" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="J29" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="K29" s="12">
+      <c r="I29" s="159" t="s">
+        <v>35</v>
+      </c>
+      <c r="J29" s="159" t="s">
+        <v>35</v>
+      </c>
+      <c r="K29" s="157">
         <v>1</v>
       </c>
-      <c r="L29" s="53">
+      <c r="L29" s="179">
         <v>6</v>
       </c>
-      <c r="M29" s="23">
+      <c r="M29" s="159">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N29" s="47" t="s">
-        <v>197</v>
-      </c>
-      <c r="O29" s="37">
+      <c r="N29" s="160" t="s">
+        <v>196</v>
+      </c>
+      <c r="O29" s="161">
         <v>0.99</v>
       </c>
-      <c r="P29" s="37">
+      <c r="P29" s="161">
         <f t="shared" si="9"/>
         <v>0.99</v>
       </c>
-      <c r="Q29" s="37">
+      <c r="Q29" s="161">
         <f t="shared" si="10"/>
         <v>5.9399999999999995</v>
       </c>
-      <c r="R29" s="37">
+      <c r="R29" s="161">
         <v>0.99</v>
       </c>
-      <c r="S29" s="37">
+      <c r="S29" s="161">
         <f t="shared" si="11"/>
         <v>4.95</v>
       </c>
-      <c r="T29" s="168" t="s">
+      <c r="T29" s="127" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3951,63 +3999,63 @@
       <c r="A30" s="7">
         <v>28</v>
       </c>
-      <c r="B30" s="127"/>
-      <c r="C30" s="85" t="s">
+      <c r="B30" s="140"/>
+      <c r="C30" s="180" t="s">
         <v>148</v>
       </c>
-      <c r="D30" s="79" t="s">
+      <c r="D30" s="181" t="s">
         <v>149</v>
       </c>
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="182" t="s">
         <v>150</v>
       </c>
-      <c r="F30" s="79" t="s">
+      <c r="F30" s="181" t="s">
         <v>151</v>
       </c>
-      <c r="G30" s="17" t="s">
+      <c r="G30" s="183" t="s">
         <v>152</v>
       </c>
-      <c r="H30" s="18" t="s">
+      <c r="H30" s="184" t="s">
         <v>153</v>
       </c>
-      <c r="I30" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="J30" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="K30" s="16">
+      <c r="I30" s="185" t="s">
+        <v>35</v>
+      </c>
+      <c r="J30" s="183" t="s">
+        <v>35</v>
+      </c>
+      <c r="K30" s="182">
         <v>1</v>
       </c>
-      <c r="L30" s="54">
+      <c r="L30" s="186">
         <v>6</v>
       </c>
-      <c r="M30" s="28">
+      <c r="M30" s="185">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N30" s="39" t="s">
+      <c r="N30" s="187" t="s">
         <v>29</v>
       </c>
-      <c r="O30" s="41">
+      <c r="O30" s="188">
         <v>3.1053000000000002</v>
       </c>
-      <c r="P30" s="41">
+      <c r="P30" s="188">
         <f t="shared" si="9"/>
         <v>3.1053000000000002</v>
       </c>
-      <c r="Q30" s="41">
+      <c r="Q30" s="188">
         <f t="shared" si="10"/>
         <v>18.631800000000002</v>
       </c>
-      <c r="R30" s="71">
+      <c r="R30" s="189">
         <v>3.1053000000000002</v>
       </c>
-      <c r="S30" s="41">
+      <c r="S30" s="188">
         <f t="shared" si="11"/>
         <v>15.5265</v>
       </c>
-      <c r="T30" s="99" t="s">
+      <c r="T30" s="83" t="s">
         <v>195</v>
       </c>
     </row>
@@ -4015,220 +4063,220 @@
       <c r="A31" s="7">
         <v>29</v>
       </c>
-      <c r="B31" s="128" t="s">
+      <c r="B31" s="141" t="s">
         <v>154</v>
       </c>
-      <c r="C31" s="135" t="s">
+      <c r="C31" s="107" t="s">
         <v>155</v>
       </c>
-      <c r="D31" s="88" t="s">
+      <c r="D31" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E31" s="163" t="s">
+      <c r="E31" s="122" t="s">
         <v>76</v>
       </c>
-      <c r="F31" s="88" t="s">
+      <c r="F31" s="72" t="s">
         <v>157</v>
       </c>
-      <c r="G31" s="86" t="s">
+      <c r="G31" s="70" t="s">
         <v>158</v>
       </c>
-      <c r="H31" s="87" t="s">
+      <c r="H31" s="71" t="s">
         <v>159</v>
       </c>
-      <c r="I31" s="90" t="s">
-        <v>35</v>
-      </c>
-      <c r="J31" s="86" t="s">
-        <v>35</v>
-      </c>
-      <c r="K31" s="164">
+      <c r="I31" s="74" t="s">
+        <v>35</v>
+      </c>
+      <c r="J31" s="70" t="s">
+        <v>35</v>
+      </c>
+      <c r="K31" s="123">
         <v>1</v>
       </c>
-      <c r="L31" s="165">
+      <c r="L31" s="124">
         <v>7</v>
       </c>
-      <c r="M31" s="90">
+      <c r="M31" s="74">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N31" s="132" t="s">
+      <c r="N31" s="104" t="s">
         <v>29</v>
       </c>
-      <c r="O31" s="133">
+      <c r="O31" s="105">
         <v>0.22420000000000001</v>
       </c>
-      <c r="P31" s="133">
+      <c r="P31" s="105">
         <f t="shared" si="9"/>
         <v>0.22420000000000001</v>
       </c>
-      <c r="Q31" s="133">
+      <c r="Q31" s="105">
         <f t="shared" si="10"/>
         <v>1.5694000000000001</v>
       </c>
-      <c r="R31" s="133">
+      <c r="R31" s="105">
         <v>0.22420000000000001</v>
       </c>
-      <c r="S31" s="133">
+      <c r="S31" s="105">
         <f t="shared" si="11"/>
         <v>1.121</v>
       </c>
-      <c r="T31" s="166"/>
+      <c r="T31" s="125"/>
     </row>
     <row r="32" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A32" s="7">
         <v>30</v>
       </c>
-      <c r="B32" s="128"/>
-      <c r="C32" s="100" t="s">
+      <c r="B32" s="141"/>
+      <c r="C32" s="84" t="s">
         <v>160</v>
       </c>
-      <c r="D32" s="101" t="s">
+      <c r="D32" s="85" t="s">
         <v>161</v>
       </c>
-      <c r="E32" s="101" t="s">
+      <c r="E32" s="85" t="s">
         <v>76</v>
       </c>
-      <c r="F32" s="104" t="s">
+      <c r="F32" s="88" t="s">
         <v>162</v>
       </c>
-      <c r="G32" s="106" t="s">
-        <v>35</v>
-      </c>
-      <c r="H32" s="106" t="s">
-        <v>35</v>
-      </c>
-      <c r="I32" s="106" t="s">
-        <v>35</v>
-      </c>
-      <c r="J32" s="106" t="s">
-        <v>35</v>
-      </c>
-      <c r="K32" s="106">
+      <c r="G32" s="90" t="s">
+        <v>35</v>
+      </c>
+      <c r="H32" s="90" t="s">
+        <v>35</v>
+      </c>
+      <c r="I32" s="90" t="s">
+        <v>35</v>
+      </c>
+      <c r="J32" s="90" t="s">
+        <v>35</v>
+      </c>
+      <c r="K32" s="90">
         <v>1</v>
       </c>
-      <c r="L32" s="106" t="s">
-        <v>35</v>
-      </c>
-      <c r="M32" s="107">
+      <c r="L32" s="90" t="s">
+        <v>35</v>
+      </c>
+      <c r="M32" s="91">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N32" s="108" t="s">
-        <v>35</v>
-      </c>
-      <c r="O32" s="109" t="s">
-        <v>35</v>
-      </c>
-      <c r="P32" s="109" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q32" s="109" t="s">
-        <v>35</v>
-      </c>
-      <c r="R32" s="109" t="s">
-        <v>35</v>
-      </c>
-      <c r="S32" s="109" t="s">
-        <v>35</v>
-      </c>
-      <c r="T32" s="110" t="s">
-        <v>198</v>
+      <c r="N32" s="92" t="s">
+        <v>35</v>
+      </c>
+      <c r="O32" s="93" t="s">
+        <v>35</v>
+      </c>
+      <c r="P32" s="93" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q32" s="93" t="s">
+        <v>35</v>
+      </c>
+      <c r="R32" s="93" t="s">
+        <v>35</v>
+      </c>
+      <c r="S32" s="93" t="s">
+        <v>35</v>
+      </c>
+      <c r="T32" s="94" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="33" spans="1:20" ht="15" customHeight="1" thickBot="1">
       <c r="A33" s="7">
         <v>31</v>
       </c>
-      <c r="B33" s="129"/>
-      <c r="C33" s="102" t="s">
+      <c r="B33" s="142"/>
+      <c r="C33" s="86" t="s">
         <v>163</v>
       </c>
-      <c r="D33" s="103" t="s">
+      <c r="D33" s="87" t="s">
         <v>164</v>
       </c>
-      <c r="E33" s="103" t="s">
+      <c r="E33" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="F33" s="105" t="s">
+      <c r="F33" s="89" t="s">
         <v>165</v>
       </c>
-      <c r="G33" s="111" t="s">
-        <v>35</v>
-      </c>
-      <c r="H33" s="112" t="s">
-        <v>35</v>
-      </c>
-      <c r="I33" s="112" t="s">
-        <v>35</v>
-      </c>
-      <c r="J33" s="112" t="s">
-        <v>35</v>
-      </c>
-      <c r="K33" s="112">
+      <c r="G33" s="95" t="s">
+        <v>35</v>
+      </c>
+      <c r="H33" s="96" t="s">
+        <v>35</v>
+      </c>
+      <c r="I33" s="96" t="s">
+        <v>35</v>
+      </c>
+      <c r="J33" s="96" t="s">
+        <v>35</v>
+      </c>
+      <c r="K33" s="96">
         <v>5</v>
       </c>
-      <c r="L33" s="112" t="s">
-        <v>35</v>
-      </c>
-      <c r="M33" s="113">
+      <c r="L33" s="96" t="s">
+        <v>35</v>
+      </c>
+      <c r="M33" s="97">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="N33" s="114" t="s">
-        <v>35</v>
-      </c>
-      <c r="O33" s="115" t="s">
-        <v>35</v>
-      </c>
-      <c r="P33" s="115" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q33" s="115" t="s">
-        <v>35</v>
-      </c>
-      <c r="R33" s="115" t="s">
-        <v>35</v>
-      </c>
-      <c r="S33" s="115" t="s">
-        <v>35</v>
-      </c>
-      <c r="T33" s="116" t="s">
-        <v>198</v>
+      <c r="N33" s="98" t="s">
+        <v>35</v>
+      </c>
+      <c r="O33" s="99" t="s">
+        <v>35</v>
+      </c>
+      <c r="P33" s="99" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q33" s="99" t="s">
+        <v>35</v>
+      </c>
+      <c r="R33" s="99" t="s">
+        <v>35</v>
+      </c>
+      <c r="S33" s="99" t="s">
+        <v>35</v>
+      </c>
+      <c r="T33" s="100" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="34" spans="1:20" ht="19.5" thickBot="1">
-      <c r="K34" s="123" t="s">
+      <c r="K34" s="133" t="s">
         <v>166</v>
       </c>
-      <c r="L34" s="123"/>
-      <c r="M34" s="123"/>
-      <c r="N34" s="123"/>
-      <c r="O34" s="55">
+      <c r="L34" s="133"/>
+      <c r="M34" s="133"/>
+      <c r="N34" s="133"/>
+      <c r="O34" s="46">
         <f>SUM(O3:O31)</f>
-        <v>9.8609100000000005</v>
-      </c>
-      <c r="P34" s="56"/>
-      <c r="Q34" s="55">
+        <v>10.142300000000001</v>
+      </c>
+      <c r="P34" s="47"/>
+      <c r="Q34" s="46">
         <f>SUM(Q3:Q31)</f>
-        <v>69.812219999999996</v>
+        <v>85.510799999999989</v>
       </c>
     </row>
     <row r="35" spans="1:20" ht="18.75">
-      <c r="K35" s="124" t="s">
+      <c r="K35" s="134" t="s">
         <v>167</v>
       </c>
-      <c r="L35" s="124"/>
-      <c r="M35" s="124"/>
-      <c r="N35" s="124"/>
-      <c r="O35" s="57">
+      <c r="L35" s="134"/>
+      <c r="M35" s="134"/>
+      <c r="N35" s="134"/>
+      <c r="O35" s="48">
         <f>SUM(O33:O34)</f>
-        <v>9.8609100000000005</v>
-      </c>
-      <c r="P35" s="56"/>
-      <c r="Q35" s="57">
+        <v>10.142300000000001</v>
+      </c>
+      <c r="P35" s="47"/>
+      <c r="Q35" s="48">
         <f>Q34/5</f>
-        <v>13.962444</v>
+        <v>17.102159999999998</v>
       </c>
     </row>
   </sheetData>
@@ -4678,21 +4726,21 @@
     <hyperlink ref="N3" r:id="rId10"/>
     <hyperlink ref="N5" r:id="rId11"/>
     <hyperlink ref="N13" r:id="rId12"/>
-    <hyperlink ref="N14" r:id="rId13"/>
-    <hyperlink ref="N22" r:id="rId14"/>
-    <hyperlink ref="N24" r:id="rId15"/>
-    <hyperlink ref="N20" r:id="rId16"/>
-    <hyperlink ref="N21" r:id="rId17"/>
-    <hyperlink ref="N23" r:id="rId18"/>
-    <hyperlink ref="N30" r:id="rId19"/>
-    <hyperlink ref="N4" r:id="rId20"/>
-    <hyperlink ref="N8" r:id="rId21"/>
-    <hyperlink ref="N9" r:id="rId22"/>
-    <hyperlink ref="N10" r:id="rId23"/>
-    <hyperlink ref="N11" r:id="rId24"/>
-    <hyperlink ref="N26" r:id="rId25"/>
-    <hyperlink ref="N29" r:id="rId26"/>
-    <hyperlink ref="N27" r:id="rId27"/>
+    <hyperlink ref="N22" r:id="rId13"/>
+    <hyperlink ref="N24" r:id="rId14"/>
+    <hyperlink ref="N20" r:id="rId15"/>
+    <hyperlink ref="N21" r:id="rId16"/>
+    <hyperlink ref="N23" r:id="rId17"/>
+    <hyperlink ref="N30" r:id="rId18"/>
+    <hyperlink ref="N4" r:id="rId19"/>
+    <hyperlink ref="N8" r:id="rId20"/>
+    <hyperlink ref="N9" r:id="rId21"/>
+    <hyperlink ref="N10" r:id="rId22"/>
+    <hyperlink ref="N11" r:id="rId23"/>
+    <hyperlink ref="N29" r:id="rId24"/>
+    <hyperlink ref="N27" r:id="rId25"/>
+    <hyperlink ref="N14" r:id="rId26"/>
+    <hyperlink ref="N26" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId28"/>
